--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,24 +11,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="165">
-  <si>
-    <t>200006232</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="140">
+  <si>
+    <t>200006299</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>4060000060C1</t>
-  </si>
-  <si>
-    <t>0920</t>
+    <t>080100152306</t>
+  </si>
+  <si>
+    <t>0020</t>
   </si>
   <si>
     <t>EA</t>
   </si>
   <si>
-    <t>活塞外套/A軸前_D290*d115*L67.2</t>
+    <t>DA15K 主軸,021856_BT40,M60,CWDIN</t>
   </si>
   <si>
     <t>0</t>
@@ -40,177 +40,144 @@
     <t>SHEO</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>1F004</t>
+  </si>
+  <si>
+    <t>組件課</t>
+  </si>
+  <si>
+    <t>REL</t>
+  </si>
+  <si>
+    <t>0802</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>200006330</t>
+  </si>
+  <si>
+    <t>080100036004</t>
+  </si>
+  <si>
+    <t>0040</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,C045</t>
+  </si>
+  <si>
+    <t>200006367</t>
+  </si>
+  <si>
+    <t>303500039801</t>
+  </si>
+  <si>
+    <t>單列斜角滾珠軸承_FAG-HS7018C.T.P4S.UL,2個1組</t>
+  </si>
+  <si>
+    <t>0128</t>
+  </si>
+  <si>
+    <t>9804</t>
+  </si>
+  <si>
+    <t>8420002329A1</t>
+  </si>
+  <si>
+    <t>0290</t>
+  </si>
+  <si>
+    <t>間隔環,前內_d90.5*D113*24,HSA2215</t>
+  </si>
+  <si>
+    <t>0102</t>
+  </si>
+  <si>
+    <t>8420002330A1</t>
+  </si>
+  <si>
+    <t>0300</t>
+  </si>
+  <si>
+    <t>間隔環,前外_d117*D140*24,HSA2215</t>
+  </si>
+  <si>
+    <t>8423000097A2</t>
+  </si>
+  <si>
+    <t>0420</t>
+  </si>
+  <si>
+    <t>吹氣環_d127xD138x14H</t>
+  </si>
+  <si>
+    <t>3154001543B3</t>
+  </si>
+  <si>
+    <t>0440</t>
+  </si>
+  <si>
+    <t>主軸前蓋_d127*D195*33L</t>
+  </si>
+  <si>
+    <t>200006368</t>
+  </si>
+  <si>
+    <t>080100113204</t>
+  </si>
+  <si>
+    <t>0060</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CW45</t>
+  </si>
+  <si>
+    <t>8814001257B3</t>
+  </si>
+  <si>
+    <t>0170</t>
+  </si>
+  <si>
+    <t>機頭加工圖,G6K_HCMC-2110</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>200006370</t>
+  </si>
+  <si>
+    <t>080100033903</t>
+  </si>
+  <si>
+    <t>0080</t>
+  </si>
+  <si>
+    <t>G2.5K主軸,010830_BT50,C0DIN</t>
+  </si>
+  <si>
+    <t>1X001</t>
+  </si>
+  <si>
+    <t>虛擬工作中心</t>
+  </si>
+  <si>
+    <t>8921000777A0</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>感應器支撐架_D30104H,D70*10H</t>
+  </si>
+  <si>
     <t>0101</t>
   </si>
   <si>
-    <t>1X001</t>
-  </si>
-  <si>
-    <t>虛擬工作中心</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>9816</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>200006299</t>
-  </si>
-  <si>
-    <t>080100152306</t>
-  </si>
-  <si>
-    <t>0020</t>
-  </si>
-  <si>
-    <t>DA15K 主軸,021856_BT40,M60,CWDIN</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>1F004</t>
-  </si>
-  <si>
-    <t>組件課</t>
-  </si>
-  <si>
-    <t>0802</t>
-  </si>
-  <si>
-    <t>200006330</t>
-  </si>
-  <si>
-    <t>080100036004</t>
-  </si>
-  <si>
-    <t>0040</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,C045</t>
-  </si>
-  <si>
-    <t>200006367</t>
-  </si>
-  <si>
-    <t>303500039801</t>
-  </si>
-  <si>
-    <t>單列斜角滾珠軸承_FAG-HS7018C.T.P4S.UL,2個1組</t>
-  </si>
-  <si>
-    <t>0128</t>
-  </si>
-  <si>
-    <t>9804</t>
-  </si>
-  <si>
-    <t>8420002329A1</t>
-  </si>
-  <si>
-    <t>0290</t>
-  </si>
-  <si>
-    <t>間隔環,前內_d90.5*D113*24,HSA2215</t>
-  </si>
-  <si>
-    <t>0102</t>
-  </si>
-  <si>
-    <t>8420002330A1</t>
-  </si>
-  <si>
-    <t>0300</t>
-  </si>
-  <si>
-    <t>間隔環,前外_d117*D140*24,HSA2215</t>
-  </si>
-  <si>
-    <t>8423000097A2</t>
-  </si>
-  <si>
-    <t>0420</t>
-  </si>
-  <si>
-    <t>吹氣環_d127xD138x14H</t>
-  </si>
-  <si>
-    <t>3154001543B3</t>
-  </si>
-  <si>
-    <t>0440</t>
-  </si>
-  <si>
-    <t>主軸前蓋_d127*D195*33L</t>
-  </si>
-  <si>
-    <t>200006368</t>
-  </si>
-  <si>
-    <t>080100113204</t>
-  </si>
-  <si>
-    <t>0060</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CW45</t>
-  </si>
-  <si>
-    <t>8814001257B3</t>
-  </si>
-  <si>
-    <t>0170</t>
-  </si>
-  <si>
-    <t>機頭加工圖,G6K_HCMC-2110</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>200006370</t>
-  </si>
-  <si>
-    <t>080100033903</t>
-  </si>
-  <si>
-    <t>0080</t>
-  </si>
-  <si>
-    <t>G2.5K主軸,010830_BT50,C0DIN</t>
-  </si>
-  <si>
-    <t>8921000777A0</t>
-  </si>
-  <si>
-    <t>0110</t>
-  </si>
-  <si>
-    <t>感應器支撐架_D30104H,D70*10H</t>
-  </si>
-  <si>
-    <t>3058000711A0</t>
-  </si>
-  <si>
-    <t>0180</t>
-  </si>
-  <si>
-    <t>左軸承箱,換檔用_PBM-135A</t>
-  </si>
-  <si>
-    <t>3058000712A0</t>
-  </si>
-  <si>
-    <t>0190</t>
-  </si>
-  <si>
-    <t>右軸承箱,換檔用 _PBM-135A</t>
-  </si>
-  <si>
     <t>8016001298A0</t>
   </si>
   <si>
@@ -304,27 +271,6 @@
     <t>0104</t>
   </si>
   <si>
-    <t>881400149200</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>機頭加工圖,G6K,齒比:0.75,Z780_SW-x26</t>
-  </si>
-  <si>
-    <t>200006387</t>
-  </si>
-  <si>
-    <t>4023000092A0</t>
-  </si>
-  <si>
-    <t>油壓缸,內蓋_d27*D90*28L</t>
-  </si>
-  <si>
-    <t>200006391</t>
-  </si>
-  <si>
     <t>200006404</t>
   </si>
   <si>
@@ -349,15 +295,6 @@
     <t>200006433</t>
   </si>
   <si>
-    <t>200006434</t>
-  </si>
-  <si>
-    <t>8814001214D3</t>
-  </si>
-  <si>
-    <t>機頭加工圖,G6K_HCMC-1682</t>
-  </si>
-  <si>
     <t>200006454</t>
   </si>
   <si>
@@ -370,9 +307,6 @@
     <t>機頭加工圖,#50G6K_HCMC-1100</t>
   </si>
   <si>
-    <t>200006465</t>
-  </si>
-  <si>
     <t>200006470</t>
   </si>
   <si>
@@ -397,15 +331,6 @@
     <t>D20K 主軸,010683_A63,M50,C0</t>
   </si>
   <si>
-    <t>312500005000</t>
-  </si>
-  <si>
-    <t>0070</t>
-  </si>
-  <si>
-    <t>油鏡_T4,旭辰</t>
-  </si>
-  <si>
     <t>8311000415A0</t>
   </si>
   <si>
@@ -418,7 +343,7 @@
     <t>馬達固定座_HSA2215/20KRPM</t>
   </si>
   <si>
-    <t>8814001399B0</t>
+    <t>8814001399A4</t>
   </si>
   <si>
     <t>機頭加工圖,Z780_#40,D20K</t>
@@ -610,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -642,79 +567,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -731,7 +656,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="2">
-        <v>46009</v>
+        <v>46059</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -808,7 +733,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="2">
-        <v>46059</v>
+        <v>46034</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -838,13 +763,13 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R3" t="s">
         <v>1</v>
@@ -856,7 +781,7 @@
         <v>12</v>
       </c>
       <c r="U3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V3" t="s">
         <v>1</v>
@@ -873,67 +798,67 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46086</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="3">
+        <v>2</v>
+      </c>
+      <c r="T4" t="s">
+        <v>12</v>
+      </c>
+      <c r="U4" t="s">
         <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="2">
-        <v>46034</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" t="s">
-        <v>1</v>
-      </c>
-      <c r="O4" t="s">
-        <v>19</v>
-      </c>
-      <c r="P4" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R4" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="3">
-        <v>1</v>
-      </c>
-      <c r="T4" t="s">
-        <v>12</v>
-      </c>
-      <c r="U4" t="s">
-        <v>22</v>
       </c>
       <c r="V4" t="s">
         <v>1</v>
@@ -950,34 +875,34 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2">
         <v>46086</v>
       </c>
       <c r="F5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="s">
         <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s">
         <v>6</v>
@@ -992,25 +917,25 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R5" t="s">
         <v>1</v>
       </c>
       <c r="S5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T5" t="s">
         <v>12</v>
       </c>
       <c r="U5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V5" t="s">
         <v>1</v>
@@ -1027,16 +952,16 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2">
         <v>46086</v>
@@ -1054,7 +979,7 @@
         <v>4</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
         <v>6</v>
@@ -1069,13 +994,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R6" t="s">
         <v>1</v>
@@ -1087,7 +1012,7 @@
         <v>12</v>
       </c>
       <c r="U6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V6" t="s">
         <v>1</v>
@@ -1104,16 +1029,16 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2">
         <v>46086</v>
@@ -1131,7 +1056,7 @@
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K7" t="s">
         <v>6</v>
@@ -1146,13 +1071,13 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R7" t="s">
         <v>1</v>
@@ -1164,7 +1089,7 @@
         <v>12</v>
       </c>
       <c r="U7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V7" t="s">
         <v>1</v>
@@ -1181,16 +1106,16 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2">
         <v>46086</v>
@@ -1208,7 +1133,7 @@
         <v>4</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
         <v>6</v>
@@ -1223,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="P8" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R8" t="s">
         <v>1</v>
@@ -1241,7 +1166,7 @@
         <v>12</v>
       </c>
       <c r="U8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V8" t="s">
         <v>1</v>
@@ -1258,19 +1183,19 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2">
-        <v>46086</v>
+        <v>46101</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -1285,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K9" t="s">
         <v>6</v>
@@ -1300,13 +1225,13 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="P9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R9" t="s">
         <v>1</v>
@@ -1318,7 +1243,7 @@
         <v>12</v>
       </c>
       <c r="U9" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="V9" t="s">
         <v>1</v>
@@ -1335,16 +1260,16 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2">
         <v>46101</v>
@@ -1362,7 +1287,7 @@
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
         <v>6</v>
@@ -1377,13 +1302,13 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="P10" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R10" t="s">
         <v>1</v>
@@ -1395,7 +1320,7 @@
         <v>12</v>
       </c>
       <c r="U10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V10" t="s">
         <v>1</v>
@@ -1418,50 +1343,50 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46064</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
+        <v>9</v>
+      </c>
+      <c r="P11" t="s">
         <v>49</v>
       </c>
-      <c r="D11" t="s">
+      <c r="Q11" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="2">
-        <v>46101</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" t="s">
-        <v>6</v>
-      </c>
-      <c r="L11" t="s">
-        <v>7</v>
-      </c>
-      <c r="M11" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" t="s">
-        <v>1</v>
-      </c>
-      <c r="O11" t="s">
-        <v>52</v>
-      </c>
-      <c r="P11" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>21</v>
-      </c>
       <c r="R11" t="s">
         <v>1</v>
       </c>
@@ -1472,7 +1397,7 @@
         <v>12</v>
       </c>
       <c r="U11" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="V11" t="s">
         <v>1</v>
@@ -1489,16 +1414,16 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2">
         <v>46064</v>
@@ -1516,7 +1441,7 @@
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K12" t="s">
         <v>6</v>
@@ -1531,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="P12" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="Q12" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="R12" t="s">
         <v>1</v>
@@ -1549,7 +1474,7 @@
         <v>12</v>
       </c>
       <c r="U12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -1566,16 +1491,16 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2">
         <v>46064</v>
@@ -1593,40 +1518,40 @@
         <v>4</v>
       </c>
       <c r="J13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" t="s">
+        <v>7</v>
+      </c>
+      <c r="M13" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>58</v>
+      </c>
+      <c r="P13" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>50</v>
+      </c>
+      <c r="R13" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13" s="3">
+        <v>1</v>
+      </c>
+      <c r="T13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U13" t="s">
         <v>59</v>
-      </c>
-      <c r="K13" t="s">
-        <v>6</v>
-      </c>
-      <c r="L13" t="s">
-        <v>7</v>
-      </c>
-      <c r="M13" t="s">
-        <v>8</v>
-      </c>
-      <c r="N13" t="s">
-        <v>1</v>
-      </c>
-      <c r="O13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P13" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>11</v>
-      </c>
-      <c r="R13" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="3">
-        <v>1</v>
-      </c>
-      <c r="T13" t="s">
-        <v>12</v>
-      </c>
-      <c r="U13" t="s">
-        <v>31</v>
       </c>
       <c r="V13" t="s">
         <v>1</v>
@@ -1643,25 +1568,25 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2">
-        <v>46064</v>
+        <v>46052</v>
       </c>
       <c r="F14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>1</v>
@@ -1685,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="O14" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="P14" t="s">
         <v>10</v>
@@ -1697,13 +1622,13 @@
         <v>1</v>
       </c>
       <c r="S14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" t="s">
         <v>12</v>
       </c>
       <c r="U14" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V14" t="s">
         <v>1</v>
@@ -1720,25 +1645,25 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2">
-        <v>46064</v>
+        <v>46100</v>
       </c>
       <c r="F15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>1</v>
@@ -1747,7 +1672,7 @@
         <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K15" t="s">
         <v>6</v>
@@ -1762,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="P15" t="s">
         <v>10</v>
@@ -1774,13 +1699,13 @@
         <v>1</v>
       </c>
       <c r="S15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" t="s">
         <v>12</v>
       </c>
       <c r="U15" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V15" t="s">
         <v>1</v>
@@ -1797,19 +1722,19 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
         <v>67</v>
       </c>
       <c r="E16" s="2">
-        <v>46064</v>
+        <v>46100</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
@@ -1824,7 +1749,7 @@
         <v>4</v>
       </c>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="K16" t="s">
         <v>6</v>
@@ -1839,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="P16" t="s">
         <v>10</v>
@@ -1857,7 +1782,7 @@
         <v>12</v>
       </c>
       <c r="U16" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="V16" t="s">
         <v>1</v>
@@ -1874,19 +1799,19 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2">
-        <v>46052</v>
+        <v>46100</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -1901,7 +1826,7 @@
         <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="K17" t="s">
         <v>6</v>
@@ -1916,13 +1841,13 @@
         <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="P17" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R17" t="s">
         <v>1</v>
@@ -1934,7 +1859,7 @@
         <v>12</v>
       </c>
       <c r="U17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V17" t="s">
         <v>1</v>
@@ -1951,19 +1876,19 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2">
-        <v>46100</v>
+        <v>46048</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -1978,7 +1903,7 @@
         <v>4</v>
       </c>
       <c r="J18" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K18" t="s">
         <v>6</v>
@@ -1990,16 +1915,16 @@
         <v>8</v>
       </c>
       <c r="N18" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="O18" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="P18" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R18" t="s">
         <v>1</v>
@@ -2011,7 +1936,7 @@
         <v>12</v>
       </c>
       <c r="U18" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V18" t="s">
         <v>1</v>
@@ -2028,35 +1953,35 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>46048</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" t="s">
         <v>74</v>
       </c>
-      <c r="B19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="2">
-        <v>46100</v>
-      </c>
-      <c r="F19" s="3">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" t="s">
-        <v>34</v>
-      </c>
       <c r="K19" t="s">
         <v>6</v>
       </c>
@@ -2070,13 +1995,13 @@
         <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="P19" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R19" t="s">
         <v>1</v>
@@ -2088,7 +2013,7 @@
         <v>12</v>
       </c>
       <c r="U19" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="V19" t="s">
         <v>1</v>
@@ -2105,19 +2030,19 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2">
-        <v>46100</v>
+        <v>46048</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
@@ -2132,7 +2057,7 @@
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s">
         <v>6</v>
@@ -2144,16 +2069,16 @@
         <v>8</v>
       </c>
       <c r="N20" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="O20" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="P20" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R20" t="s">
         <v>1</v>
@@ -2165,7 +2090,7 @@
         <v>12</v>
       </c>
       <c r="U20" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V20" t="s">
         <v>1</v>
@@ -2182,19 +2107,19 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
         <v>80</v>
       </c>
-      <c r="B21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>81</v>
       </c>
-      <c r="D21" t="s">
-        <v>7</v>
-      </c>
       <c r="E21" s="2">
-        <v>46111</v>
+        <v>46063</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -2221,16 +2146,16 @@
         <v>8</v>
       </c>
       <c r="N21" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="P21" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R21" t="s">
         <v>1</v>
@@ -2242,7 +2167,7 @@
         <v>12</v>
       </c>
       <c r="U21" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="V21" t="s">
         <v>1</v>
@@ -2259,55 +2184,55 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
       <c r="C22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46063</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" t="s">
         <v>84</v>
       </c>
-      <c r="D22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="2">
-        <v>46111</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1</v>
-      </c>
-      <c r="I22" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" t="s">
+        <v>1</v>
+      </c>
+      <c r="O22" t="s">
         <v>85</v>
       </c>
-      <c r="K22" t="s">
-        <v>6</v>
-      </c>
-      <c r="L22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M22" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" t="s">
-        <v>1</v>
-      </c>
-      <c r="O22" t="s">
-        <v>86</v>
-      </c>
       <c r="P22" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R22" t="s">
         <v>1</v>
@@ -2319,7 +2244,7 @@
         <v>12</v>
       </c>
       <c r="U22" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="V22" t="s">
         <v>1</v>
@@ -2336,19 +2261,19 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>46111</v>
+        <v>46038</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
@@ -2363,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="K23" t="s">
         <v>6</v>
@@ -2375,16 +2300,16 @@
         <v>8</v>
       </c>
       <c r="N23" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="P23" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R23" t="s">
         <v>1</v>
@@ -2396,7 +2321,7 @@
         <v>12</v>
       </c>
       <c r="U23" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="V23" t="s">
         <v>1</v>
@@ -2413,19 +2338,19 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E24" s="2">
-        <v>46063</v>
+        <v>46041</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -2440,7 +2365,7 @@
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="K24" t="s">
         <v>6</v>
@@ -2455,13 +2380,13 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R24" t="s">
         <v>1</v>
@@ -2473,7 +2398,7 @@
         <v>12</v>
       </c>
       <c r="U24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V24" t="s">
         <v>1</v>
@@ -2490,19 +2415,19 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="E25" s="2">
-        <v>46063</v>
+        <v>46041</v>
       </c>
       <c r="F25" s="3">
         <v>1</v>
@@ -2517,7 +2442,7 @@
         <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="K25" t="s">
         <v>6</v>
@@ -2532,13 +2457,13 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="P25" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R25" t="s">
         <v>1</v>
@@ -2550,7 +2475,7 @@
         <v>12</v>
       </c>
       <c r="U25" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V25" t="s">
         <v>1</v>
@@ -2567,19 +2492,19 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E26" s="2">
-        <v>46063</v>
+        <v>46034</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
@@ -2594,7 +2519,7 @@
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="K26" t="s">
         <v>6</v>
@@ -2609,13 +2534,13 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="P26" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R26" t="s">
         <v>1</v>
@@ -2627,7 +2552,7 @@
         <v>12</v>
       </c>
       <c r="U26" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V26" t="s">
         <v>1</v>
@@ -2644,34 +2569,34 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2">
-        <v>46002</v>
+        <v>46078</v>
       </c>
       <c r="F27" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G27" s="3">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27" t="s">
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s">
         <v>6</v>
@@ -2689,22 +2614,22 @@
         <v>9</v>
       </c>
       <c r="P27" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R27" t="s">
         <v>1</v>
       </c>
       <c r="S27" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T27" t="s">
         <v>12</v>
       </c>
       <c r="U27" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="V27" t="s">
         <v>1</v>
@@ -2721,34 +2646,34 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2">
-        <v>46037</v>
+        <v>46078</v>
       </c>
       <c r="F28" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G28" s="3">
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28" t="s">
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="K28" t="s">
         <v>6</v>
@@ -2763,25 +2688,25 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="P28" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R28" t="s">
         <v>1</v>
       </c>
       <c r="S28" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T28" t="s">
         <v>12</v>
       </c>
       <c r="U28" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V28" t="s">
         <v>1</v>
@@ -2798,19 +2723,19 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="E29" s="2">
-        <v>46038</v>
+        <v>46063</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
@@ -2825,7 +2750,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="K29" t="s">
         <v>6</v>
@@ -2840,13 +2765,13 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="P29" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R29" t="s">
         <v>1</v>
@@ -2858,7 +2783,7 @@
         <v>12</v>
       </c>
       <c r="U29" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="V29" t="s">
         <v>1</v>
@@ -2875,19 +2800,19 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E30" s="2">
-        <v>46041</v>
+        <v>46063</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
@@ -2902,7 +2827,7 @@
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K30" t="s">
         <v>6</v>
@@ -2917,13 +2842,13 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="P30" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R30" t="s">
         <v>1</v>
@@ -2935,7 +2860,7 @@
         <v>12</v>
       </c>
       <c r="U30" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V30" t="s">
         <v>1</v>
@@ -2952,19 +2877,19 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E31" s="2">
-        <v>46041</v>
+        <v>46065</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -2979,28 +2904,28 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
+        <v>97</v>
+      </c>
+      <c r="K31" t="s">
+        <v>6</v>
+      </c>
+      <c r="L31" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" t="s">
+        <v>8</v>
+      </c>
+      <c r="N31" t="s">
+        <v>1</v>
+      </c>
+      <c r="O31" t="s">
         <v>44</v>
       </c>
-      <c r="K31" t="s">
-        <v>6</v>
-      </c>
-      <c r="L31" t="s">
-        <v>7</v>
-      </c>
-      <c r="M31" t="s">
-        <v>8</v>
-      </c>
-      <c r="N31" t="s">
-        <v>1</v>
-      </c>
-      <c r="O31" t="s">
-        <v>35</v>
-      </c>
       <c r="P31" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R31" t="s">
         <v>1</v>
@@ -3012,7 +2937,7 @@
         <v>12</v>
       </c>
       <c r="U31" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V31" t="s">
         <v>1</v>
@@ -3029,19 +2954,19 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E32" s="2">
-        <v>46034</v>
+        <v>46066</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -3056,7 +2981,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="K32" t="s">
         <v>6</v>
@@ -3071,13 +2996,13 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="P32" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R32" t="s">
         <v>1</v>
@@ -3089,7 +3014,7 @@
         <v>12</v>
       </c>
       <c r="U32" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V32" t="s">
         <v>1</v>
@@ -3106,19 +3031,19 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E33" s="2">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
@@ -3133,7 +3058,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="K33" t="s">
         <v>6</v>
@@ -3148,25 +3073,25 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P33" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R33" t="s">
         <v>1</v>
       </c>
       <c r="S33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="s">
         <v>12</v>
       </c>
       <c r="U33" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="V33" t="s">
         <v>1</v>
@@ -3183,25 +3108,25 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E34" s="2">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="F34" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3">
         <v>1</v>
@@ -3210,7 +3135,7 @@
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="K34" t="s">
         <v>6</v>
@@ -3225,13 +3150,13 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P34" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R34" t="s">
         <v>1</v>
@@ -3243,7 +3168,7 @@
         <v>12</v>
       </c>
       <c r="U34" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V34" t="s">
         <v>1</v>
@@ -3260,19 +3185,19 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E35" s="2">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
@@ -3287,7 +3212,7 @@
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="K35" t="s">
         <v>6</v>
@@ -3302,25 +3227,25 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="P35" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R35" t="s">
         <v>1</v>
       </c>
       <c r="S35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" t="s">
         <v>12</v>
       </c>
       <c r="U35" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="V35" t="s">
         <v>1</v>
@@ -3337,19 +3262,19 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="E36" s="2">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -3364,7 +3289,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="K36" t="s">
         <v>6</v>
@@ -3379,25 +3304,25 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="P36" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q36" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R36" t="s">
         <v>1</v>
       </c>
       <c r="S36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="s">
         <v>12</v>
       </c>
       <c r="U36" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="V36" t="s">
         <v>1</v>
@@ -3414,19 +3339,19 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E37" s="2">
-        <v>46056</v>
+        <v>46050</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -3441,7 +3366,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K37" t="s">
         <v>6</v>
@@ -3456,25 +3381,25 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P37" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R37" t="s">
         <v>1</v>
       </c>
       <c r="S37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="s">
         <v>12</v>
       </c>
       <c r="U37" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="V37" t="s">
         <v>1</v>
@@ -3491,19 +3416,19 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="E38" s="2">
-        <v>46065</v>
+        <v>46044</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
@@ -3518,7 +3443,7 @@
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K38" t="s">
         <v>6</v>
@@ -3533,25 +3458,25 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P38" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="R38" t="s">
         <v>1</v>
       </c>
       <c r="S38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="s">
         <v>12</v>
       </c>
       <c r="U38" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="V38" t="s">
         <v>1</v>
@@ -3563,699 +3488,6 @@
         <v>1</v>
       </c>
       <c r="Y38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25">
-      <c r="A39" t="s">
-        <v>119</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F39" s="3">
-        <v>4</v>
-      </c>
-      <c r="G39" s="3">
-        <v>0</v>
-      </c>
-      <c r="H39" s="3">
-        <v>4</v>
-      </c>
-      <c r="I39" t="s">
-        <v>4</v>
-      </c>
-      <c r="J39" t="s">
-        <v>102</v>
-      </c>
-      <c r="K39" t="s">
-        <v>6</v>
-      </c>
-      <c r="L39" t="s">
-        <v>7</v>
-      </c>
-      <c r="M39" t="s">
-        <v>8</v>
-      </c>
-      <c r="N39" t="s">
-        <v>1</v>
-      </c>
-      <c r="O39" t="s">
-        <v>9</v>
-      </c>
-      <c r="P39" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>21</v>
-      </c>
-      <c r="R39" t="s">
-        <v>1</v>
-      </c>
-      <c r="S39" s="3">
-        <v>4</v>
-      </c>
-      <c r="T39" t="s">
-        <v>12</v>
-      </c>
-      <c r="U39" t="s">
-        <v>31</v>
-      </c>
-      <c r="V39" t="s">
-        <v>1</v>
-      </c>
-      <c r="W39" t="s">
-        <v>1</v>
-      </c>
-      <c r="X39" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25">
-      <c r="A40" t="s">
-        <v>120</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D40" t="s">
-        <v>122</v>
-      </c>
-      <c r="E40" s="2">
-        <v>46066</v>
-      </c>
-      <c r="F40" s="3">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3">
-        <v>0</v>
-      </c>
-      <c r="H40" s="3">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>4</v>
-      </c>
-      <c r="J40" t="s">
-        <v>123</v>
-      </c>
-      <c r="K40" t="s">
-        <v>6</v>
-      </c>
-      <c r="L40" t="s">
-        <v>7</v>
-      </c>
-      <c r="M40" t="s">
-        <v>8</v>
-      </c>
-      <c r="N40" t="s">
-        <v>1</v>
-      </c>
-      <c r="O40" t="s">
-        <v>86</v>
-      </c>
-      <c r="P40" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>21</v>
-      </c>
-      <c r="R40" t="s">
-        <v>1</v>
-      </c>
-      <c r="S40" s="3">
-        <v>1</v>
-      </c>
-      <c r="T40" t="s">
-        <v>12</v>
-      </c>
-      <c r="U40" t="s">
-        <v>31</v>
-      </c>
-      <c r="V40" t="s">
-        <v>1</v>
-      </c>
-      <c r="W40" t="s">
-        <v>1</v>
-      </c>
-      <c r="X40" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25">
-      <c r="A41" t="s">
-        <v>124</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" t="s">
-        <v>127</v>
-      </c>
-      <c r="K41" t="s">
-        <v>6</v>
-      </c>
-      <c r="L41" t="s">
-        <v>7</v>
-      </c>
-      <c r="M41" t="s">
-        <v>8</v>
-      </c>
-      <c r="N41" t="s">
-        <v>1</v>
-      </c>
-      <c r="O41" t="s">
-        <v>19</v>
-      </c>
-      <c r="P41" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>21</v>
-      </c>
-      <c r="R41" t="s">
-        <v>1</v>
-      </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" t="s">
-        <v>12</v>
-      </c>
-      <c r="U41" t="s">
-        <v>22</v>
-      </c>
-      <c r="V41" t="s">
-        <v>1</v>
-      </c>
-      <c r="W41" t="s">
-        <v>1</v>
-      </c>
-      <c r="X41" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25">
-      <c r="A42" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" t="s">
-        <v>128</v>
-      </c>
-      <c r="D42" t="s">
-        <v>129</v>
-      </c>
-      <c r="E42" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F42" s="3">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>1</v>
-      </c>
-      <c r="I42" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" t="s">
-        <v>130</v>
-      </c>
-      <c r="K42" t="s">
-        <v>6</v>
-      </c>
-      <c r="L42" t="s">
-        <v>7</v>
-      </c>
-      <c r="M42" t="s">
-        <v>8</v>
-      </c>
-      <c r="N42" t="s">
-        <v>1</v>
-      </c>
-      <c r="O42" t="s">
-        <v>86</v>
-      </c>
-      <c r="P42" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>21</v>
-      </c>
-      <c r="R42" t="s">
-        <v>1</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" t="s">
-        <v>12</v>
-      </c>
-      <c r="U42" t="s">
-        <v>31</v>
-      </c>
-      <c r="V42" t="s">
-        <v>1</v>
-      </c>
-      <c r="W42" t="s">
-        <v>1</v>
-      </c>
-      <c r="X42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25">
-      <c r="A43" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" t="s">
-        <v>131</v>
-      </c>
-      <c r="D43" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F43" s="3">
-        <v>2</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" t="s">
-        <v>132</v>
-      </c>
-      <c r="K43" t="s">
-        <v>6</v>
-      </c>
-      <c r="L43" t="s">
-        <v>7</v>
-      </c>
-      <c r="M43" t="s">
-        <v>8</v>
-      </c>
-      <c r="N43" t="s">
-        <v>1</v>
-      </c>
-      <c r="O43" t="s">
-        <v>9</v>
-      </c>
-      <c r="P43" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>21</v>
-      </c>
-      <c r="R43" t="s">
-        <v>1</v>
-      </c>
-      <c r="S43" s="3">
-        <v>1</v>
-      </c>
-      <c r="T43" t="s">
-        <v>12</v>
-      </c>
-      <c r="U43" t="s">
-        <v>31</v>
-      </c>
-      <c r="V43" t="s">
-        <v>1</v>
-      </c>
-      <c r="W43" t="s">
-        <v>1</v>
-      </c>
-      <c r="X43" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25">
-      <c r="A44" t="s">
-        <v>124</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
-        <v>133</v>
-      </c>
-      <c r="D44" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>1</v>
-      </c>
-      <c r="I44" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" t="s">
-        <v>134</v>
-      </c>
-      <c r="K44" t="s">
-        <v>6</v>
-      </c>
-      <c r="L44" t="s">
-        <v>7</v>
-      </c>
-      <c r="M44" t="s">
-        <v>8</v>
-      </c>
-      <c r="N44" t="s">
-        <v>1</v>
-      </c>
-      <c r="O44" t="s">
-        <v>9</v>
-      </c>
-      <c r="P44" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>21</v>
-      </c>
-      <c r="R44" t="s">
-        <v>1</v>
-      </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
-      <c r="T44" t="s">
-        <v>12</v>
-      </c>
-      <c r="U44" t="s">
-        <v>31</v>
-      </c>
-      <c r="V44" t="s">
-        <v>1</v>
-      </c>
-      <c r="W44" t="s">
-        <v>1</v>
-      </c>
-      <c r="X44" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25">
-      <c r="A45" t="s">
-        <v>124</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" t="s">
-        <v>135</v>
-      </c>
-      <c r="D45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E45" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1</v>
-      </c>
-      <c r="I45" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" t="s">
-        <v>136</v>
-      </c>
-      <c r="K45" t="s">
-        <v>6</v>
-      </c>
-      <c r="L45" t="s">
-        <v>7</v>
-      </c>
-      <c r="M45" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" t="s">
-        <v>1</v>
-      </c>
-      <c r="O45" t="s">
-        <v>52</v>
-      </c>
-      <c r="P45" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>21</v>
-      </c>
-      <c r="R45" t="s">
-        <v>1</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" t="s">
-        <v>12</v>
-      </c>
-      <c r="U45" t="s">
-        <v>31</v>
-      </c>
-      <c r="V45" t="s">
-        <v>1</v>
-      </c>
-      <c r="W45" t="s">
-        <v>1</v>
-      </c>
-      <c r="X45" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25">
-      <c r="A46" t="s">
-        <v>124</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>121</v>
-      </c>
-      <c r="D46" t="s">
-        <v>58</v>
-      </c>
-      <c r="E46" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F46" s="3">
-        <v>1</v>
-      </c>
-      <c r="G46" s="3">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3">
-        <v>1</v>
-      </c>
-      <c r="I46" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" t="s">
-        <v>123</v>
-      </c>
-      <c r="K46" t="s">
-        <v>6</v>
-      </c>
-      <c r="L46" t="s">
-        <v>7</v>
-      </c>
-      <c r="M46" t="s">
-        <v>8</v>
-      </c>
-      <c r="N46" t="s">
-        <v>1</v>
-      </c>
-      <c r="O46" t="s">
-        <v>86</v>
-      </c>
-      <c r="P46" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>21</v>
-      </c>
-      <c r="R46" t="s">
-        <v>1</v>
-      </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
-      <c r="T46" t="s">
-        <v>12</v>
-      </c>
-      <c r="U46" t="s">
-        <v>1</v>
-      </c>
-      <c r="V46" t="s">
-        <v>1</v>
-      </c>
-      <c r="W46" t="s">
-        <v>1</v>
-      </c>
-      <c r="X46" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25">
-      <c r="A47" t="s">
-        <v>137</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="2">
-        <v>46044</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1</v>
-      </c>
-      <c r="I47" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" t="s">
-        <v>139</v>
-      </c>
-      <c r="K47" t="s">
-        <v>6</v>
-      </c>
-      <c r="L47" t="s">
-        <v>7</v>
-      </c>
-      <c r="M47" t="s">
-        <v>8</v>
-      </c>
-      <c r="N47" t="s">
-        <v>1</v>
-      </c>
-      <c r="O47" t="s">
-        <v>9</v>
-      </c>
-      <c r="P47" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>21</v>
-      </c>
-      <c r="R47" t="s">
-        <v>1</v>
-      </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" t="s">
-        <v>12</v>
-      </c>
-      <c r="U47" t="s">
-        <v>1</v>
-      </c>
-      <c r="V47" t="s">
-        <v>1</v>
-      </c>
-      <c r="W47" t="s">
-        <v>1</v>
-      </c>
-      <c r="X47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y47" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,351 +11,429 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="140">
-  <si>
-    <t>200006299</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="166">
+  <si>
+    <t>200006366</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>080100152306</t>
+    <t>4023000061C0</t>
+  </si>
+  <si>
+    <t>0060</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>油壓缸/打刀油缸_行程14</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>SHEO</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>1F004</t>
+  </si>
+  <si>
+    <t>組件課</t>
+  </si>
+  <si>
+    <t>REL</t>
+  </si>
+  <si>
+    <t>9804</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>8429000727A0</t>
+  </si>
+  <si>
+    <t>0080</t>
+  </si>
+  <si>
+    <t>彈簧座_d22*D32*16</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>200006367</t>
+  </si>
+  <si>
+    <t>8423000097A2</t>
+  </si>
+  <si>
+    <t>0420</t>
+  </si>
+  <si>
+    <t>吹氣環_d127xD138x14H</t>
+  </si>
+  <si>
+    <t>0102</t>
+  </si>
+  <si>
+    <t>3154001543B3</t>
+  </si>
+  <si>
+    <t>0440</t>
+  </si>
+  <si>
+    <t>主軸前蓋_d127*D195*33L</t>
+  </si>
+  <si>
+    <t>200006368</t>
+  </si>
+  <si>
+    <t>080100113204</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021305_BT50,CW45</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>0802</t>
+  </si>
+  <si>
+    <t>200006370</t>
+  </si>
+  <si>
+    <t>080100033903</t>
+  </si>
+  <si>
+    <t>G2.5K主軸,010830_BT50,C0DIN</t>
+  </si>
+  <si>
+    <t>1X001</t>
+  </si>
+  <si>
+    <t>虛擬工作中心</t>
+  </si>
+  <si>
+    <t>200006371</t>
+  </si>
+  <si>
+    <t>3154001366C1</t>
+  </si>
+  <si>
+    <t>0290</t>
+  </si>
+  <si>
+    <t>主軸前蓋_246*430*79</t>
+  </si>
+  <si>
+    <t>200006385</t>
+  </si>
+  <si>
+    <t>8310000702A1</t>
+  </si>
+  <si>
+    <t>0170</t>
+  </si>
+  <si>
+    <t>馬達座_G8K-a22</t>
+  </si>
+  <si>
+    <t>0104</t>
+  </si>
+  <si>
+    <t>200006390</t>
+  </si>
+  <si>
+    <t>4023000108B0</t>
+  </si>
+  <si>
+    <t>0370</t>
+  </si>
+  <si>
+    <t>打刀油缸_83-62-12</t>
+  </si>
+  <si>
+    <t>200006423</t>
+  </si>
+  <si>
+    <t>0360</t>
+  </si>
+  <si>
+    <t>0380</t>
+  </si>
+  <si>
+    <t>200006431</t>
+  </si>
+  <si>
+    <t>200006432</t>
+  </si>
+  <si>
+    <t>080100120402</t>
+  </si>
+  <si>
+    <t>0050</t>
+  </si>
+  <si>
+    <t>G8K 主軸,021387_BT50,0W45</t>
+  </si>
+  <si>
+    <t>200006433</t>
+  </si>
+  <si>
+    <t>200006452</t>
+  </si>
+  <si>
+    <t>080100023404</t>
+  </si>
+  <si>
+    <t>0040</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BT50,C0DIN</t>
+  </si>
+  <si>
+    <t>200006454</t>
+  </si>
+  <si>
+    <t>8814001415C0</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>機頭加工圖,#50G6K_HCMC-1100</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>200006456</t>
+  </si>
+  <si>
+    <t>8814001018A1</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>機頭滑座加工圖_PI-1,Z780</t>
+  </si>
+  <si>
+    <t>200006460</t>
+  </si>
+  <si>
+    <t>200006466</t>
+  </si>
+  <si>
+    <t>8916000299A1</t>
+  </si>
+  <si>
+    <t>0450</t>
+  </si>
+  <si>
+    <t>防濺護罩,左/AHC用_d532*108H</t>
+  </si>
+  <si>
+    <t>0107</t>
+  </si>
+  <si>
+    <t>9816</t>
+  </si>
+  <si>
+    <t>200006471</t>
+  </si>
+  <si>
+    <t>8342000234A0</t>
+  </si>
+  <si>
+    <t>0190</t>
+  </si>
+  <si>
+    <t>吊桿螺帽_M16*25*8</t>
+  </si>
+  <si>
+    <t>3214000289B0</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>吊桿,DDS20K_MVP-8</t>
+  </si>
+  <si>
+    <t>3154001577B0</t>
+  </si>
+  <si>
+    <t>0430</t>
+  </si>
+  <si>
+    <t>主軸前蓋_d82.5*D148*H28</t>
+  </si>
+  <si>
+    <t>200006475</t>
+  </si>
+  <si>
+    <t>080100050201</t>
+  </si>
+  <si>
+    <t>0030</t>
+  </si>
+  <si>
+    <t>D20K 主軸,010683_A63,M50,C0</t>
+  </si>
+  <si>
+    <t>8310000667A1</t>
+  </si>
+  <si>
+    <t>馬達固定座_HSA2215/20KRPM</t>
+  </si>
+  <si>
+    <t>200006476</t>
+  </si>
+  <si>
+    <t>8420002210A0</t>
+  </si>
+  <si>
+    <t>0230</t>
+  </si>
+  <si>
+    <t>下間隔環組,DDS20K_d65*D100*18</t>
+  </si>
+  <si>
+    <t>5063000121B0</t>
+  </si>
+  <si>
+    <t>0310</t>
+  </si>
+  <si>
+    <t>油壓缸活塞,DDS20K_MVP-8(D100*d70*63.5H)</t>
+  </si>
+  <si>
+    <t>200006486</t>
+  </si>
+  <si>
+    <t>200006487</t>
+  </si>
+  <si>
+    <t>200006488</t>
+  </si>
+  <si>
+    <t>3241000017A1</t>
+  </si>
+  <si>
+    <t>直齒離合器,C軸2.5度_D330*d280*H40,144T</t>
+  </si>
+  <si>
+    <t>8319000682A0</t>
+  </si>
+  <si>
+    <t>金屬墊片,A軸軸承箱用_d142*D186*4t</t>
+  </si>
+  <si>
+    <t>892300066700</t>
+  </si>
+  <si>
+    <t>0610</t>
+  </si>
+  <si>
+    <t>出貨固定板_EA/EAY,HF-AU</t>
+  </si>
+  <si>
+    <t>200006495</t>
+  </si>
+  <si>
+    <t>200006496</t>
+  </si>
+  <si>
+    <t>305000001101</t>
+  </si>
+  <si>
+    <t>陶珠軸承_FAG-HC7014C.T.P4S.UL,2個1組</t>
+  </si>
+  <si>
+    <t>EC210689</t>
+  </si>
+  <si>
+    <t>0128</t>
+  </si>
+  <si>
+    <t>305000001201</t>
   </si>
   <si>
     <t>0020</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>DA15K 主軸,021856_BT40,M60,CWDIN</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0010</t>
-  </si>
-  <si>
-    <t>SHEO</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>1F004</t>
-  </si>
-  <si>
-    <t>組件課</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>0802</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>200006330</t>
-  </si>
-  <si>
-    <t>080100036004</t>
-  </si>
-  <si>
-    <t>0040</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,C045</t>
-  </si>
-  <si>
-    <t>200006367</t>
-  </si>
-  <si>
-    <t>303500039801</t>
-  </si>
-  <si>
-    <t>單列斜角滾珠軸承_FAG-HS7018C.T.P4S.UL,2個1組</t>
-  </si>
-  <si>
-    <t>0128</t>
-  </si>
-  <si>
-    <t>9804</t>
-  </si>
-  <si>
-    <t>8420002329A1</t>
-  </si>
-  <si>
-    <t>0290</t>
-  </si>
-  <si>
-    <t>間隔環,前內_d90.5*D113*24,HSA2215</t>
-  </si>
-  <si>
-    <t>0102</t>
-  </si>
-  <si>
-    <t>8420002330A1</t>
-  </si>
-  <si>
-    <t>0300</t>
-  </si>
-  <si>
-    <t>間隔環,前外_d117*D140*24,HSA2215</t>
-  </si>
-  <si>
-    <t>8423000097A2</t>
-  </si>
-  <si>
-    <t>0420</t>
-  </si>
-  <si>
-    <t>吹氣環_d127xD138x14H</t>
-  </si>
-  <si>
-    <t>3154001543B3</t>
-  </si>
-  <si>
-    <t>0440</t>
-  </si>
-  <si>
-    <t>主軸前蓋_d127*D195*33L</t>
-  </si>
-  <si>
-    <t>200006368</t>
-  </si>
-  <si>
-    <t>080100113204</t>
-  </si>
-  <si>
-    <t>0060</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CW45</t>
-  </si>
-  <si>
-    <t>8814001257B3</t>
-  </si>
-  <si>
-    <t>0170</t>
-  </si>
-  <si>
-    <t>機頭加工圖,G6K_HCMC-2110</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>200006370</t>
-  </si>
-  <si>
-    <t>080100033903</t>
-  </si>
-  <si>
-    <t>0080</t>
-  </si>
-  <si>
-    <t>G2.5K主軸,010830_BT50,C0DIN</t>
-  </si>
-  <si>
-    <t>1X001</t>
-  </si>
-  <si>
-    <t>虛擬工作中心</t>
-  </si>
-  <si>
-    <t>8921000777A0</t>
-  </si>
-  <si>
-    <t>0110</t>
-  </si>
-  <si>
-    <t>感應器支撐架_D30104H,D70*10H</t>
-  </si>
-  <si>
-    <t>0101</t>
-  </si>
-  <si>
-    <t>8016001298A0</t>
-  </si>
-  <si>
-    <t>0260</t>
-  </si>
-  <si>
-    <t>板金架_L765xW152xH38</t>
-  </si>
-  <si>
-    <t>0107</t>
-  </si>
-  <si>
-    <t>9801</t>
-  </si>
-  <si>
-    <t>200006371</t>
-  </si>
-  <si>
-    <t>3154001366C1</t>
-  </si>
-  <si>
-    <t>主軸前蓋_246*430*79</t>
-  </si>
-  <si>
-    <t>200006375</t>
-  </si>
-  <si>
-    <t>8420002327A0</t>
-  </si>
-  <si>
-    <t>0330</t>
-  </si>
-  <si>
-    <t>間隔環,前下_d90*D129*13.5,HSA2215</t>
-  </si>
-  <si>
-    <t>0350</t>
-  </si>
-  <si>
-    <t>0360</t>
-  </si>
-  <si>
-    <t>200006377</t>
-  </si>
-  <si>
-    <t>305000001101</t>
-  </si>
-  <si>
-    <t>陶珠軸承_FAG-HC7014C.T.P4S.UL,2個1組</t>
-  </si>
-  <si>
-    <t>EC210689</t>
-  </si>
-  <si>
-    <t>321400027300</t>
-  </si>
-  <si>
-    <t>抓刀筒夾,OTT_BT40</t>
+    <t>陶珠軸承_FAG-HC7013C.T.P4S.UL,2個1組</t>
+  </si>
+  <si>
+    <t>111400007900</t>
+  </si>
+  <si>
+    <t>0180</t>
+  </si>
+  <si>
+    <t>盤型彈簧/左旋_40-20-1</t>
   </si>
   <si>
     <t>0120</t>
   </si>
   <si>
-    <t>0801</t>
-  </si>
-  <si>
-    <t>305000001201</t>
-  </si>
-  <si>
-    <t>陶珠軸承_FAG-HC7013C.T.P4S.UL,2個1組</t>
-  </si>
-  <si>
-    <t>200006385</t>
-  </si>
-  <si>
-    <t>080100022704</t>
-  </si>
-  <si>
-    <t>0050</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BT50,0045</t>
-  </si>
-  <si>
-    <t>8310000702A1</t>
-  </si>
-  <si>
-    <t>馬達座_G8K-a22</t>
-  </si>
-  <si>
-    <t>0104</t>
-  </si>
-  <si>
-    <t>200006404</t>
-  </si>
-  <si>
-    <t>200006423</t>
-  </si>
-  <si>
-    <t>0380</t>
-  </si>
-  <si>
-    <t>200006431</t>
-  </si>
-  <si>
-    <t>200006432</t>
-  </si>
-  <si>
-    <t>080100120402</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021387_BT50,0W45</t>
-  </si>
-  <si>
-    <t>200006433</t>
-  </si>
-  <si>
-    <t>200006454</t>
-  </si>
-  <si>
-    <t>8814001415C0</t>
-  </si>
-  <si>
-    <t>0240</t>
-  </si>
-  <si>
-    <t>機頭加工圖,#50G6K_HCMC-1100</t>
-  </si>
-  <si>
-    <t>200006470</t>
-  </si>
-  <si>
-    <t>3227000055C0</t>
-  </si>
-  <si>
-    <t>0100</t>
-  </si>
-  <si>
-    <t>撓性聯軸器,ROTEX_98ShA-GS6.0-d38,6.0P-d50</t>
-  </si>
-  <si>
-    <t>200006475</t>
-  </si>
-  <si>
-    <t>080100050201</t>
-  </si>
-  <si>
-    <t>0030</t>
-  </si>
-  <si>
-    <t>D20K 主軸,010683_A63,M50,C0</t>
-  </si>
-  <si>
-    <t>8311000415A0</t>
-  </si>
-  <si>
-    <t>前油箱蓋板_195*160*15</t>
-  </si>
-  <si>
-    <t>8310000667A1</t>
-  </si>
-  <si>
-    <t>馬達固定座_HSA2215/20KRPM</t>
-  </si>
-  <si>
-    <t>8814001399A4</t>
-  </si>
-  <si>
-    <t>機頭加工圖,Z780_#40,D20K</t>
-  </si>
-  <si>
-    <t>630000329</t>
-  </si>
-  <si>
-    <t>2050000123A2</t>
-  </si>
-  <si>
-    <t>中間軸齒輪_m2.5*72t*25w</t>
+    <t>200006502</t>
+  </si>
+  <si>
+    <t>305000004501</t>
+  </si>
+  <si>
+    <t>陶珠軸承_FAG-HC7013E.T.P4S.UL,2個1組</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>5063000120A0</t>
+  </si>
+  <si>
+    <t>0220</t>
+  </si>
+  <si>
+    <t>油壓缸外蓋,DDS20K_MVP-8(D100*d70*H64)</t>
+  </si>
+  <si>
+    <t>5063000163B0</t>
+  </si>
+  <si>
+    <t>油壓缸底蓋_MVP-10</t>
+  </si>
+  <si>
+    <t>630000333</t>
+  </si>
+  <si>
+    <t>080200555000</t>
+  </si>
+  <si>
+    <t>0070</t>
+  </si>
+  <si>
+    <t>MVP-8機頭D15K,021581_#40,38F18,C,AT8</t>
+  </si>
+  <si>
+    <t>630000338</t>
+  </si>
+  <si>
+    <t>080100084704</t>
+  </si>
+  <si>
+    <t>D15K 主軸,010017_BT40,M60,CWDIN</t>
   </si>
   <si>
     <t>訂單</t>
@@ -535,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y50"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -547,7 +625,7 @@
     <col min="7" max="7" bestFit="1" width="10" customWidth="1"/>
     <col min="8" max="8" bestFit="1" width="10" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="12" customWidth="1"/>
-    <col min="10" max="10" bestFit="1" width="38" customWidth="1"/>
+    <col min="10" max="10" bestFit="1" width="36" customWidth="1"/>
     <col min="11" max="11" bestFit="1" width="4" customWidth="1"/>
     <col min="12" max="12" bestFit="1" width="6" customWidth="1"/>
     <col min="13" max="13" bestFit="1" width="6" customWidth="1"/>
@@ -567,79 +645,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -656,7 +734,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="2">
-        <v>46059</v>
+        <v>46091</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -721,49 +799,49 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="2">
+        <v>46091</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2">
-        <v>46034</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
         <v>18</v>
-      </c>
-      <c r="K3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N3" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" t="s">
-        <v>9</v>
       </c>
       <c r="P3" t="s">
         <v>10</v>
@@ -775,7 +853,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="s">
         <v>12</v>
@@ -807,25 +885,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2">
         <v>46086</v>
       </c>
       <c r="F4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="s">
         <v>4</v>
       </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" t="s">
         <v>6</v>
@@ -840,7 +918,7 @@
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P4" t="s">
         <v>10</v>
@@ -852,13 +930,13 @@
         <v>1</v>
       </c>
       <c r="S4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="s">
         <v>12</v>
       </c>
       <c r="U4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V4" t="s">
         <v>1</v>
@@ -917,7 +995,7 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P5" t="s">
         <v>10</v>
@@ -935,7 +1013,7 @@
         <v>12</v>
       </c>
       <c r="U5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V5" t="s">
         <v>1</v>
@@ -952,7 +1030,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -961,40 +1039,40 @@
         <v>28</v>
       </c>
       <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46101</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="2">
-        <v>46086</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
         <v>30</v>
-      </c>
-      <c r="K6" t="s">
-        <v>6</v>
-      </c>
-      <c r="L6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" t="s">
-        <v>27</v>
       </c>
       <c r="P6" t="s">
         <v>10</v>
@@ -1012,7 +1090,7 @@
         <v>12</v>
       </c>
       <c r="U6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="V6" t="s">
         <v>1</v>
@@ -1029,67 +1107,67 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46064</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="3">
+        <v>1</v>
+      </c>
+      <c r="T7" t="s">
+        <v>12</v>
+      </c>
+      <c r="U7" t="s">
         <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="2">
-        <v>46086</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>4</v>
-      </c>
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" t="s">
-        <v>7</v>
-      </c>
-      <c r="M7" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="3">
-        <v>1</v>
-      </c>
-      <c r="T7" t="s">
-        <v>12</v>
-      </c>
-      <c r="U7" t="s">
-        <v>23</v>
       </c>
       <c r="V7" t="s">
         <v>1</v>
@@ -1106,19 +1184,19 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2">
-        <v>46086</v>
+        <v>46052</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -1133,7 +1211,7 @@
         <v>4</v>
       </c>
       <c r="J8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s">
         <v>6</v>
@@ -1148,7 +1226,7 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P8" t="s">
         <v>10</v>
@@ -1166,7 +1244,7 @@
         <v>12</v>
       </c>
       <c r="U8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V8" t="s">
         <v>1</v>
@@ -1183,19 +1261,19 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2">
-        <v>46101</v>
+        <v>46063</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -1210,7 +1288,7 @@
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
         <v>6</v>
@@ -1225,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="P9" t="s">
         <v>10</v>
@@ -1260,19 +1338,19 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
@@ -1287,7 +1365,7 @@
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K10" t="s">
         <v>6</v>
@@ -1302,7 +1380,7 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="P10" t="s">
         <v>10</v>
@@ -1320,7 +1398,7 @@
         <v>12</v>
       </c>
       <c r="U10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V10" t="s">
         <v>1</v>
@@ -1337,19 +1415,19 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2">
-        <v>46064</v>
+        <v>46041</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
@@ -1364,7 +1442,7 @@
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="K11" t="s">
         <v>6</v>
@@ -1379,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="P11" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="R11" t="s">
         <v>1</v>
@@ -1414,19 +1492,19 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
       </c>
       <c r="E12" s="2">
-        <v>46064</v>
+        <v>46041</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
@@ -1441,7 +1519,7 @@
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="K12" t="s">
         <v>6</v>
@@ -1456,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="P12" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="R12" t="s">
         <v>1</v>
@@ -1474,7 +1552,7 @@
         <v>12</v>
       </c>
       <c r="U12" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -1491,19 +1569,19 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2">
-        <v>46064</v>
+        <v>46034</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
@@ -1518,7 +1596,7 @@
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="K13" t="s">
         <v>6</v>
@@ -1533,13 +1611,13 @@
         <v>1</v>
       </c>
       <c r="O13" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="P13" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="R13" t="s">
         <v>1</v>
@@ -1551,7 +1629,7 @@
         <v>12</v>
       </c>
       <c r="U13" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="V13" t="s">
         <v>1</v>
@@ -1568,19 +1646,19 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2">
-        <v>46052</v>
+        <v>46078</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
@@ -1595,7 +1673,7 @@
         <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K14" t="s">
         <v>6</v>
@@ -1610,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="O14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P14" t="s">
         <v>10</v>
@@ -1628,7 +1706,7 @@
         <v>12</v>
       </c>
       <c r="U14" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="V14" t="s">
         <v>1</v>
@@ -1645,19 +1723,19 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2">
-        <v>46100</v>
+        <v>46063</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
@@ -1672,7 +1750,7 @@
         <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="K15" t="s">
         <v>6</v>
@@ -1687,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P15" t="s">
         <v>10</v>
@@ -1705,7 +1783,7 @@
         <v>12</v>
       </c>
       <c r="U15" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V15" t="s">
         <v>1</v>
@@ -1722,7 +1800,7 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
@@ -1731,10 +1809,10 @@
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="E16" s="2">
-        <v>46100</v>
+        <v>46063</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
@@ -1764,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P16" t="s">
         <v>10</v>
@@ -1782,7 +1860,7 @@
         <v>12</v>
       </c>
       <c r="U16" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V16" t="s">
         <v>1</v>
@@ -1799,19 +1877,19 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2">
-        <v>46100</v>
+        <v>46079</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -1826,22 +1904,22 @@
         <v>4</v>
       </c>
       <c r="J17" t="s">
+        <v>62</v>
+      </c>
+      <c r="K17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L17" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" t="s">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
         <v>30</v>
-      </c>
-      <c r="K17" t="s">
-        <v>6</v>
-      </c>
-      <c r="L17" t="s">
-        <v>7</v>
-      </c>
-      <c r="M17" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" t="s">
-        <v>1</v>
-      </c>
-      <c r="O17" t="s">
-        <v>27</v>
       </c>
       <c r="P17" t="s">
         <v>10</v>
@@ -1859,7 +1937,7 @@
         <v>12</v>
       </c>
       <c r="U17" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="V17" t="s">
         <v>1</v>
@@ -1876,19 +1954,19 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2">
-        <v>46048</v>
+        <v>46065</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -1903,7 +1981,7 @@
         <v>4</v>
       </c>
       <c r="J18" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="K18" t="s">
         <v>6</v>
@@ -1915,10 +1993,10 @@
         <v>8</v>
       </c>
       <c r="N18" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="P18" t="s">
         <v>10</v>
@@ -1936,7 +2014,7 @@
         <v>12</v>
       </c>
       <c r="U18" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V18" t="s">
         <v>1</v>
@@ -1953,19 +2031,19 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="E19" s="2">
-        <v>46048</v>
+        <v>46077</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
@@ -1980,7 +2058,7 @@
         <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="K19" t="s">
         <v>6</v>
@@ -1995,7 +2073,7 @@
         <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="P19" t="s">
         <v>10</v>
@@ -2007,13 +2085,13 @@
         <v>1</v>
       </c>
       <c r="S19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="s">
         <v>12</v>
       </c>
       <c r="U19" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="V19" t="s">
         <v>1</v>
@@ -2030,19 +2108,19 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
         <v>69</v>
       </c>
-      <c r="B20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
-      </c>
       <c r="D20" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2">
-        <v>46048</v>
+        <v>46077</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
@@ -2057,7 +2135,7 @@
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K20" t="s">
         <v>6</v>
@@ -2069,10 +2147,10 @@
         <v>8</v>
       </c>
       <c r="N20" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="O20" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="P20" t="s">
         <v>10</v>
@@ -2084,13 +2162,13 @@
         <v>1</v>
       </c>
       <c r="S20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="s">
         <v>12</v>
       </c>
       <c r="U20" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="V20" t="s">
         <v>1</v>
@@ -2107,19 +2185,19 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2">
-        <v>46063</v>
+        <v>46085</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -2134,7 +2212,7 @@
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="K21" t="s">
         <v>6</v>
@@ -2184,19 +2262,19 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="E22" s="2">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
@@ -2211,7 +2289,7 @@
         <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="K22" t="s">
         <v>6</v>
@@ -2226,13 +2304,13 @@
         <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="P22" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q22" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R22" t="s">
         <v>1</v>
@@ -2244,7 +2322,7 @@
         <v>12</v>
       </c>
       <c r="U22" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="V22" t="s">
         <v>1</v>
@@ -2261,34 +2339,34 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="E23" s="2">
-        <v>46038</v>
+        <v>46059</v>
       </c>
       <c r="F23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="3">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="s">
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s">
         <v>6</v>
@@ -2303,7 +2381,7 @@
         <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="P23" t="s">
         <v>10</v>
@@ -2315,13 +2393,13 @@
         <v>1</v>
       </c>
       <c r="S23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T23" t="s">
         <v>12</v>
       </c>
       <c r="U23" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="V23" t="s">
         <v>1</v>
@@ -2338,19 +2416,19 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2">
-        <v>46041</v>
+        <v>46059</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -2365,7 +2443,7 @@
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="K24" t="s">
         <v>6</v>
@@ -2380,7 +2458,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P24" t="s">
         <v>10</v>
@@ -2398,7 +2476,7 @@
         <v>12</v>
       </c>
       <c r="U24" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V24" t="s">
         <v>1</v>
@@ -2415,35 +2493,35 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" t="s">
         <v>87</v>
       </c>
-      <c r="B25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" s="2">
+        <v>46059</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="2">
-        <v>46041</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1</v>
-      </c>
-      <c r="I25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J25" t="s">
-        <v>36</v>
-      </c>
       <c r="K25" t="s">
         <v>6</v>
       </c>
@@ -2457,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P25" t="s">
         <v>10</v>
@@ -2475,7 +2553,7 @@
         <v>12</v>
       </c>
       <c r="U25" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V25" t="s">
         <v>1</v>
@@ -2498,13 +2576,13 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E26" s="2">
-        <v>46034</v>
+        <v>46050</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
@@ -2519,7 +2597,7 @@
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s">
         <v>6</v>
@@ -2534,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P26" t="s">
         <v>10</v>
@@ -2546,13 +2624,13 @@
         <v>1</v>
       </c>
       <c r="S26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="s">
         <v>12</v>
       </c>
       <c r="U26" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="V26" t="s">
         <v>1</v>
@@ -2569,19 +2647,19 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="E27" s="2">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="F27" s="3">
         <v>1</v>
@@ -2596,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s">
         <v>6</v>
@@ -2623,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="s">
         <v>12</v>
@@ -2646,34 +2724,34 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="F28" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="3">
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="s">
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s">
         <v>6</v>
@@ -2688,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="P28" t="s">
         <v>10</v>
@@ -2700,13 +2778,13 @@
         <v>1</v>
       </c>
       <c r="S28" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" t="s">
         <v>12</v>
       </c>
       <c r="U28" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V28" t="s">
         <v>1</v>
@@ -2723,19 +2801,19 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="E29" s="2">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
@@ -2750,7 +2828,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="K29" t="s">
         <v>6</v>
@@ -2765,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P29" t="s">
         <v>10</v>
@@ -2783,7 +2861,7 @@
         <v>12</v>
       </c>
       <c r="U29" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V29" t="s">
         <v>1</v>
@@ -2800,19 +2878,19 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2">
-        <v>46063</v>
+        <v>46050</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
@@ -2827,7 +2905,7 @@
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="K30" t="s">
         <v>6</v>
@@ -2842,7 +2920,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P30" t="s">
         <v>10</v>
@@ -2860,7 +2938,7 @@
         <v>12</v>
       </c>
       <c r="U30" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V30" t="s">
         <v>1</v>
@@ -2877,19 +2955,19 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E31" s="2">
-        <v>46065</v>
+        <v>46050</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -2904,7 +2982,7 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K31" t="s">
         <v>6</v>
@@ -2919,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="P31" t="s">
         <v>10</v>
@@ -2937,7 +3015,7 @@
         <v>12</v>
       </c>
       <c r="U31" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V31" t="s">
         <v>1</v>
@@ -2954,19 +3032,19 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2">
-        <v>46066</v>
+        <v>46092</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -2981,7 +3059,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="K32" t="s">
         <v>6</v>
@@ -2996,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="P32" t="s">
         <v>10</v>
@@ -3014,7 +3092,7 @@
         <v>12</v>
       </c>
       <c r="U32" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V32" t="s">
         <v>1</v>
@@ -3031,19 +3109,19 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="E33" s="2">
-        <v>46050</v>
+        <v>46092</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
@@ -3058,7 +3136,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="K33" t="s">
         <v>6</v>
@@ -3073,7 +3151,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="P33" t="s">
         <v>10</v>
@@ -3085,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="s">
         <v>12</v>
@@ -3108,35 +3186,35 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
       <c r="C34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>46094</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>4</v>
+      </c>
+      <c r="J34" t="s">
         <v>106</v>
       </c>
-      <c r="D34" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F34" s="3">
-        <v>2</v>
-      </c>
-      <c r="G34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3">
-        <v>1</v>
-      </c>
-      <c r="I34" t="s">
-        <v>4</v>
-      </c>
-      <c r="J34" t="s">
-        <v>107</v>
-      </c>
       <c r="K34" t="s">
         <v>6</v>
       </c>
@@ -3150,13 +3228,13 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="P34" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q34" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R34" t="s">
         <v>1</v>
@@ -3168,7 +3246,7 @@
         <v>12</v>
       </c>
       <c r="U34" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="V34" t="s">
         <v>1</v>
@@ -3185,35 +3263,35 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="2">
+        <v>46094</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" t="s">
         <v>108</v>
       </c>
-      <c r="D35" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" t="s">
-        <v>109</v>
-      </c>
       <c r="K35" t="s">
         <v>6</v>
       </c>
@@ -3227,25 +3305,25 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="P35" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q35" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R35" t="s">
         <v>1</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="s">
         <v>12</v>
       </c>
       <c r="U35" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="V35" t="s">
         <v>1</v>
@@ -3262,19 +3340,19 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="E36" s="2">
-        <v>46050</v>
+        <v>46094</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -3289,7 +3367,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="K36" t="s">
         <v>6</v>
@@ -3304,25 +3382,25 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P36" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q36" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R36" t="s">
         <v>1</v>
       </c>
       <c r="S36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="s">
         <v>12</v>
       </c>
       <c r="U36" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="V36" t="s">
         <v>1</v>
@@ -3339,19 +3417,19 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" t="s">
         <v>110</v>
       </c>
-      <c r="D37" t="s">
-        <v>75</v>
-      </c>
       <c r="E37" s="2">
-        <v>46050</v>
+        <v>46094</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -3381,25 +3459,25 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="P37" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q37" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R37" t="s">
         <v>1</v>
       </c>
       <c r="S37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="s">
         <v>12</v>
       </c>
       <c r="U37" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="V37" t="s">
         <v>1</v>
@@ -3422,13 +3500,13 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="E38" s="2">
-        <v>46044</v>
+        <v>46092</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
@@ -3443,7 +3521,7 @@
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="K38" t="s">
         <v>6</v>
@@ -3458,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="P38" t="s">
         <v>10</v>
@@ -3470,13 +3548,13 @@
         <v>1</v>
       </c>
       <c r="S38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="s">
         <v>12</v>
       </c>
       <c r="U38" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="V38" t="s">
         <v>1</v>
@@ -3488,6 +3566,930 @@
         <v>1</v>
       </c>
       <c r="Y38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
+      <c r="A39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="2">
+        <v>46093</v>
+      </c>
+      <c r="F39" s="3">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>4</v>
+      </c>
+      <c r="J39" t="s">
+        <v>115</v>
+      </c>
+      <c r="K39" t="s">
+        <v>6</v>
+      </c>
+      <c r="L39" t="s">
+        <v>7</v>
+      </c>
+      <c r="M39" t="s">
+        <v>8</v>
+      </c>
+      <c r="N39" t="s">
+        <v>116</v>
+      </c>
+      <c r="O39" t="s">
+        <v>117</v>
+      </c>
+      <c r="P39" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>11</v>
+      </c>
+      <c r="R39" t="s">
+        <v>1</v>
+      </c>
+      <c r="S39" s="3">
+        <v>1</v>
+      </c>
+      <c r="T39" t="s">
+        <v>12</v>
+      </c>
+      <c r="U39" t="s">
+        <v>13</v>
+      </c>
+      <c r="V39" t="s">
+        <v>1</v>
+      </c>
+      <c r="W39" t="s">
+        <v>1</v>
+      </c>
+      <c r="X39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
+      <c r="A40" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" s="2">
+        <v>46093</v>
+      </c>
+      <c r="F40" s="3">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>4</v>
+      </c>
+      <c r="J40" t="s">
+        <v>120</v>
+      </c>
+      <c r="K40" t="s">
+        <v>6</v>
+      </c>
+      <c r="L40" t="s">
+        <v>7</v>
+      </c>
+      <c r="M40" t="s">
+        <v>8</v>
+      </c>
+      <c r="N40" t="s">
+        <v>116</v>
+      </c>
+      <c r="O40" t="s">
+        <v>117</v>
+      </c>
+      <c r="P40" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>11</v>
+      </c>
+      <c r="R40" t="s">
+        <v>1</v>
+      </c>
+      <c r="S40" s="3">
+        <v>1</v>
+      </c>
+      <c r="T40" t="s">
+        <v>12</v>
+      </c>
+      <c r="U40" t="s">
+        <v>13</v>
+      </c>
+      <c r="V40" t="s">
+        <v>1</v>
+      </c>
+      <c r="W40" t="s">
+        <v>1</v>
+      </c>
+      <c r="X40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
+      <c r="A41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" s="2">
+        <v>46093</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" t="s">
+        <v>123</v>
+      </c>
+      <c r="K41" t="s">
+        <v>6</v>
+      </c>
+      <c r="L41" t="s">
+        <v>7</v>
+      </c>
+      <c r="M41" t="s">
+        <v>8</v>
+      </c>
+      <c r="N41" t="s">
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
+        <v>124</v>
+      </c>
+      <c r="P41" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>11</v>
+      </c>
+      <c r="R41" t="s">
+        <v>1</v>
+      </c>
+      <c r="S41" s="3">
+        <v>1</v>
+      </c>
+      <c r="T41" t="s">
+        <v>12</v>
+      </c>
+      <c r="U41" t="s">
+        <v>13</v>
+      </c>
+      <c r="V41" t="s">
+        <v>1</v>
+      </c>
+      <c r="W41" t="s">
+        <v>1</v>
+      </c>
+      <c r="X41" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
+      <c r="A42" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="2">
+        <v>46093</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>4</v>
+      </c>
+      <c r="J42" t="s">
+        <v>49</v>
+      </c>
+      <c r="K42" t="s">
+        <v>6</v>
+      </c>
+      <c r="L42" t="s">
+        <v>7</v>
+      </c>
+      <c r="M42" t="s">
+        <v>8</v>
+      </c>
+      <c r="N42" t="s">
+        <v>1</v>
+      </c>
+      <c r="O42" t="s">
+        <v>23</v>
+      </c>
+      <c r="P42" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>11</v>
+      </c>
+      <c r="R42" t="s">
+        <v>1</v>
+      </c>
+      <c r="S42" s="3">
+        <v>1</v>
+      </c>
+      <c r="T42" t="s">
+        <v>12</v>
+      </c>
+      <c r="U42" t="s">
+        <v>13</v>
+      </c>
+      <c r="V42" t="s">
+        <v>1</v>
+      </c>
+      <c r="W42" t="s">
+        <v>1</v>
+      </c>
+      <c r="X42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
+      <c r="A43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>126</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="2">
+        <v>46086</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>2</v>
+      </c>
+      <c r="I43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" t="s">
+        <v>127</v>
+      </c>
+      <c r="K43" t="s">
+        <v>6</v>
+      </c>
+      <c r="L43" t="s">
+        <v>7</v>
+      </c>
+      <c r="M43" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" t="s">
+        <v>1</v>
+      </c>
+      <c r="O43" t="s">
+        <v>117</v>
+      </c>
+      <c r="P43" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>11</v>
+      </c>
+      <c r="R43" t="s">
+        <v>1</v>
+      </c>
+      <c r="S43" s="3">
+        <v>2</v>
+      </c>
+      <c r="T43" t="s">
+        <v>12</v>
+      </c>
+      <c r="U43" t="s">
+        <v>13</v>
+      </c>
+      <c r="V43" t="s">
+        <v>1</v>
+      </c>
+      <c r="W43" t="s">
+        <v>1</v>
+      </c>
+      <c r="X43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
+      <c r="A44" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" s="2">
+        <v>46086</v>
+      </c>
+      <c r="F44" s="3">
+        <v>2</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>2</v>
+      </c>
+      <c r="I44" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" t="s">
+        <v>82</v>
+      </c>
+      <c r="K44" t="s">
+        <v>6</v>
+      </c>
+      <c r="L44" t="s">
+        <v>7</v>
+      </c>
+      <c r="M44" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" t="s">
+        <v>1</v>
+      </c>
+      <c r="O44" t="s">
+        <v>23</v>
+      </c>
+      <c r="P44" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>11</v>
+      </c>
+      <c r="R44" t="s">
+        <v>1</v>
+      </c>
+      <c r="S44" s="3">
+        <v>2</v>
+      </c>
+      <c r="T44" t="s">
+        <v>12</v>
+      </c>
+      <c r="U44" t="s">
+        <v>13</v>
+      </c>
+      <c r="V44" t="s">
+        <v>1</v>
+      </c>
+      <c r="W44" t="s">
+        <v>1</v>
+      </c>
+      <c r="X44" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
+      <c r="A45" t="s">
+        <v>125</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="2">
+        <v>46086</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" t="s">
+        <v>85</v>
+      </c>
+      <c r="K45" t="s">
+        <v>6</v>
+      </c>
+      <c r="L45" t="s">
+        <v>7</v>
+      </c>
+      <c r="M45" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" t="s">
+        <v>1</v>
+      </c>
+      <c r="O45" t="s">
+        <v>23</v>
+      </c>
+      <c r="P45" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>11</v>
+      </c>
+      <c r="R45" t="s">
+        <v>1</v>
+      </c>
+      <c r="S45" s="3">
+        <v>1</v>
+      </c>
+      <c r="T45" t="s">
+        <v>12</v>
+      </c>
+      <c r="U45" t="s">
+        <v>13</v>
+      </c>
+      <c r="V45" t="s">
+        <v>1</v>
+      </c>
+      <c r="W45" t="s">
+        <v>1</v>
+      </c>
+      <c r="X45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25">
+      <c r="A46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="2">
+        <v>46086</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" t="s">
+        <v>131</v>
+      </c>
+      <c r="K46" t="s">
+        <v>6</v>
+      </c>
+      <c r="L46" t="s">
+        <v>7</v>
+      </c>
+      <c r="M46" t="s">
+        <v>8</v>
+      </c>
+      <c r="N46" t="s">
+        <v>1</v>
+      </c>
+      <c r="O46" t="s">
+        <v>23</v>
+      </c>
+      <c r="P46" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>11</v>
+      </c>
+      <c r="R46" t="s">
+        <v>1</v>
+      </c>
+      <c r="S46" s="3">
+        <v>1</v>
+      </c>
+      <c r="T46" t="s">
+        <v>12</v>
+      </c>
+      <c r="U46" t="s">
+        <v>13</v>
+      </c>
+      <c r="V46" t="s">
+        <v>1</v>
+      </c>
+      <c r="W46" t="s">
+        <v>1</v>
+      </c>
+      <c r="X46" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25">
+      <c r="A47" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" t="s">
+        <v>97</v>
+      </c>
+      <c r="E47" s="2">
+        <v>46086</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" t="s">
+        <v>101</v>
+      </c>
+      <c r="K47" t="s">
+        <v>6</v>
+      </c>
+      <c r="L47" t="s">
+        <v>7</v>
+      </c>
+      <c r="M47" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" t="s">
+        <v>1</v>
+      </c>
+      <c r="O47" t="s">
+        <v>23</v>
+      </c>
+      <c r="P47" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>11</v>
+      </c>
+      <c r="R47" t="s">
+        <v>1</v>
+      </c>
+      <c r="S47" s="3">
+        <v>1</v>
+      </c>
+      <c r="T47" t="s">
+        <v>12</v>
+      </c>
+      <c r="U47" t="s">
+        <v>13</v>
+      </c>
+      <c r="V47" t="s">
+        <v>1</v>
+      </c>
+      <c r="W47" t="s">
+        <v>1</v>
+      </c>
+      <c r="X47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25">
+      <c r="A48" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>132</v>
+      </c>
+      <c r="D48" t="s">
+        <v>52</v>
+      </c>
+      <c r="E48" s="2">
+        <v>46086</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" t="s">
+        <v>133</v>
+      </c>
+      <c r="K48" t="s">
+        <v>6</v>
+      </c>
+      <c r="L48" t="s">
+        <v>7</v>
+      </c>
+      <c r="M48" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" t="s">
+        <v>1</v>
+      </c>
+      <c r="O48" t="s">
+        <v>23</v>
+      </c>
+      <c r="P48" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>11</v>
+      </c>
+      <c r="R48" t="s">
+        <v>1</v>
+      </c>
+      <c r="S48" s="3">
+        <v>1</v>
+      </c>
+      <c r="T48" t="s">
+        <v>12</v>
+      </c>
+      <c r="U48" t="s">
+        <v>13</v>
+      </c>
+      <c r="V48" t="s">
+        <v>1</v>
+      </c>
+      <c r="W48" t="s">
+        <v>1</v>
+      </c>
+      <c r="X48" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25">
+      <c r="A49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="2">
+        <v>46059</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" t="s">
+        <v>137</v>
+      </c>
+      <c r="K49" t="s">
+        <v>6</v>
+      </c>
+      <c r="L49" t="s">
+        <v>7</v>
+      </c>
+      <c r="M49" t="s">
+        <v>8</v>
+      </c>
+      <c r="N49" t="s">
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
+        <v>30</v>
+      </c>
+      <c r="P49" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>11</v>
+      </c>
+      <c r="R49" t="s">
+        <v>1</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" t="s">
+        <v>12</v>
+      </c>
+      <c r="U49" t="s">
+        <v>1</v>
+      </c>
+      <c r="V49" t="s">
+        <v>1</v>
+      </c>
+      <c r="W49" t="s">
+        <v>1</v>
+      </c>
+      <c r="X49" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25">
+      <c r="A50" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50" s="2">
+        <v>46064</v>
+      </c>
+      <c r="F50" s="3">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>4</v>
+      </c>
+      <c r="J50" t="s">
+        <v>140</v>
+      </c>
+      <c r="K50" t="s">
+        <v>6</v>
+      </c>
+      <c r="L50" t="s">
+        <v>7</v>
+      </c>
+      <c r="M50" t="s">
+        <v>8</v>
+      </c>
+      <c r="N50" t="s">
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
+        <v>30</v>
+      </c>
+      <c r="P50" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>11</v>
+      </c>
+      <c r="R50" t="s">
+        <v>1</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" t="s">
+        <v>12</v>
+      </c>
+      <c r="U50" t="s">
+        <v>1</v>
+      </c>
+      <c r="V50" t="s">
+        <v>1</v>
+      </c>
+      <c r="W50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y50" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="193">
   <si>
     <t>200006366</t>
   </si>
@@ -232,187 +232,268 @@
     <t>200006460</t>
   </si>
   <si>
-    <t>200006466</t>
-  </si>
-  <si>
-    <t>8916000299A1</t>
-  </si>
-  <si>
-    <t>0450</t>
-  </si>
-  <si>
-    <t>防濺護罩,左/AHC用_d532*108H</t>
+    <t>200006471</t>
+  </si>
+  <si>
+    <t>8342000234A0</t>
+  </si>
+  <si>
+    <t>0190</t>
+  </si>
+  <si>
+    <t>吊桿螺帽_M16*25*8</t>
+  </si>
+  <si>
+    <t>3214000289B0</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>吊桿,DDS20K_MVP-8</t>
+  </si>
+  <si>
+    <t>3154001577B0</t>
+  </si>
+  <si>
+    <t>0430</t>
+  </si>
+  <si>
+    <t>主軸前蓋_d82.5*D148*H28</t>
+  </si>
+  <si>
+    <t>200006475</t>
+  </si>
+  <si>
+    <t>080100050201</t>
+  </si>
+  <si>
+    <t>0030</t>
+  </si>
+  <si>
+    <t>D20K 主軸,010683_A63,M50,C0</t>
+  </si>
+  <si>
+    <t>8310000667A1</t>
+  </si>
+  <si>
+    <t>馬達固定座_HSA2215/20KRPM</t>
+  </si>
+  <si>
+    <t>200006476</t>
+  </si>
+  <si>
+    <t>200006486</t>
+  </si>
+  <si>
+    <t>200006487</t>
+  </si>
+  <si>
+    <t>200006488</t>
+  </si>
+  <si>
+    <t>3241000017A1</t>
+  </si>
+  <si>
+    <t>直齒離合器,C軸2.5度_D330*d280*H40,144T</t>
+  </si>
+  <si>
+    <t>9816</t>
+  </si>
+  <si>
+    <t>8319000682A0</t>
+  </si>
+  <si>
+    <t>金屬墊片,A軸軸承箱用_d142*D186*4t</t>
+  </si>
+  <si>
+    <t>892300066700</t>
+  </si>
+  <si>
+    <t>0610</t>
+  </si>
+  <si>
+    <t>出貨固定板_EA/EAY,HF-AU</t>
   </si>
   <si>
     <t>0107</t>
   </si>
   <si>
-    <t>9816</t>
-  </si>
-  <si>
-    <t>200006471</t>
-  </si>
-  <si>
-    <t>8342000234A0</t>
-  </si>
-  <si>
-    <t>0190</t>
-  </si>
-  <si>
-    <t>吊桿螺帽_M16*25*8</t>
-  </si>
-  <si>
-    <t>3214000289B0</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>吊桿,DDS20K_MVP-8</t>
-  </si>
-  <si>
-    <t>3154001577B0</t>
-  </si>
-  <si>
-    <t>0430</t>
-  </si>
-  <si>
-    <t>主軸前蓋_d82.5*D148*H28</t>
-  </si>
-  <si>
-    <t>200006475</t>
-  </si>
-  <si>
-    <t>080100050201</t>
-  </si>
-  <si>
-    <t>0030</t>
-  </si>
-  <si>
-    <t>D20K 主軸,010683_A63,M50,C0</t>
-  </si>
-  <si>
-    <t>8310000667A1</t>
-  </si>
-  <si>
-    <t>馬達固定座_HSA2215/20KRPM</t>
-  </si>
-  <si>
-    <t>200006476</t>
-  </si>
-  <si>
-    <t>8420002210A0</t>
+    <t>200006495</t>
+  </si>
+  <si>
+    <t>200006496</t>
+  </si>
+  <si>
+    <t>111400007900</t>
+  </si>
+  <si>
+    <t>0180</t>
+  </si>
+  <si>
+    <t>盤型彈簧/左旋_40-20-1</t>
+  </si>
+  <si>
+    <t>0120</t>
+  </si>
+  <si>
+    <t>200006501</t>
+  </si>
+  <si>
+    <t>881400142300</t>
+  </si>
+  <si>
+    <t>機頭加工圖,HSKA63D長套筒_MVP-13</t>
+  </si>
+  <si>
+    <t>3227000055C0</t>
+  </si>
+  <si>
+    <t>0090</t>
+  </si>
+  <si>
+    <t>撓性聯軸器,ROTEX_98ShA-GS6.0-d38,6.0P-d50</t>
+  </si>
+  <si>
+    <t>200006502</t>
+  </si>
+  <si>
+    <t>305000004501</t>
+  </si>
+  <si>
+    <t>陶珠軸承_FAG-HC7013E.T.P4S.UL,2個1組</t>
+  </si>
+  <si>
+    <t>0128</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>5063000120A0</t>
+  </si>
+  <si>
+    <t>0220</t>
+  </si>
+  <si>
+    <t>油壓缸外蓋,DDS20K_MVP-8(D100*d70*H64)</t>
+  </si>
+  <si>
+    <t>5063000163B0</t>
+  </si>
+  <si>
+    <t>油壓缸底蓋_MVP-10</t>
+  </si>
+  <si>
+    <t>200006526</t>
+  </si>
+  <si>
+    <t>305000005200</t>
+  </si>
+  <si>
+    <t>陶珠軸承_GMN-HYKH6012 2RZCTAP4UL</t>
+  </si>
+  <si>
+    <t>305000005300</t>
+  </si>
+  <si>
+    <t>0020</t>
+  </si>
+  <si>
+    <t>陶珠軸承_GMN-HYKH6013 2RZCTAP4UL</t>
+  </si>
+  <si>
+    <t>8420002211A0</t>
   </si>
   <si>
     <t>0230</t>
   </si>
   <si>
-    <t>下間隔環組,DDS20K_d65*D100*18</t>
-  </si>
-  <si>
-    <t>5063000121B0</t>
-  </si>
-  <si>
-    <t>0310</t>
-  </si>
-  <si>
-    <t>油壓缸活塞,DDS20K_MVP-8(D100*d70*63.5H)</t>
-  </si>
-  <si>
-    <t>200006486</t>
-  </si>
-  <si>
-    <t>200006487</t>
-  </si>
-  <si>
-    <t>200006488</t>
-  </si>
-  <si>
-    <t>3241000017A1</t>
-  </si>
-  <si>
-    <t>直齒離合器,C軸2.5度_D330*d280*H40,144T</t>
-  </si>
-  <si>
-    <t>8319000682A0</t>
-  </si>
-  <si>
-    <t>金屬墊片,A軸軸承箱用_d142*D186*4t</t>
-  </si>
-  <si>
-    <t>892300066700</t>
-  </si>
-  <si>
-    <t>0610</t>
-  </si>
-  <si>
-    <t>出貨固定板_EA/EAY,HF-AU</t>
-  </si>
-  <si>
-    <t>200006495</t>
-  </si>
-  <si>
-    <t>200006496</t>
-  </si>
-  <si>
-    <t>305000001101</t>
-  </si>
-  <si>
-    <t>陶珠軸承_FAG-HC7014C.T.P4S.UL,2個1組</t>
-  </si>
-  <si>
-    <t>EC210689</t>
-  </si>
-  <si>
-    <t>0128</t>
-  </si>
-  <si>
-    <t>305000001201</t>
-  </si>
-  <si>
-    <t>0020</t>
-  </si>
-  <si>
-    <t>陶珠軸承_FAG-HC7013C.T.P4S.UL,2個1組</t>
-  </si>
-  <si>
-    <t>111400007900</t>
-  </si>
-  <si>
-    <t>0180</t>
-  </si>
-  <si>
-    <t>盤型彈簧/左旋_40-20-1</t>
-  </si>
-  <si>
-    <t>0120</t>
-  </si>
-  <si>
-    <t>200006502</t>
-  </si>
-  <si>
-    <t>305000004501</t>
-  </si>
-  <si>
-    <t>陶珠軸承_FAG-HC7013E.T.P4S.UL,2個1組</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>5063000120A0</t>
-  </si>
-  <si>
-    <t>0220</t>
-  </si>
-  <si>
-    <t>油壓缸外蓋,DDS20K_MVP-8(D100*d70*H64)</t>
-  </si>
-  <si>
-    <t>5063000163B0</t>
-  </si>
-  <si>
-    <t>油壓缸底蓋_MVP-10</t>
+    <t>上間隔環組,DDS20K_d60*D95*14</t>
+  </si>
+  <si>
+    <t>5063000119A0</t>
+  </si>
+  <si>
+    <t>0260</t>
+  </si>
+  <si>
+    <t>油壓缸底蓋,DDS20K_MVP-8(d70)</t>
+  </si>
+  <si>
+    <t>8921000806A1</t>
+  </si>
+  <si>
+    <t>0410</t>
+  </si>
+  <si>
+    <t>感應器支撐架_MVP-8</t>
+  </si>
+  <si>
+    <t>200006527</t>
+  </si>
+  <si>
+    <t>111400008100</t>
+  </si>
+  <si>
+    <t>0150</t>
+  </si>
+  <si>
+    <t>盤型彈簧_φ34*φ16.6*2t</t>
+  </si>
+  <si>
+    <t>8420002213A2</t>
+  </si>
+  <si>
+    <t>0320</t>
+  </si>
+  <si>
+    <t>間隔環,DDS20K_d60*D75*143</t>
+  </si>
+  <si>
+    <t>8420002463A1</t>
+  </si>
+  <si>
+    <t>套環_d64*D97*7.5,MVP</t>
+  </si>
+  <si>
+    <t>200006528</t>
+  </si>
+  <si>
+    <t>312800005100</t>
+  </si>
+  <si>
+    <t>油封_RS1300700-T46NA B+S K型特康</t>
+  </si>
+  <si>
+    <t>312800005600</t>
+  </si>
+  <si>
+    <t>油封_PQ1401000-T46 B+S AQ-type</t>
+  </si>
+  <si>
+    <t>200006530</t>
+  </si>
+  <si>
+    <t>303500039801</t>
+  </si>
+  <si>
+    <t>單列斜角滾珠軸承_FAG-HS7018C.T.P4S.UL,2個1組</t>
+  </si>
+  <si>
+    <t>8010000388A0</t>
+  </si>
+  <si>
+    <t>感應塊_70-965</t>
+  </si>
+  <si>
+    <t>3059000331A1</t>
+  </si>
+  <si>
+    <t>0390</t>
+  </si>
+  <si>
+    <t>主軸承箱_HCMC-1682,#50,G8K</t>
   </si>
   <si>
     <t>630000333</t>
@@ -613,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y82"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -625,16 +706,16 @@
     <col min="7" max="7" bestFit="1" width="10" customWidth="1"/>
     <col min="8" max="8" bestFit="1" width="10" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="12" customWidth="1"/>
-    <col min="10" max="10" bestFit="1" width="36" customWidth="1"/>
+    <col min="10" max="10" bestFit="1" width="38" customWidth="1"/>
     <col min="11" max="11" bestFit="1" width="4" customWidth="1"/>
     <col min="12" max="12" bestFit="1" width="6" customWidth="1"/>
     <col min="13" max="13" bestFit="1" width="6" customWidth="1"/>
-    <col min="14" max="14" bestFit="1" width="10" customWidth="1"/>
+    <col min="14" max="14" bestFit="1" width="6" customWidth="1"/>
     <col min="15" max="15" bestFit="1" width="6" customWidth="1"/>
     <col min="16" max="16" bestFit="1" width="7" customWidth="1"/>
     <col min="17" max="17" bestFit="1" width="8" customWidth="1"/>
     <col min="18" max="18" bestFit="1" width="6" customWidth="1"/>
-    <col min="19" max="19" bestFit="1" width="10" customWidth="1"/>
+    <col min="19" max="19" bestFit="1" width="11" customWidth="1"/>
     <col min="20" max="20" bestFit="1" width="6" customWidth="1"/>
     <col min="21" max="21" bestFit="1" width="6" customWidth="1"/>
     <col min="22" max="22" bestFit="1" width="6" customWidth="1"/>
@@ -645,79 +726,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -2274,16 +2355,16 @@
         <v>75</v>
       </c>
       <c r="E22" s="2">
-        <v>46065</v>
+        <v>46059</v>
       </c>
       <c r="F22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="s">
         <v>4</v>
@@ -2304,25 +2385,25 @@
         <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="P22" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="R22" t="s">
         <v>1</v>
       </c>
       <c r="S22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" t="s">
         <v>12</v>
       </c>
       <c r="U22" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="V22" t="s">
         <v>1</v>
@@ -2339,34 +2420,34 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2">
         <v>46059</v>
       </c>
       <c r="F23" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="3">
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="s">
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K23" t="s">
         <v>6</v>
@@ -2393,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="S23" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" t="s">
         <v>12</v>
@@ -2416,16 +2497,16 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2">
         <v>46059</v>
@@ -2443,7 +2524,7 @@
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s">
         <v>6</v>
@@ -2493,35 +2574,35 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="2">
+        <v>46050</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" t="s">
         <v>86</v>
       </c>
-      <c r="D25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="2">
-        <v>46059</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1</v>
-      </c>
-      <c r="I25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J25" t="s">
-        <v>88</v>
-      </c>
       <c r="K25" t="s">
         <v>6</v>
       </c>
@@ -2535,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="P25" t="s">
         <v>10</v>
@@ -2547,13 +2628,13 @@
         <v>1</v>
       </c>
       <c r="S25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="s">
         <v>12</v>
       </c>
       <c r="U25" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="V25" t="s">
         <v>1</v>
@@ -2570,16 +2651,16 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="E26" s="2">
         <v>46050</v>
@@ -2597,7 +2678,7 @@
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s">
         <v>6</v>
@@ -2612,7 +2693,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="P26" t="s">
         <v>10</v>
@@ -2630,7 +2711,7 @@
         <v>12</v>
       </c>
       <c r="U26" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="V26" t="s">
         <v>1</v>
@@ -2653,28 +2734,28 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2">
         <v>46050</v>
       </c>
       <c r="F27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="3">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="s">
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="K27" t="s">
         <v>6</v>
@@ -2689,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="P27" t="s">
         <v>10</v>
@@ -2701,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T27" t="s">
         <v>12</v>
@@ -2724,34 +2805,34 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E28" s="2">
         <v>46050</v>
       </c>
       <c r="F28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="3">
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="s">
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K28" t="s">
         <v>6</v>
@@ -2778,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="S28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T28" t="s">
         <v>12</v>
@@ -2801,19 +2882,19 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2">
-        <v>46050</v>
+        <v>46092</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
@@ -2828,7 +2909,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="K29" t="s">
         <v>6</v>
@@ -2878,19 +2959,19 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2">
-        <v>46050</v>
+        <v>46092</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
@@ -2905,7 +2986,7 @@
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="K30" t="s">
         <v>6</v>
@@ -2955,67 +3036,67 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="2">
+        <v>46094</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>4</v>
+      </c>
+      <c r="J31" t="s">
+        <v>94</v>
+      </c>
+      <c r="K31" t="s">
+        <v>6</v>
+      </c>
+      <c r="L31" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" t="s">
+        <v>8</v>
+      </c>
+      <c r="N31" t="s">
+        <v>1</v>
+      </c>
+      <c r="O31" t="s">
+        <v>9</v>
+      </c>
+      <c r="P31" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>36</v>
+      </c>
+      <c r="R31" t="s">
+        <v>1</v>
+      </c>
+      <c r="S31" s="3">
+        <v>1</v>
+      </c>
+      <c r="T31" t="s">
+        <v>12</v>
+      </c>
+      <c r="U31" t="s">
         <v>95</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" t="s">
-        <v>100</v>
-      </c>
-      <c r="E31" s="2">
-        <v>46050</v>
-      </c>
-      <c r="F31" s="3">
-        <v>1</v>
-      </c>
-      <c r="G31" s="3">
-        <v>0</v>
-      </c>
-      <c r="H31" s="3">
-        <v>1</v>
-      </c>
-      <c r="I31" t="s">
-        <v>4</v>
-      </c>
-      <c r="J31" t="s">
-        <v>101</v>
-      </c>
-      <c r="K31" t="s">
-        <v>6</v>
-      </c>
-      <c r="L31" t="s">
-        <v>7</v>
-      </c>
-      <c r="M31" t="s">
-        <v>8</v>
-      </c>
-      <c r="N31" t="s">
-        <v>1</v>
-      </c>
-      <c r="O31" t="s">
-        <v>23</v>
-      </c>
-      <c r="P31" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>11</v>
-      </c>
-      <c r="R31" t="s">
-        <v>1</v>
-      </c>
-      <c r="S31" s="3">
-        <v>1</v>
-      </c>
-      <c r="T31" t="s">
-        <v>12</v>
-      </c>
-      <c r="U31" t="s">
-        <v>13</v>
       </c>
       <c r="V31" t="s">
         <v>1</v>
@@ -3032,19 +3113,19 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E32" s="2">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -3059,7 +3140,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="K32" t="s">
         <v>6</v>
@@ -3074,13 +3155,13 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="P32" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q32" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R32" t="s">
         <v>1</v>
@@ -3092,7 +3173,7 @@
         <v>12</v>
       </c>
       <c r="U32" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="V32" t="s">
         <v>1</v>
@@ -3109,19 +3190,19 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="E33" s="2">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
@@ -3136,7 +3217,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="K33" t="s">
         <v>6</v>
@@ -3151,13 +3232,13 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="P33" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q33" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="R33" t="s">
         <v>1</v>
@@ -3169,7 +3250,7 @@
         <v>12</v>
       </c>
       <c r="U33" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="V33" t="s">
         <v>1</v>
@@ -3186,19 +3267,19 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="E34" s="2">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
@@ -3213,7 +3294,7 @@
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="K34" t="s">
         <v>6</v>
@@ -3228,13 +3309,13 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="P34" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="R34" t="s">
         <v>1</v>
@@ -3246,7 +3327,7 @@
         <v>12</v>
       </c>
       <c r="U34" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="V34" t="s">
         <v>1</v>
@@ -3263,55 +3344,55 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
         <v>104</v>
       </c>
-      <c r="B35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="2">
+        <v>46093</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" t="s">
+        <v>106</v>
+      </c>
+      <c r="K35" t="s">
+        <v>6</v>
+      </c>
+      <c r="L35" t="s">
+        <v>7</v>
+      </c>
+      <c r="M35" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" t="s">
+        <v>1</v>
+      </c>
+      <c r="O35" t="s">
         <v>107</v>
       </c>
-      <c r="D35" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="2">
-        <v>46094</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" t="s">
-        <v>108</v>
-      </c>
-      <c r="K35" t="s">
-        <v>6</v>
-      </c>
-      <c r="L35" t="s">
-        <v>7</v>
-      </c>
-      <c r="M35" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" t="s">
-        <v>1</v>
-      </c>
-      <c r="O35" t="s">
-        <v>9</v>
-      </c>
       <c r="P35" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="R35" t="s">
         <v>1</v>
@@ -3323,7 +3404,7 @@
         <v>12</v>
       </c>
       <c r="U35" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="V35" t="s">
         <v>1</v>
@@ -3340,19 +3421,19 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E36" s="2">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -3367,7 +3448,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="K36" t="s">
         <v>6</v>
@@ -3382,13 +3463,13 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="P36" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q36" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="R36" t="s">
         <v>1</v>
@@ -3400,7 +3481,7 @@
         <v>12</v>
       </c>
       <c r="U36" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="V36" t="s">
         <v>1</v>
@@ -3417,7 +3498,7 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
@@ -3426,26 +3507,26 @@
         <v>109</v>
       </c>
       <c r="D37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="2">
+        <v>46085</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>4</v>
+      </c>
+      <c r="J37" t="s">
         <v>110</v>
       </c>
-      <c r="E37" s="2">
-        <v>46094</v>
-      </c>
-      <c r="F37" s="3">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3">
-        <v>0</v>
-      </c>
-      <c r="H37" s="3">
-        <v>1</v>
-      </c>
-      <c r="I37" t="s">
-        <v>4</v>
-      </c>
-      <c r="J37" t="s">
-        <v>111</v>
-      </c>
       <c r="K37" t="s">
         <v>6</v>
       </c>
@@ -3459,13 +3540,13 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="P37" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="R37" t="s">
         <v>1</v>
@@ -3477,7 +3558,7 @@
         <v>12</v>
       </c>
       <c r="U37" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="V37" t="s">
         <v>1</v>
@@ -3494,19 +3575,19 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" t="s">
         <v>112</v>
       </c>
-      <c r="B38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" t="s">
-        <v>52</v>
-      </c>
       <c r="E38" s="2">
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
@@ -3521,7 +3602,7 @@
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="K38" t="s">
         <v>6</v>
@@ -3536,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="P38" t="s">
         <v>10</v>
@@ -3571,34 +3652,34 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
       </c>
       <c r="E39" s="2">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="F39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="3">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" t="s">
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K39" t="s">
         <v>6</v>
@@ -3610,7 +3691,7 @@
         <v>8</v>
       </c>
       <c r="N39" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="O39" t="s">
         <v>117</v>
@@ -3625,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="S39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T39" t="s">
         <v>12</v>
@@ -3648,34 +3729,34 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E40" s="2">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="F40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="3">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" t="s">
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="K40" t="s">
         <v>6</v>
@@ -3687,10 +3768,10 @@
         <v>8</v>
       </c>
       <c r="N40" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="P40" t="s">
         <v>10</v>
@@ -3702,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="S40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T40" t="s">
         <v>12</v>
@@ -3725,19 +3806,19 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E41" s="2">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="F41" s="3">
         <v>1</v>
@@ -3752,7 +3833,7 @@
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="K41" t="s">
         <v>6</v>
@@ -3767,7 +3848,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="P41" t="s">
         <v>10</v>
@@ -3802,19 +3883,19 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="E42" s="2">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="F42" s="3">
         <v>1</v>
@@ -3829,7 +3910,7 @@
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="K42" t="s">
         <v>6</v>
@@ -3879,34 +3960,34 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="E43" s="2">
         <v>46086</v>
       </c>
       <c r="F43" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" t="s">
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="K43" t="s">
         <v>6</v>
@@ -3921,7 +4002,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="P43" t="s">
         <v>10</v>
@@ -3933,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="S43" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T43" t="s">
         <v>12</v>
@@ -3956,19 +4037,19 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
         <v>125</v>
       </c>
-      <c r="B44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
-        <v>80</v>
-      </c>
       <c r="D44" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="E44" s="2">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="F44" s="3">
         <v>2</v>
@@ -3983,7 +4064,7 @@
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="K44" t="s">
         <v>6</v>
@@ -3998,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="P44" t="s">
         <v>10</v>
@@ -4010,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="S44" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T44" t="s">
         <v>12</v>
@@ -4033,34 +4114,34 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B45" t="s">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="D45" t="s">
         <v>128</v>
       </c>
       <c r="E45" s="2">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="F45" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" t="s">
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="K45" t="s">
         <v>6</v>
@@ -4075,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="P45" t="s">
         <v>10</v>
@@ -4087,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="S45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="s">
         <v>12</v>
@@ -4110,34 +4191,34 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="D46" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E46" s="2">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="F46" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="3">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" t="s">
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="K46" t="s">
         <v>6</v>
@@ -4164,7 +4245,7 @@
         <v>1</v>
       </c>
       <c r="S46" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T46" t="s">
         <v>12</v>
@@ -4187,19 +4268,19 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="E47" s="2">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
@@ -4214,7 +4295,7 @@
         <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="K47" t="s">
         <v>6</v>
@@ -4264,19 +4345,19 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E48" s="2">
-        <v>46086</v>
+        <v>46083</v>
       </c>
       <c r="F48" s="3">
         <v>1</v>
@@ -4291,7 +4372,7 @@
         <v>4</v>
       </c>
       <c r="J48" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s">
         <v>6</v>
@@ -4341,35 +4422,35 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" t="s">
+        <v>124</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" t="s">
         <v>134</v>
       </c>
-      <c r="B49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="E49" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" t="s">
         <v>135</v>
       </c>
-      <c r="D49" t="s">
-        <v>136</v>
-      </c>
-      <c r="E49" s="2">
-        <v>46059</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" t="s">
-        <v>137</v>
-      </c>
       <c r="K49" t="s">
         <v>6</v>
       </c>
@@ -4383,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P49" t="s">
         <v>10</v>
@@ -4395,13 +4476,13 @@
         <v>1</v>
       </c>
       <c r="S49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="s">
         <v>12</v>
       </c>
       <c r="U49" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="V49" t="s">
         <v>1</v>
@@ -4418,78 +4499,2542 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" t="s">
+        <v>124</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F50" s="3">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>4</v>
+      </c>
+      <c r="J50" t="s">
+        <v>121</v>
+      </c>
+      <c r="K50" t="s">
+        <v>6</v>
+      </c>
+      <c r="L50" t="s">
+        <v>7</v>
+      </c>
+      <c r="M50" t="s">
+        <v>8</v>
+      </c>
+      <c r="N50" t="s">
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
+        <v>23</v>
+      </c>
+      <c r="P50" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>11</v>
+      </c>
+      <c r="R50" t="s">
+        <v>1</v>
+      </c>
+      <c r="S50" s="3">
+        <v>1</v>
+      </c>
+      <c r="T50" t="s">
+        <v>12</v>
+      </c>
+      <c r="U50" t="s">
+        <v>13</v>
+      </c>
+      <c r="V50" t="s">
+        <v>1</v>
+      </c>
+      <c r="W50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F51" s="3">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>4</v>
+      </c>
+      <c r="J51" t="s">
         <v>138</v>
       </c>
-      <c r="B50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="K51" t="s">
+        <v>6</v>
+      </c>
+      <c r="L51" t="s">
+        <v>7</v>
+      </c>
+      <c r="M51" t="s">
+        <v>8</v>
+      </c>
+      <c r="N51" t="s">
+        <v>1</v>
+      </c>
+      <c r="O51" t="s">
+        <v>101</v>
+      </c>
+      <c r="P51" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>11</v>
+      </c>
+      <c r="R51" t="s">
+        <v>1</v>
+      </c>
+      <c r="S51" s="3">
+        <v>1</v>
+      </c>
+      <c r="T51" t="s">
+        <v>12</v>
+      </c>
+      <c r="U51" t="s">
+        <v>13</v>
+      </c>
+      <c r="V51" t="s">
+        <v>1</v>
+      </c>
+      <c r="W51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X51" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
-      <c r="D50" t="s">
+      <c r="B52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>125</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>2</v>
+      </c>
+      <c r="I52" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" t="s">
+        <v>126</v>
+      </c>
+      <c r="K52" t="s">
+        <v>6</v>
+      </c>
+      <c r="L52" t="s">
+        <v>7</v>
+      </c>
+      <c r="M52" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" t="s">
+        <v>1</v>
+      </c>
+      <c r="O52" t="s">
+        <v>117</v>
+      </c>
+      <c r="P52" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>11</v>
+      </c>
+      <c r="R52" t="s">
+        <v>1</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" t="s">
+        <v>12</v>
+      </c>
+      <c r="U52" t="s">
+        <v>13</v>
+      </c>
+      <c r="V52" t="s">
+        <v>1</v>
+      </c>
+      <c r="W52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25">
+      <c r="A53" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>127</v>
+      </c>
+      <c r="D53" t="s">
+        <v>128</v>
+      </c>
+      <c r="E53" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F53" s="3">
+        <v>2</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <v>2</v>
+      </c>
+      <c r="I53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J53" t="s">
+        <v>129</v>
+      </c>
+      <c r="K53" t="s">
+        <v>6</v>
+      </c>
+      <c r="L53" t="s">
+        <v>7</v>
+      </c>
+      <c r="M53" t="s">
+        <v>8</v>
+      </c>
+      <c r="N53" t="s">
+        <v>1</v>
+      </c>
+      <c r="O53" t="s">
+        <v>117</v>
+      </c>
+      <c r="P53" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>11</v>
+      </c>
+      <c r="R53" t="s">
+        <v>1</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" t="s">
+        <v>12</v>
+      </c>
+      <c r="U53" t="s">
+        <v>13</v>
+      </c>
+      <c r="V53" t="s">
+        <v>1</v>
+      </c>
+      <c r="W53" t="s">
+        <v>1</v>
+      </c>
+      <c r="X53" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25">
+      <c r="A54" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E54" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F54" s="3">
+        <v>60</v>
+      </c>
+      <c r="G54" s="3">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3">
+        <v>60</v>
+      </c>
+      <c r="I54" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" t="s">
+        <v>142</v>
+      </c>
+      <c r="K54" t="s">
+        <v>6</v>
+      </c>
+      <c r="L54" t="s">
+        <v>7</v>
+      </c>
+      <c r="M54" t="s">
+        <v>8</v>
+      </c>
+      <c r="N54" t="s">
+        <v>1</v>
+      </c>
+      <c r="O54" t="s">
+        <v>107</v>
+      </c>
+      <c r="P54" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>11</v>
+      </c>
+      <c r="R54" t="s">
+        <v>1</v>
+      </c>
+      <c r="S54" s="3">
+        <v>60</v>
+      </c>
+      <c r="T54" t="s">
+        <v>12</v>
+      </c>
+      <c r="U54" t="s">
+        <v>13</v>
+      </c>
+      <c r="V54" t="s">
+        <v>1</v>
+      </c>
+      <c r="W54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25">
+      <c r="A55" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" t="s">
+        <v>118</v>
+      </c>
+      <c r="E55" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F55" s="3">
+        <v>2</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3">
+        <v>2</v>
+      </c>
+      <c r="I55" t="s">
+        <v>4</v>
+      </c>
+      <c r="J55" t="s">
+        <v>76</v>
+      </c>
+      <c r="K55" t="s">
+        <v>6</v>
+      </c>
+      <c r="L55" t="s">
+        <v>7</v>
+      </c>
+      <c r="M55" t="s">
+        <v>8</v>
+      </c>
+      <c r="N55" t="s">
+        <v>1</v>
+      </c>
+      <c r="O55" t="s">
+        <v>23</v>
+      </c>
+      <c r="P55" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>11</v>
+      </c>
+      <c r="R55" t="s">
+        <v>1</v>
+      </c>
+      <c r="S55" s="3">
+        <v>2</v>
+      </c>
+      <c r="T55" t="s">
+        <v>12</v>
+      </c>
+      <c r="U55" t="s">
+        <v>13</v>
+      </c>
+      <c r="V55" t="s">
+        <v>1</v>
+      </c>
+      <c r="W55" t="s">
+        <v>1</v>
+      </c>
+      <c r="X55" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25">
+      <c r="A56" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>130</v>
+      </c>
+      <c r="D56" t="s">
+        <v>131</v>
+      </c>
+      <c r="E56" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F56" s="3">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" t="s">
+        <v>4</v>
+      </c>
+      <c r="J56" t="s">
+        <v>132</v>
+      </c>
+      <c r="K56" t="s">
+        <v>6</v>
+      </c>
+      <c r="L56" t="s">
+        <v>7</v>
+      </c>
+      <c r="M56" t="s">
+        <v>8</v>
+      </c>
+      <c r="N56" t="s">
+        <v>1</v>
+      </c>
+      <c r="O56" t="s">
+        <v>23</v>
+      </c>
+      <c r="P56" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>11</v>
+      </c>
+      <c r="R56" t="s">
+        <v>1</v>
+      </c>
+      <c r="S56" s="3">
+        <v>1</v>
+      </c>
+      <c r="T56" t="s">
+        <v>12</v>
+      </c>
+      <c r="U56" t="s">
+        <v>13</v>
+      </c>
+      <c r="V56" t="s">
+        <v>1</v>
+      </c>
+      <c r="W56" t="s">
+        <v>1</v>
+      </c>
+      <c r="X56" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25">
+      <c r="A57" t="s">
+        <v>139</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>77</v>
+      </c>
+      <c r="D57" t="s">
+        <v>65</v>
+      </c>
+      <c r="E57" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" t="s">
+        <v>79</v>
+      </c>
+      <c r="K57" t="s">
+        <v>6</v>
+      </c>
+      <c r="L57" t="s">
+        <v>7</v>
+      </c>
+      <c r="M57" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" t="s">
+        <v>1</v>
+      </c>
+      <c r="O57" t="s">
+        <v>23</v>
+      </c>
+      <c r="P57" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>11</v>
+      </c>
+      <c r="R57" t="s">
+        <v>1</v>
+      </c>
+      <c r="S57" s="3">
+        <v>1</v>
+      </c>
+      <c r="T57" t="s">
+        <v>12</v>
+      </c>
+      <c r="U57" t="s">
+        <v>13</v>
+      </c>
+      <c r="V57" t="s">
+        <v>1</v>
+      </c>
+      <c r="W57" t="s">
+        <v>1</v>
+      </c>
+      <c r="X57" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25">
+      <c r="A58" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1</v>
+      </c>
+      <c r="I58" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" t="s">
+        <v>135</v>
+      </c>
+      <c r="K58" t="s">
+        <v>6</v>
+      </c>
+      <c r="L58" t="s">
+        <v>7</v>
+      </c>
+      <c r="M58" t="s">
+        <v>8</v>
+      </c>
+      <c r="N58" t="s">
+        <v>1</v>
+      </c>
+      <c r="O58" t="s">
+        <v>23</v>
+      </c>
+      <c r="P58" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>11</v>
+      </c>
+      <c r="R58" t="s">
+        <v>1</v>
+      </c>
+      <c r="S58" s="3">
+        <v>1</v>
+      </c>
+      <c r="T58" t="s">
+        <v>12</v>
+      </c>
+      <c r="U58" t="s">
+        <v>13</v>
+      </c>
+      <c r="V58" t="s">
+        <v>1</v>
+      </c>
+      <c r="W58" t="s">
+        <v>1</v>
+      </c>
+      <c r="X58" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25">
+      <c r="A59" t="s">
+        <v>139</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
         <v>119</v>
       </c>
-      <c r="E50" s="2">
+      <c r="D59" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1</v>
+      </c>
+      <c r="I59" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" t="s">
+        <v>121</v>
+      </c>
+      <c r="K59" t="s">
+        <v>6</v>
+      </c>
+      <c r="L59" t="s">
+        <v>7</v>
+      </c>
+      <c r="M59" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" t="s">
+        <v>1</v>
+      </c>
+      <c r="O59" t="s">
+        <v>23</v>
+      </c>
+      <c r="P59" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>11</v>
+      </c>
+      <c r="R59" t="s">
+        <v>1</v>
+      </c>
+      <c r="S59" s="3">
+        <v>1</v>
+      </c>
+      <c r="T59" t="s">
+        <v>12</v>
+      </c>
+      <c r="U59" t="s">
+        <v>13</v>
+      </c>
+      <c r="V59" t="s">
+        <v>1</v>
+      </c>
+      <c r="W59" t="s">
+        <v>1</v>
+      </c>
+      <c r="X59" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25">
+      <c r="A60" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" t="s">
+        <v>144</v>
+      </c>
+      <c r="E60" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
+        <v>1</v>
+      </c>
+      <c r="I60" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" t="s">
+        <v>145</v>
+      </c>
+      <c r="K60" t="s">
+        <v>6</v>
+      </c>
+      <c r="L60" t="s">
+        <v>7</v>
+      </c>
+      <c r="M60" t="s">
+        <v>8</v>
+      </c>
+      <c r="N60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O60" t="s">
+        <v>23</v>
+      </c>
+      <c r="P60" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>11</v>
+      </c>
+      <c r="R60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S60" s="3">
+        <v>1</v>
+      </c>
+      <c r="T60" t="s">
+        <v>12</v>
+      </c>
+      <c r="U60" t="s">
+        <v>13</v>
+      </c>
+      <c r="V60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25">
+      <c r="A61" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>146</v>
+      </c>
+      <c r="D61" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>4</v>
+      </c>
+      <c r="J61" t="s">
+        <v>147</v>
+      </c>
+      <c r="K61" t="s">
+        <v>6</v>
+      </c>
+      <c r="L61" t="s">
+        <v>7</v>
+      </c>
+      <c r="M61" t="s">
+        <v>8</v>
+      </c>
+      <c r="N61" t="s">
+        <v>1</v>
+      </c>
+      <c r="O61" t="s">
+        <v>23</v>
+      </c>
+      <c r="P61" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>11</v>
+      </c>
+      <c r="R61" t="s">
+        <v>1</v>
+      </c>
+      <c r="S61" s="3">
+        <v>1</v>
+      </c>
+      <c r="T61" t="s">
+        <v>12</v>
+      </c>
+      <c r="U61" t="s">
+        <v>13</v>
+      </c>
+      <c r="V61" t="s">
+        <v>1</v>
+      </c>
+      <c r="W61" t="s">
+        <v>1</v>
+      </c>
+      <c r="X61" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25">
+      <c r="A62" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>136</v>
+      </c>
+      <c r="D62" t="s">
+        <v>137</v>
+      </c>
+      <c r="E62" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" t="s">
+        <v>138</v>
+      </c>
+      <c r="K62" t="s">
+        <v>6</v>
+      </c>
+      <c r="L62" t="s">
+        <v>7</v>
+      </c>
+      <c r="M62" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" t="s">
+        <v>1</v>
+      </c>
+      <c r="O62" t="s">
+        <v>101</v>
+      </c>
+      <c r="P62" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>11</v>
+      </c>
+      <c r="R62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1</v>
+      </c>
+      <c r="T62" t="s">
+        <v>12</v>
+      </c>
+      <c r="U62" t="s">
+        <v>13</v>
+      </c>
+      <c r="V62" t="s">
+        <v>1</v>
+      </c>
+      <c r="W62" t="s">
+        <v>1</v>
+      </c>
+      <c r="X62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25">
+      <c r="A63" t="s">
+        <v>148</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>125</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F63" s="3">
+        <v>2</v>
+      </c>
+      <c r="G63" s="3">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3">
+        <v>2</v>
+      </c>
+      <c r="I63" t="s">
+        <v>4</v>
+      </c>
+      <c r="J63" t="s">
+        <v>126</v>
+      </c>
+      <c r="K63" t="s">
+        <v>6</v>
+      </c>
+      <c r="L63" t="s">
+        <v>7</v>
+      </c>
+      <c r="M63" t="s">
+        <v>8</v>
+      </c>
+      <c r="N63" t="s">
+        <v>1</v>
+      </c>
+      <c r="O63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>11</v>
+      </c>
+      <c r="R63" t="s">
+        <v>1</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" t="s">
+        <v>12</v>
+      </c>
+      <c r="U63" t="s">
+        <v>13</v>
+      </c>
+      <c r="V63" t="s">
+        <v>1</v>
+      </c>
+      <c r="W63" t="s">
+        <v>1</v>
+      </c>
+      <c r="X63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25">
+      <c r="A64" t="s">
+        <v>148</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>127</v>
+      </c>
+      <c r="D64" t="s">
+        <v>128</v>
+      </c>
+      <c r="E64" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F64" s="3">
+        <v>2</v>
+      </c>
+      <c r="G64" s="3">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3">
+        <v>2</v>
+      </c>
+      <c r="I64" t="s">
+        <v>4</v>
+      </c>
+      <c r="J64" t="s">
+        <v>129</v>
+      </c>
+      <c r="K64" t="s">
+        <v>6</v>
+      </c>
+      <c r="L64" t="s">
+        <v>7</v>
+      </c>
+      <c r="M64" t="s">
+        <v>8</v>
+      </c>
+      <c r="N64" t="s">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
+        <v>117</v>
+      </c>
+      <c r="P64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>11</v>
+      </c>
+      <c r="R64" t="s">
+        <v>1</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" t="s">
+        <v>12</v>
+      </c>
+      <c r="U64" t="s">
+        <v>13</v>
+      </c>
+      <c r="V64" t="s">
+        <v>1</v>
+      </c>
+      <c r="W64" t="s">
+        <v>1</v>
+      </c>
+      <c r="X64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25">
+      <c r="A65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" t="s">
+        <v>141</v>
+      </c>
+      <c r="E65" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F65" s="3">
+        <v>60</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3">
+        <v>60</v>
+      </c>
+      <c r="I65" t="s">
+        <v>4</v>
+      </c>
+      <c r="J65" t="s">
+        <v>142</v>
+      </c>
+      <c r="K65" t="s">
+        <v>6</v>
+      </c>
+      <c r="L65" t="s">
+        <v>7</v>
+      </c>
+      <c r="M65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O65" t="s">
+        <v>107</v>
+      </c>
+      <c r="P65" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>11</v>
+      </c>
+      <c r="R65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S65" s="3">
+        <v>60</v>
+      </c>
+      <c r="T65" t="s">
+        <v>12</v>
+      </c>
+      <c r="U65" t="s">
+        <v>13</v>
+      </c>
+      <c r="V65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W65" t="s">
+        <v>1</v>
+      </c>
+      <c r="X65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25">
+      <c r="A66" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>149</v>
+      </c>
+      <c r="D66" t="s">
+        <v>43</v>
+      </c>
+      <c r="E66" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" t="s">
+        <v>150</v>
+      </c>
+      <c r="K66" t="s">
+        <v>6</v>
+      </c>
+      <c r="L66" t="s">
+        <v>7</v>
+      </c>
+      <c r="M66" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" t="s">
+        <v>1</v>
+      </c>
+      <c r="O66" t="s">
+        <v>107</v>
+      </c>
+      <c r="P66" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>11</v>
+      </c>
+      <c r="R66" t="s">
+        <v>1</v>
+      </c>
+      <c r="S66" s="3">
+        <v>1</v>
+      </c>
+      <c r="T66" t="s">
+        <v>12</v>
+      </c>
+      <c r="U66" t="s">
+        <v>13</v>
+      </c>
+      <c r="V66" t="s">
+        <v>1</v>
+      </c>
+      <c r="W66" t="s">
+        <v>1</v>
+      </c>
+      <c r="X66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25">
+      <c r="A67" t="s">
+        <v>148</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>151</v>
+      </c>
+      <c r="D67" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F67" s="3">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3">
+        <v>1</v>
+      </c>
+      <c r="I67" t="s">
+        <v>4</v>
+      </c>
+      <c r="J67" t="s">
+        <v>152</v>
+      </c>
+      <c r="K67" t="s">
+        <v>6</v>
+      </c>
+      <c r="L67" t="s">
+        <v>7</v>
+      </c>
+      <c r="M67" t="s">
+        <v>8</v>
+      </c>
+      <c r="N67" t="s">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>107</v>
+      </c>
+      <c r="P67" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>11</v>
+      </c>
+      <c r="R67" t="s">
+        <v>1</v>
+      </c>
+      <c r="S67" s="3">
+        <v>1</v>
+      </c>
+      <c r="T67" t="s">
+        <v>12</v>
+      </c>
+      <c r="U67" t="s">
+        <v>13</v>
+      </c>
+      <c r="V67" t="s">
+        <v>1</v>
+      </c>
+      <c r="W67" t="s">
+        <v>1</v>
+      </c>
+      <c r="X67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25">
+      <c r="A68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>74</v>
+      </c>
+      <c r="D68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E68" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F68" s="3">
+        <v>2</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3">
+        <v>2</v>
+      </c>
+      <c r="I68" t="s">
+        <v>4</v>
+      </c>
+      <c r="J68" t="s">
+        <v>76</v>
+      </c>
+      <c r="K68" t="s">
+        <v>6</v>
+      </c>
+      <c r="L68" t="s">
+        <v>7</v>
+      </c>
+      <c r="M68" t="s">
+        <v>8</v>
+      </c>
+      <c r="N68" t="s">
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
+        <v>23</v>
+      </c>
+      <c r="P68" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>11</v>
+      </c>
+      <c r="R68" t="s">
+        <v>1</v>
+      </c>
+      <c r="S68" s="3">
+        <v>2</v>
+      </c>
+      <c r="T68" t="s">
+        <v>12</v>
+      </c>
+      <c r="U68" t="s">
+        <v>13</v>
+      </c>
+      <c r="V68" t="s">
+        <v>1</v>
+      </c>
+      <c r="W68" t="s">
+        <v>1</v>
+      </c>
+      <c r="X68" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25">
+      <c r="A69" t="s">
+        <v>148</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>130</v>
+      </c>
+      <c r="D69" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F69" s="3">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3">
+        <v>1</v>
+      </c>
+      <c r="I69" t="s">
+        <v>4</v>
+      </c>
+      <c r="J69" t="s">
+        <v>132</v>
+      </c>
+      <c r="K69" t="s">
+        <v>6</v>
+      </c>
+      <c r="L69" t="s">
+        <v>7</v>
+      </c>
+      <c r="M69" t="s">
+        <v>8</v>
+      </c>
+      <c r="N69" t="s">
+        <v>1</v>
+      </c>
+      <c r="O69" t="s">
+        <v>23</v>
+      </c>
+      <c r="P69" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>11</v>
+      </c>
+      <c r="R69" t="s">
+        <v>1</v>
+      </c>
+      <c r="S69" s="3">
+        <v>1</v>
+      </c>
+      <c r="T69" t="s">
+        <v>12</v>
+      </c>
+      <c r="U69" t="s">
+        <v>13</v>
+      </c>
+      <c r="V69" t="s">
+        <v>1</v>
+      </c>
+      <c r="W69" t="s">
+        <v>1</v>
+      </c>
+      <c r="X69" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25">
+      <c r="A70" t="s">
+        <v>148</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" t="s">
+        <v>65</v>
+      </c>
+      <c r="E70" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F70" s="3">
+        <v>1</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <v>1</v>
+      </c>
+      <c r="I70" t="s">
+        <v>4</v>
+      </c>
+      <c r="J70" t="s">
+        <v>79</v>
+      </c>
+      <c r="K70" t="s">
+        <v>6</v>
+      </c>
+      <c r="L70" t="s">
+        <v>7</v>
+      </c>
+      <c r="M70" t="s">
+        <v>8</v>
+      </c>
+      <c r="N70" t="s">
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
+        <v>23</v>
+      </c>
+      <c r="P70" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>11</v>
+      </c>
+      <c r="R70" t="s">
+        <v>1</v>
+      </c>
+      <c r="S70" s="3">
+        <v>1</v>
+      </c>
+      <c r="T70" t="s">
+        <v>12</v>
+      </c>
+      <c r="U70" t="s">
+        <v>13</v>
+      </c>
+      <c r="V70" t="s">
+        <v>1</v>
+      </c>
+      <c r="W70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25">
+      <c r="A71" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
+        <v>133</v>
+      </c>
+      <c r="D71" t="s">
+        <v>134</v>
+      </c>
+      <c r="E71" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F71" s="3">
+        <v>1</v>
+      </c>
+      <c r="G71" s="3">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3">
+        <v>1</v>
+      </c>
+      <c r="I71" t="s">
+        <v>4</v>
+      </c>
+      <c r="J71" t="s">
+        <v>135</v>
+      </c>
+      <c r="K71" t="s">
+        <v>6</v>
+      </c>
+      <c r="L71" t="s">
+        <v>7</v>
+      </c>
+      <c r="M71" t="s">
+        <v>8</v>
+      </c>
+      <c r="N71" t="s">
+        <v>1</v>
+      </c>
+      <c r="O71" t="s">
+        <v>23</v>
+      </c>
+      <c r="P71" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>11</v>
+      </c>
+      <c r="R71" t="s">
+        <v>1</v>
+      </c>
+      <c r="S71" s="3">
+        <v>1</v>
+      </c>
+      <c r="T71" t="s">
+        <v>12</v>
+      </c>
+      <c r="U71" t="s">
+        <v>13</v>
+      </c>
+      <c r="V71" t="s">
+        <v>1</v>
+      </c>
+      <c r="W71" t="s">
+        <v>1</v>
+      </c>
+      <c r="X71" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25">
+      <c r="A72" t="s">
+        <v>148</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
+        <v>119</v>
+      </c>
+      <c r="D72" t="s">
+        <v>70</v>
+      </c>
+      <c r="E72" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F72" s="3">
+        <v>1</v>
+      </c>
+      <c r="G72" s="3">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" t="s">
+        <v>121</v>
+      </c>
+      <c r="K72" t="s">
+        <v>6</v>
+      </c>
+      <c r="L72" t="s">
+        <v>7</v>
+      </c>
+      <c r="M72" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" t="s">
+        <v>1</v>
+      </c>
+      <c r="O72" t="s">
+        <v>23</v>
+      </c>
+      <c r="P72" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>11</v>
+      </c>
+      <c r="R72" t="s">
+        <v>1</v>
+      </c>
+      <c r="S72" s="3">
+        <v>1</v>
+      </c>
+      <c r="T72" t="s">
+        <v>12</v>
+      </c>
+      <c r="U72" t="s">
+        <v>13</v>
+      </c>
+      <c r="V72" t="s">
+        <v>1</v>
+      </c>
+      <c r="W72" t="s">
+        <v>1</v>
+      </c>
+      <c r="X72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25">
+      <c r="A73" t="s">
+        <v>148</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s">
+        <v>143</v>
+      </c>
+      <c r="D73" t="s">
+        <v>144</v>
+      </c>
+      <c r="E73" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F73" s="3">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>4</v>
+      </c>
+      <c r="J73" t="s">
+        <v>145</v>
+      </c>
+      <c r="K73" t="s">
+        <v>6</v>
+      </c>
+      <c r="L73" t="s">
+        <v>7</v>
+      </c>
+      <c r="M73" t="s">
+        <v>8</v>
+      </c>
+      <c r="N73" t="s">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
+        <v>23</v>
+      </c>
+      <c r="P73" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>11</v>
+      </c>
+      <c r="R73" t="s">
+        <v>1</v>
+      </c>
+      <c r="S73" s="3">
+        <v>1</v>
+      </c>
+      <c r="T73" t="s">
+        <v>12</v>
+      </c>
+      <c r="U73" t="s">
+        <v>13</v>
+      </c>
+      <c r="V73" t="s">
+        <v>1</v>
+      </c>
+      <c r="W73" t="s">
+        <v>1</v>
+      </c>
+      <c r="X73" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25">
+      <c r="A74" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>146</v>
+      </c>
+      <c r="D74" t="s">
+        <v>48</v>
+      </c>
+      <c r="E74" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F74" s="3">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>4</v>
+      </c>
+      <c r="J74" t="s">
+        <v>147</v>
+      </c>
+      <c r="K74" t="s">
+        <v>6</v>
+      </c>
+      <c r="L74" t="s">
+        <v>7</v>
+      </c>
+      <c r="M74" t="s">
+        <v>8</v>
+      </c>
+      <c r="N74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O74" t="s">
+        <v>23</v>
+      </c>
+      <c r="P74" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>11</v>
+      </c>
+      <c r="R74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S74" s="3">
+        <v>1</v>
+      </c>
+      <c r="T74" t="s">
+        <v>12</v>
+      </c>
+      <c r="U74" t="s">
+        <v>13</v>
+      </c>
+      <c r="V74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W74" t="s">
+        <v>1</v>
+      </c>
+      <c r="X74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25">
+      <c r="A75" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>136</v>
+      </c>
+      <c r="D75" t="s">
+        <v>137</v>
+      </c>
+      <c r="E75" s="2">
+        <v>46083</v>
+      </c>
+      <c r="F75" s="3">
+        <v>1</v>
+      </c>
+      <c r="G75" s="3">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>4</v>
+      </c>
+      <c r="J75" t="s">
+        <v>138</v>
+      </c>
+      <c r="K75" t="s">
+        <v>6</v>
+      </c>
+      <c r="L75" t="s">
+        <v>7</v>
+      </c>
+      <c r="M75" t="s">
+        <v>8</v>
+      </c>
+      <c r="N75" t="s">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
+        <v>101</v>
+      </c>
+      <c r="P75" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>11</v>
+      </c>
+      <c r="R75" t="s">
+        <v>1</v>
+      </c>
+      <c r="S75" s="3">
+        <v>1</v>
+      </c>
+      <c r="T75" t="s">
+        <v>12</v>
+      </c>
+      <c r="U75" t="s">
+        <v>13</v>
+      </c>
+      <c r="V75" t="s">
+        <v>1</v>
+      </c>
+      <c r="W75" t="s">
+        <v>1</v>
+      </c>
+      <c r="X75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25">
+      <c r="A76" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>154</v>
+      </c>
+      <c r="D76" t="s">
+        <v>128</v>
+      </c>
+      <c r="E76" s="2">
+        <v>46099</v>
+      </c>
+      <c r="F76" s="3">
+        <v>2</v>
+      </c>
+      <c r="G76" s="3">
+        <v>1</v>
+      </c>
+      <c r="H76" s="3">
+        <v>1</v>
+      </c>
+      <c r="I76" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" t="s">
+        <v>155</v>
+      </c>
+      <c r="K76" t="s">
+        <v>6</v>
+      </c>
+      <c r="L76" t="s">
+        <v>7</v>
+      </c>
+      <c r="M76" t="s">
+        <v>8</v>
+      </c>
+      <c r="N76" t="s">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
+        <v>117</v>
+      </c>
+      <c r="P76" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>11</v>
+      </c>
+      <c r="R76" t="s">
+        <v>1</v>
+      </c>
+      <c r="S76" s="3">
+        <v>2</v>
+      </c>
+      <c r="T76" t="s">
+        <v>12</v>
+      </c>
+      <c r="U76" t="s">
+        <v>13</v>
+      </c>
+      <c r="V76" t="s">
+        <v>1</v>
+      </c>
+      <c r="W76" t="s">
+        <v>1</v>
+      </c>
+      <c r="X76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25">
+      <c r="A77" t="s">
+        <v>153</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>156</v>
+      </c>
+      <c r="D77" t="s">
+        <v>107</v>
+      </c>
+      <c r="E77" s="2">
+        <v>46099</v>
+      </c>
+      <c r="F77" s="3">
+        <v>1</v>
+      </c>
+      <c r="G77" s="3">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3">
+        <v>1</v>
+      </c>
+      <c r="I77" t="s">
+        <v>4</v>
+      </c>
+      <c r="J77" t="s">
+        <v>157</v>
+      </c>
+      <c r="K77" t="s">
+        <v>6</v>
+      </c>
+      <c r="L77" t="s">
+        <v>7</v>
+      </c>
+      <c r="M77" t="s">
+        <v>8</v>
+      </c>
+      <c r="N77" t="s">
+        <v>1</v>
+      </c>
+      <c r="O77" t="s">
+        <v>23</v>
+      </c>
+      <c r="P77" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>11</v>
+      </c>
+      <c r="R77" t="s">
+        <v>1</v>
+      </c>
+      <c r="S77" s="3">
+        <v>1</v>
+      </c>
+      <c r="T77" t="s">
+        <v>12</v>
+      </c>
+      <c r="U77" t="s">
+        <v>13</v>
+      </c>
+      <c r="V77" t="s">
+        <v>1</v>
+      </c>
+      <c r="W77" t="s">
+        <v>1</v>
+      </c>
+      <c r="X77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25">
+      <c r="A78" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" t="s">
+        <v>51</v>
+      </c>
+      <c r="E78" s="2">
+        <v>46099</v>
+      </c>
+      <c r="F78" s="3">
+        <v>1</v>
+      </c>
+      <c r="G78" s="3">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>4</v>
+      </c>
+      <c r="J78" t="s">
+        <v>22</v>
+      </c>
+      <c r="K78" t="s">
+        <v>6</v>
+      </c>
+      <c r="L78" t="s">
+        <v>7</v>
+      </c>
+      <c r="M78" t="s">
+        <v>8</v>
+      </c>
+      <c r="N78" t="s">
+        <v>1</v>
+      </c>
+      <c r="O78" t="s">
+        <v>23</v>
+      </c>
+      <c r="P78" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>11</v>
+      </c>
+      <c r="R78" t="s">
+        <v>1</v>
+      </c>
+      <c r="S78" s="3">
+        <v>1</v>
+      </c>
+      <c r="T78" t="s">
+        <v>12</v>
+      </c>
+      <c r="U78" t="s">
+        <v>13</v>
+      </c>
+      <c r="V78" t="s">
+        <v>1</v>
+      </c>
+      <c r="W78" t="s">
+        <v>1</v>
+      </c>
+      <c r="X78" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25">
+      <c r="A79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" t="s">
+        <v>52</v>
+      </c>
+      <c r="E79" s="2">
+        <v>46099</v>
+      </c>
+      <c r="F79" s="3">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>4</v>
+      </c>
+      <c r="J79" t="s">
+        <v>26</v>
+      </c>
+      <c r="K79" t="s">
+        <v>6</v>
+      </c>
+      <c r="L79" t="s">
+        <v>7</v>
+      </c>
+      <c r="M79" t="s">
+        <v>8</v>
+      </c>
+      <c r="N79" t="s">
+        <v>1</v>
+      </c>
+      <c r="O79" t="s">
+        <v>23</v>
+      </c>
+      <c r="P79" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>11</v>
+      </c>
+      <c r="R79" t="s">
+        <v>1</v>
+      </c>
+      <c r="S79" s="3">
+        <v>1</v>
+      </c>
+      <c r="T79" t="s">
+        <v>12</v>
+      </c>
+      <c r="U79" t="s">
+        <v>13</v>
+      </c>
+      <c r="V79" t="s">
+        <v>1</v>
+      </c>
+      <c r="W79" t="s">
+        <v>1</v>
+      </c>
+      <c r="X79" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25">
+      <c r="A80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>158</v>
+      </c>
+      <c r="D80" t="s">
+        <v>159</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46099</v>
+      </c>
+      <c r="F80" s="3">
+        <v>1</v>
+      </c>
+      <c r="G80" s="3">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3">
+        <v>1</v>
+      </c>
+      <c r="I80" t="s">
+        <v>4</v>
+      </c>
+      <c r="J80" t="s">
+        <v>160</v>
+      </c>
+      <c r="K80" t="s">
+        <v>6</v>
+      </c>
+      <c r="L80" t="s">
+        <v>7</v>
+      </c>
+      <c r="M80" t="s">
+        <v>8</v>
+      </c>
+      <c r="N80" t="s">
+        <v>1</v>
+      </c>
+      <c r="O80" t="s">
+        <v>23</v>
+      </c>
+      <c r="P80" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>11</v>
+      </c>
+      <c r="R80" t="s">
+        <v>1</v>
+      </c>
+      <c r="S80" s="3">
+        <v>1</v>
+      </c>
+      <c r="T80" t="s">
+        <v>12</v>
+      </c>
+      <c r="U80" t="s">
+        <v>13</v>
+      </c>
+      <c r="V80" t="s">
+        <v>1</v>
+      </c>
+      <c r="W80" t="s">
+        <v>1</v>
+      </c>
+      <c r="X80" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25">
+      <c r="A81" t="s">
+        <v>161</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>162</v>
+      </c>
+      <c r="D81" t="s">
+        <v>163</v>
+      </c>
+      <c r="E81" s="2">
+        <v>46059</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
+        <v>1</v>
+      </c>
+      <c r="I81" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" t="s">
+        <v>164</v>
+      </c>
+      <c r="K81" t="s">
+        <v>6</v>
+      </c>
+      <c r="L81" t="s">
+        <v>7</v>
+      </c>
+      <c r="M81" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" t="s">
+        <v>1</v>
+      </c>
+      <c r="O81" t="s">
+        <v>30</v>
+      </c>
+      <c r="P81" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>11</v>
+      </c>
+      <c r="R81" t="s">
+        <v>1</v>
+      </c>
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" t="s">
+        <v>12</v>
+      </c>
+      <c r="U81" t="s">
+        <v>1</v>
+      </c>
+      <c r="V81" t="s">
+        <v>1</v>
+      </c>
+      <c r="W81" t="s">
+        <v>1</v>
+      </c>
+      <c r="X81" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25">
+      <c r="A82" t="s">
+        <v>165</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>166</v>
+      </c>
+      <c r="D82" t="s">
+        <v>128</v>
+      </c>
+      <c r="E82" s="2">
         <v>46064</v>
       </c>
-      <c r="F50" s="3">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3">
-        <v>0</v>
-      </c>
-      <c r="H50" s="3">
-        <v>1</v>
-      </c>
-      <c r="I50" t="s">
-        <v>4</v>
-      </c>
-      <c r="J50" t="s">
-        <v>140</v>
-      </c>
-      <c r="K50" t="s">
-        <v>6</v>
-      </c>
-      <c r="L50" t="s">
-        <v>7</v>
-      </c>
-      <c r="M50" t="s">
-        <v>8</v>
-      </c>
-      <c r="N50" t="s">
-        <v>1</v>
-      </c>
-      <c r="O50" t="s">
+      <c r="F82" s="3">
+        <v>1</v>
+      </c>
+      <c r="G82" s="3">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3">
+        <v>1</v>
+      </c>
+      <c r="I82" t="s">
+        <v>4</v>
+      </c>
+      <c r="J82" t="s">
+        <v>167</v>
+      </c>
+      <c r="K82" t="s">
+        <v>6</v>
+      </c>
+      <c r="L82" t="s">
+        <v>7</v>
+      </c>
+      <c r="M82" t="s">
+        <v>8</v>
+      </c>
+      <c r="N82" t="s">
+        <v>1</v>
+      </c>
+      <c r="O82" t="s">
         <v>30</v>
       </c>
-      <c r="P50" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>11</v>
-      </c>
-      <c r="R50" t="s">
-        <v>1</v>
-      </c>
-      <c r="S50" s="3">
-        <v>0</v>
-      </c>
-      <c r="T50" t="s">
-        <v>12</v>
-      </c>
-      <c r="U50" t="s">
-        <v>1</v>
-      </c>
-      <c r="V50" t="s">
-        <v>1</v>
-      </c>
-      <c r="W50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y50" t="s">
+      <c r="P82" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>11</v>
+      </c>
+      <c r="R82" t="s">
+        <v>1</v>
+      </c>
+      <c r="S82" s="3">
+        <v>0</v>
+      </c>
+      <c r="T82" t="s">
+        <v>12</v>
+      </c>
+      <c r="U82" t="s">
+        <v>1</v>
+      </c>
+      <c r="V82" t="s">
+        <v>1</v>
+      </c>
+      <c r="W82" t="s">
+        <v>1</v>
+      </c>
+      <c r="X82" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y82" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,510 +11,507 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="193">
-  <si>
-    <t>200006366</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="192">
+  <si>
+    <t>200006418</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>4023000061C0</t>
+    <t>080100087604</t>
+  </si>
+  <si>
+    <t>0020</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>D15K 主軸,010017_BBT40,M60,CW45</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>SHEO</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>1F004</t>
+  </si>
+  <si>
+    <t>組件課</t>
+  </si>
+  <si>
+    <t>REL</t>
+  </si>
+  <si>
+    <t>0802</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>200006445</t>
+  </si>
+  <si>
+    <t>8814001214D3</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>機頭加工圖,G6K_HCMC-1682</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>9804</t>
+  </si>
+  <si>
+    <t>200006482</t>
+  </si>
+  <si>
+    <t>8923000586A0</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>固定板,A軸前銅套用_d142*D166*3L</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>1X001</t>
+  </si>
+  <si>
+    <t>虛擬工作中心</t>
+  </si>
+  <si>
+    <t>9816</t>
+  </si>
+  <si>
+    <t>8420002369A0</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>襯套,A軸前_d130*D145*18L</t>
+  </si>
+  <si>
+    <t>4060000066C0</t>
+  </si>
+  <si>
+    <t>0310</t>
+  </si>
+  <si>
+    <t>活塞,A軸法蘭前部_d130*D186*129.5L</t>
+  </si>
+  <si>
+    <t>3209000356A0</t>
+  </si>
+  <si>
+    <t>0350</t>
+  </si>
+  <si>
+    <t>#50 主軸,CTS,BBT_D143*368L</t>
+  </si>
+  <si>
+    <t>0102</t>
+  </si>
+  <si>
+    <t>3217000174A0</t>
+  </si>
+  <si>
+    <t>0440</t>
+  </si>
+  <si>
+    <t>通心軸,CTS打刀用_D80*d13*H36.2</t>
+  </si>
+  <si>
+    <t>200006488</t>
+  </si>
+  <si>
+    <t>3241000017A1</t>
   </si>
   <si>
     <t>0060</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>油壓缸/打刀油缸_行程14</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0010</t>
-  </si>
-  <si>
-    <t>SHEO</t>
-  </si>
-  <si>
-    <t>0101</t>
-  </si>
-  <si>
-    <t>1F004</t>
-  </si>
-  <si>
-    <t>組件課</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>9804</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>8429000727A0</t>
+    <t>直齒離合器,C軸2.5度_D330*d280*H40,144T</t>
+  </si>
+  <si>
+    <t>200006489</t>
+  </si>
+  <si>
+    <t>200006490</t>
+  </si>
+  <si>
+    <t>200006500</t>
+  </si>
+  <si>
+    <t>8420002111A1</t>
+  </si>
+  <si>
+    <t>0130</t>
+  </si>
+  <si>
+    <t>間隔環組,中_HF4C15-011+012/MCS40-233</t>
+  </si>
+  <si>
+    <t>3214000272C0</t>
+  </si>
+  <si>
+    <t>0360</t>
+  </si>
+  <si>
+    <t>吊桿_MVP-10</t>
+  </si>
+  <si>
+    <t>200006511</t>
+  </si>
+  <si>
+    <t>200006529</t>
+  </si>
+  <si>
+    <t>2051000147A1</t>
+  </si>
+  <si>
+    <t>0070</t>
+  </si>
+  <si>
+    <t>中間軸大齒輪_D186*d62*35H</t>
+  </si>
+  <si>
+    <t>2051000148A1</t>
   </si>
   <si>
     <t>0080</t>
   </si>
   <si>
-    <t>彈簧座_d22*D32*16</t>
+    <t>栓槽轂齒輪_D90*d39*106L</t>
+  </si>
+  <si>
+    <t>3211000085A0</t>
+  </si>
+  <si>
+    <t>0090</t>
+  </si>
+  <si>
+    <t>中間軸_D38*d30*226L</t>
+  </si>
+  <si>
+    <t>200006548</t>
+  </si>
+  <si>
+    <t>200006573</t>
+  </si>
+  <si>
+    <t>3154001348A1</t>
+  </si>
+  <si>
+    <t>主軸前蓋_INC-H-90</t>
+  </si>
+  <si>
+    <t>200006574</t>
+  </si>
+  <si>
+    <t>3211000059B0</t>
+  </si>
+  <si>
+    <t>0050</t>
+  </si>
+  <si>
+    <t>中間軸_PI-1</t>
+  </si>
+  <si>
+    <t>2051000143A0</t>
+  </si>
+  <si>
+    <t>中間軸小齒輪/37T_PI-1</t>
+  </si>
+  <si>
+    <t>2056000065B0</t>
+  </si>
+  <si>
+    <t>中間軸大齒輪/74T_PI-1</t>
+  </si>
+  <si>
+    <t>200006578</t>
+  </si>
+  <si>
+    <t>080100021502</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>3210000386B0</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>傳動軸_d50*D103*774L</t>
+  </si>
+  <si>
+    <t>999800001600</t>
+  </si>
+  <si>
+    <t>0250</t>
+  </si>
+  <si>
+    <t>內藏式主軸轉子組,FANUC_10K807N,021458</t>
   </si>
   <si>
     <t>0100</t>
   </si>
   <si>
-    <t>200006367</t>
-  </si>
-  <si>
-    <t>8423000097A2</t>
-  </si>
-  <si>
-    <t>0420</t>
-  </si>
-  <si>
-    <t>吹氣環_d127xD138x14H</t>
-  </si>
-  <si>
-    <t>0102</t>
-  </si>
-  <si>
-    <t>3154001543B3</t>
-  </si>
-  <si>
-    <t>0440</t>
-  </si>
-  <si>
-    <t>主軸前蓋_d127*D195*33L</t>
-  </si>
-  <si>
-    <t>200006368</t>
-  </si>
-  <si>
-    <t>080100113204</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021305_BT50,CW45</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>0802</t>
-  </si>
-  <si>
-    <t>200006370</t>
-  </si>
-  <si>
-    <t>080100033903</t>
-  </si>
-  <si>
-    <t>G2.5K主軸,010830_BT50,C0DIN</t>
-  </si>
-  <si>
-    <t>1X001</t>
-  </si>
-  <si>
-    <t>虛擬工作中心</t>
-  </si>
-  <si>
-    <t>200006371</t>
-  </si>
-  <si>
-    <t>3154001366C1</t>
-  </si>
-  <si>
-    <t>0290</t>
-  </si>
-  <si>
-    <t>主軸前蓋_246*430*79</t>
-  </si>
-  <si>
-    <t>200006385</t>
-  </si>
-  <si>
-    <t>8310000702A1</t>
-  </si>
-  <si>
-    <t>0170</t>
-  </si>
-  <si>
-    <t>馬達座_G8K-a22</t>
-  </si>
-  <si>
-    <t>0104</t>
-  </si>
-  <si>
-    <t>200006390</t>
-  </si>
-  <si>
-    <t>4023000108B0</t>
+    <t>610400005000</t>
+  </si>
+  <si>
+    <t>0260</t>
+  </si>
+  <si>
+    <t>內藏式主軸轉子加工圖,FANUC_A06B-2726-B651#2231</t>
+  </si>
+  <si>
+    <t>0126</t>
+  </si>
+  <si>
+    <t>610400002700</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>內藏式主軸轉子,FANUC_A06B-2726-B651#2231</t>
+  </si>
+  <si>
+    <t>200006579</t>
+  </si>
+  <si>
+    <t>3227000145A0</t>
+  </si>
+  <si>
+    <t>0500</t>
+  </si>
+  <si>
+    <t>撓性聯軸器,主軸,Mayr_100/953.221/50/50S</t>
+  </si>
+  <si>
+    <t>0120</t>
+  </si>
+  <si>
+    <t>200006580</t>
+  </si>
+  <si>
+    <t>892300066800</t>
+  </si>
+  <si>
+    <t>0480</t>
+  </si>
+  <si>
+    <t>出貨固定板_EA/EAY,HF-A90/AE/M90/MU</t>
+  </si>
+  <si>
+    <t>0107</t>
+  </si>
+  <si>
+    <t>200006624</t>
+  </si>
+  <si>
+    <t>3154001424A1</t>
+  </si>
+  <si>
+    <t>0330</t>
+  </si>
+  <si>
+    <t>主軸前蓋,DDS20K長套筒_d82.5*D148*H27.5</t>
+  </si>
+  <si>
+    <t>8423000091A0</t>
+  </si>
+  <si>
+    <t>吹氣環_d82.5*D91*H9.25</t>
+  </si>
+  <si>
+    <t>200006637</t>
+  </si>
+  <si>
+    <t>3059000318B1</t>
+  </si>
+  <si>
+    <t>0320</t>
+  </si>
+  <si>
+    <t>主軸承箱_直結式,#30,24000RPM</t>
+  </si>
+  <si>
+    <t>200006652</t>
+  </si>
+  <si>
+    <t>0140</t>
+  </si>
+  <si>
+    <t>200006666</t>
+  </si>
+  <si>
+    <t>8814001457A2</t>
+  </si>
+  <si>
+    <t>0040</t>
+  </si>
+  <si>
+    <t>機頭加工圖,#40D長套筒_S-Plus 8</t>
+  </si>
+  <si>
+    <t>200006668</t>
+  </si>
+  <si>
+    <t>3215000603A1</t>
+  </si>
+  <si>
+    <t>打刀筒,CTS_LG-800</t>
+  </si>
+  <si>
+    <t>200006669</t>
+  </si>
+  <si>
+    <t>200006670</t>
+  </si>
+  <si>
+    <t>8015002766B0</t>
+  </si>
+  <si>
+    <t>增壓缸底座_MVP-13P</t>
+  </si>
+  <si>
+    <t>200006671</t>
+  </si>
+  <si>
+    <t>8814001455A2</t>
+  </si>
+  <si>
+    <t>機頭加工圖,#40P短套筒_MVP-11</t>
+  </si>
+  <si>
+    <t>200006674</t>
+  </si>
+  <si>
+    <t>0190</t>
+  </si>
+  <si>
+    <t>200006675</t>
+  </si>
+  <si>
+    <t>200006676</t>
+  </si>
+  <si>
+    <t>080100045203</t>
+  </si>
+  <si>
+    <t>0030</t>
+  </si>
+  <si>
+    <t>D12K 主軸,021274_BBT50,M50,C045</t>
+  </si>
+  <si>
+    <t>8311000404A0</t>
+  </si>
+  <si>
+    <t>前油箱蓋板_270x200*15</t>
+  </si>
+  <si>
+    <t>3227000101A0</t>
+  </si>
+  <si>
+    <t>撓性聯軸器,主軸,GS-P42_98ShA-GS,6.0-d48,6.0-d50</t>
+  </si>
+  <si>
+    <t>200006686</t>
+  </si>
+  <si>
+    <t>305000005200</t>
+  </si>
+  <si>
+    <t>陶珠軸承_GMN-HYKH6012 2RZCTAP4UL</t>
+  </si>
+  <si>
+    <t>0128</t>
+  </si>
+  <si>
+    <t>305000005300</t>
+  </si>
+  <si>
+    <t>陶珠軸承_GMN-HYKH6013 2RZCTAP4UL</t>
   </si>
   <si>
     <t>0370</t>
   </si>
   <si>
-    <t>打刀油缸_83-62-12</t>
-  </si>
-  <si>
-    <t>200006423</t>
-  </si>
-  <si>
-    <t>0360</t>
-  </si>
-  <si>
-    <t>0380</t>
-  </si>
-  <si>
-    <t>200006431</t>
-  </si>
-  <si>
-    <t>200006432</t>
-  </si>
-  <si>
-    <t>080100120402</t>
-  </si>
-  <si>
-    <t>0050</t>
-  </si>
-  <si>
-    <t>G8K 主軸,021387_BT50,0W45</t>
-  </si>
-  <si>
-    <t>200006433</t>
-  </si>
-  <si>
-    <t>200006452</t>
-  </si>
-  <si>
-    <t>080100023404</t>
-  </si>
-  <si>
-    <t>0040</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BT50,C0DIN</t>
-  </si>
-  <si>
-    <t>200006454</t>
-  </si>
-  <si>
-    <t>8814001415C0</t>
-  </si>
-  <si>
-    <t>0240</t>
-  </si>
-  <si>
-    <t>機頭加工圖,#50G6K_HCMC-1100</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>200006456</t>
-  </si>
-  <si>
-    <t>8814001018A1</t>
-  </si>
-  <si>
-    <t>0270</t>
-  </si>
-  <si>
-    <t>機頭滑座加工圖_PI-1,Z780</t>
-  </si>
-  <si>
-    <t>200006460</t>
-  </si>
-  <si>
-    <t>200006471</t>
-  </si>
-  <si>
-    <t>8342000234A0</t>
-  </si>
-  <si>
-    <t>0190</t>
-  </si>
-  <si>
-    <t>吊桿螺帽_M16*25*8</t>
-  </si>
-  <si>
-    <t>3214000289B0</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>吊桿,DDS20K_MVP-8</t>
-  </si>
-  <si>
-    <t>3154001577B0</t>
-  </si>
-  <si>
-    <t>0430</t>
-  </si>
-  <si>
-    <t>主軸前蓋_d82.5*D148*H28</t>
-  </si>
-  <si>
-    <t>200006475</t>
-  </si>
-  <si>
-    <t>080100050201</t>
-  </si>
-  <si>
-    <t>0030</t>
-  </si>
-  <si>
-    <t>D20K 主軸,010683_A63,M50,C0</t>
-  </si>
-  <si>
-    <t>8310000667A1</t>
-  </si>
-  <si>
-    <t>馬達固定座_HSA2215/20KRPM</t>
-  </si>
-  <si>
-    <t>200006476</t>
-  </si>
-  <si>
-    <t>200006486</t>
-  </si>
-  <si>
-    <t>200006487</t>
-  </si>
-  <si>
-    <t>200006488</t>
-  </si>
-  <si>
-    <t>3241000017A1</t>
-  </si>
-  <si>
-    <t>直齒離合器,C軸2.5度_D330*d280*H40,144T</t>
-  </si>
-  <si>
-    <t>9816</t>
-  </si>
-  <si>
-    <t>8319000682A0</t>
-  </si>
-  <si>
-    <t>金屬墊片,A軸軸承箱用_d142*D186*4t</t>
-  </si>
-  <si>
-    <t>892300066700</t>
-  </si>
-  <si>
-    <t>0610</t>
-  </si>
-  <si>
-    <t>出貨固定板_EA/EAY,HF-AU</t>
-  </si>
-  <si>
-    <t>0107</t>
-  </si>
-  <si>
-    <t>200006495</t>
-  </si>
-  <si>
-    <t>200006496</t>
-  </si>
-  <si>
-    <t>111400007900</t>
-  </si>
-  <si>
-    <t>0180</t>
-  </si>
-  <si>
-    <t>盤型彈簧/左旋_40-20-1</t>
-  </si>
-  <si>
-    <t>0120</t>
-  </si>
-  <si>
-    <t>200006501</t>
-  </si>
-  <si>
-    <t>881400142300</t>
-  </si>
-  <si>
-    <t>機頭加工圖,HSKA63D長套筒_MVP-13</t>
-  </si>
-  <si>
-    <t>3227000055C0</t>
-  </si>
-  <si>
-    <t>0090</t>
-  </si>
-  <si>
-    <t>撓性聯軸器,ROTEX_98ShA-GS6.0-d38,6.0P-d50</t>
-  </si>
-  <si>
-    <t>200006502</t>
-  </si>
-  <si>
-    <t>305000004501</t>
-  </si>
-  <si>
-    <t>陶珠軸承_FAG-HC7013E.T.P4S.UL,2個1組</t>
-  </si>
-  <si>
-    <t>0128</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>5063000120A0</t>
-  </si>
-  <si>
-    <t>0220</t>
-  </si>
-  <si>
-    <t>油壓缸外蓋,DDS20K_MVP-8(D100*d70*H64)</t>
-  </si>
-  <si>
-    <t>5063000163B0</t>
-  </si>
-  <si>
-    <t>油壓缸底蓋_MVP-10</t>
-  </si>
-  <si>
-    <t>200006526</t>
-  </si>
-  <si>
-    <t>305000005200</t>
-  </si>
-  <si>
-    <t>陶珠軸承_GMN-HYKH6012 2RZCTAP4UL</t>
-  </si>
-  <si>
-    <t>305000005300</t>
-  </si>
-  <si>
-    <t>0020</t>
-  </si>
-  <si>
-    <t>陶珠軸承_GMN-HYKH6013 2RZCTAP4UL</t>
-  </si>
-  <si>
-    <t>8420002211A0</t>
-  </si>
-  <si>
-    <t>0230</t>
-  </si>
-  <si>
-    <t>上間隔環組,DDS20K_d60*D95*14</t>
-  </si>
-  <si>
-    <t>5063000119A0</t>
-  </si>
-  <si>
-    <t>0260</t>
-  </si>
-  <si>
-    <t>油壓缸底蓋,DDS20K_MVP-8(d70)</t>
-  </si>
-  <si>
-    <t>8921000806A1</t>
-  </si>
-  <si>
-    <t>0410</t>
-  </si>
-  <si>
-    <t>感應器支撐架_MVP-8</t>
-  </si>
-  <si>
-    <t>200006527</t>
-  </si>
-  <si>
-    <t>111400008100</t>
-  </si>
-  <si>
-    <t>0150</t>
-  </si>
-  <si>
-    <t>盤型彈簧_φ34*φ16.6*2t</t>
-  </si>
-  <si>
-    <t>8420002213A2</t>
-  </si>
-  <si>
-    <t>0320</t>
-  </si>
-  <si>
-    <t>間隔環,DDS20K_d60*D75*143</t>
-  </si>
-  <si>
-    <t>8420002463A1</t>
-  </si>
-  <si>
-    <t>套環_d64*D97*7.5,MVP</t>
-  </si>
-  <si>
-    <t>200006528</t>
-  </si>
-  <si>
-    <t>312800005100</t>
-  </si>
-  <si>
-    <t>油封_RS1300700-T46NA B+S K型特康</t>
-  </si>
-  <si>
-    <t>312800005600</t>
-  </si>
-  <si>
-    <t>油封_PQ1401000-T46 B+S AQ-type</t>
-  </si>
-  <si>
-    <t>200006530</t>
-  </si>
-  <si>
-    <t>303500039801</t>
-  </si>
-  <si>
-    <t>單列斜角滾珠軸承_FAG-HS7018C.T.P4S.UL,2個1組</t>
-  </si>
-  <si>
-    <t>8010000388A0</t>
-  </si>
-  <si>
-    <t>感應塊_70-965</t>
-  </si>
-  <si>
-    <t>3059000331A1</t>
-  </si>
-  <si>
-    <t>0390</t>
-  </si>
-  <si>
-    <t>主軸承箱_HCMC-1682,#50,G8K</t>
-  </si>
-  <si>
-    <t>630000333</t>
-  </si>
-  <si>
-    <t>080200555000</t>
-  </si>
-  <si>
-    <t>0070</t>
-  </si>
-  <si>
-    <t>MVP-8機頭D15K,021581_#40,38F18,C,AT8</t>
-  </si>
-  <si>
-    <t>630000338</t>
-  </si>
-  <si>
-    <t>080100084704</t>
-  </si>
-  <si>
-    <t>D15K 主軸,010017_BT40,M60,CWDIN</t>
+    <t>630000348</t>
+  </si>
+  <si>
+    <t>080200572300</t>
+  </si>
+  <si>
+    <t>SMC-5機頭D24K,031793_#40,22F15,C</t>
+  </si>
+  <si>
+    <t>630000351</t>
+  </si>
+  <si>
+    <t>080100076403</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021444_BT40,8YU,CW45</t>
+  </si>
+  <si>
+    <t>630000352</t>
+  </si>
+  <si>
+    <t>080100059604</t>
+  </si>
+  <si>
+    <t>P12K 主軸,021361_BT40,5GT,0W45</t>
+  </si>
+  <si>
+    <t>630000354</t>
+  </si>
+  <si>
+    <t>3227000130A0</t>
+  </si>
+  <si>
+    <t>撓性聯軸器,主軸,GS42P_98ShA,6.0-d48,6.0-d55</t>
+  </si>
+  <si>
+    <t>1092001297A0</t>
+  </si>
+  <si>
+    <t>平行鍵/雙圓頭_16*6*90L</t>
+  </si>
+  <si>
+    <t>3227000129A0</t>
+  </si>
+  <si>
+    <t>撓性聯軸器,主軸,GS42P_98ShA,6.0-d48,6.0-d48</t>
+  </si>
+  <si>
+    <t>1092001294A0</t>
+  </si>
+  <si>
+    <t>平行鍵/雙圓頭_14*5.5*80L</t>
   </si>
   <si>
     <t>訂單</t>
@@ -694,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y82"/>
+  <dimension ref="A1:Y54"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -706,7 +703,7 @@
     <col min="7" max="7" bestFit="1" width="10" customWidth="1"/>
     <col min="8" max="8" bestFit="1" width="10" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="12" customWidth="1"/>
-    <col min="10" max="10" bestFit="1" width="38" customWidth="1"/>
+    <col min="10" max="10" bestFit="1" width="42" customWidth="1"/>
     <col min="11" max="11" bestFit="1" width="4" customWidth="1"/>
     <col min="12" max="12" bestFit="1" width="6" customWidth="1"/>
     <col min="13" max="13" bestFit="1" width="6" customWidth="1"/>
@@ -715,7 +712,7 @@
     <col min="16" max="16" bestFit="1" width="7" customWidth="1"/>
     <col min="17" max="17" bestFit="1" width="8" customWidth="1"/>
     <col min="18" max="18" bestFit="1" width="6" customWidth="1"/>
-    <col min="19" max="19" bestFit="1" width="11" customWidth="1"/>
+    <col min="19" max="19" bestFit="1" width="10" customWidth="1"/>
     <col min="20" max="20" bestFit="1" width="6" customWidth="1"/>
     <col min="21" max="21" bestFit="1" width="6" customWidth="1"/>
     <col min="22" max="22" bestFit="1" width="6" customWidth="1"/>
@@ -726,79 +723,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -815,7 +812,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="2">
-        <v>46091</v>
+        <v>46121</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -880,34 +877,34 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2">
-        <v>46091</v>
+        <v>46142</v>
       </c>
       <c r="F3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="s">
         <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
         <v>6</v>
@@ -922,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P3" t="s">
         <v>10</v>
@@ -934,13 +931,13 @@
         <v>1</v>
       </c>
       <c r="S3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="s">
         <v>12</v>
       </c>
       <c r="U3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V3" t="s">
         <v>1</v>
@@ -957,19 +954,19 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2">
-        <v>46086</v>
+        <v>46125</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
@@ -984,7 +981,7 @@
         <v>4</v>
       </c>
       <c r="J4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K4" t="s">
         <v>6</v>
@@ -999,13 +996,13 @@
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R4" t="s">
         <v>1</v>
@@ -1017,7 +1014,7 @@
         <v>12</v>
       </c>
       <c r="U4" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V4" t="s">
         <v>1</v>
@@ -1034,55 +1031,55 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46125</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2">
-        <v>46086</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="P5" t="s">
         <v>26</v>
       </c>
-      <c r="K5" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M5" t="s">
-        <v>8</v>
-      </c>
-      <c r="N5" t="s">
-        <v>1</v>
-      </c>
-      <c r="O5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" t="s">
-        <v>10</v>
-      </c>
       <c r="Q5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R5" t="s">
         <v>1</v>
@@ -1094,7 +1091,7 @@
         <v>12</v>
       </c>
       <c r="U5" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V5" t="s">
         <v>1</v>
@@ -1111,67 +1108,67 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46125</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="R6" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="3">
+        <v>1</v>
+      </c>
+      <c r="T6" t="s">
+        <v>12</v>
+      </c>
+      <c r="U6" t="s">
         <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2">
-        <v>46101</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" t="s">
-        <v>6</v>
-      </c>
-      <c r="L6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>11</v>
-      </c>
-      <c r="R6" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="3">
-        <v>1</v>
-      </c>
-      <c r="T6" t="s">
-        <v>12</v>
-      </c>
-      <c r="U6" t="s">
-        <v>31</v>
       </c>
       <c r="V6" t="s">
         <v>1</v>
@@ -1188,19 +1185,19 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2">
-        <v>46064</v>
+        <v>46125</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1215,7 +1212,7 @@
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K7" t="s">
         <v>6</v>
@@ -1230,13 +1227,13 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="P7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="R7" t="s">
         <v>1</v>
@@ -1248,7 +1245,7 @@
         <v>12</v>
       </c>
       <c r="U7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V7" t="s">
         <v>1</v>
@@ -1265,19 +1262,19 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2">
-        <v>46052</v>
+        <v>46125</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -1292,7 +1289,7 @@
         <v>4</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
         <v>6</v>
@@ -1307,13 +1304,13 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q8" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R8" t="s">
         <v>1</v>
@@ -1325,7 +1322,7 @@
         <v>12</v>
       </c>
       <c r="U8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V8" t="s">
         <v>1</v>
@@ -1342,19 +1339,19 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2">
-        <v>46063</v>
+        <v>46094</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -1369,7 +1366,7 @@
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K9" t="s">
         <v>6</v>
@@ -1384,13 +1381,13 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="P9" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R9" t="s">
         <v>1</v>
@@ -1402,7 +1399,7 @@
         <v>12</v>
       </c>
       <c r="U9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V9" t="s">
         <v>1</v>
@@ -1425,13 +1422,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
@@ -1446,7 +1443,7 @@
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K10" t="s">
         <v>6</v>
@@ -1461,13 +1458,13 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P10" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R10" t="s">
         <v>1</v>
@@ -1479,7 +1476,7 @@
         <v>12</v>
       </c>
       <c r="U10" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V10" t="s">
         <v>1</v>
@@ -1496,19 +1493,19 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2">
-        <v>46041</v>
+        <v>46122</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
@@ -1523,7 +1520,7 @@
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="K11" t="s">
         <v>6</v>
@@ -1538,13 +1535,13 @@
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P11" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R11" t="s">
         <v>1</v>
@@ -1556,7 +1553,7 @@
         <v>12</v>
       </c>
       <c r="U11" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V11" t="s">
         <v>1</v>
@@ -1573,19 +1570,19 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
         <v>50</v>
       </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
       <c r="E12" s="2">
-        <v>46041</v>
+        <v>46155</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
@@ -1600,7 +1597,7 @@
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="K12" t="s">
         <v>6</v>
@@ -1615,7 +1612,7 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="P12" t="s">
         <v>10</v>
@@ -1633,7 +1630,7 @@
         <v>12</v>
       </c>
       <c r="U12" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -1650,19 +1647,19 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
         <v>53</v>
       </c>
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
-      </c>
       <c r="E13" s="2">
-        <v>46034</v>
+        <v>46155</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
@@ -1677,7 +1674,7 @@
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="K13" t="s">
         <v>6</v>
@@ -1692,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="O13" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="P13" t="s">
         <v>10</v>
@@ -1710,7 +1707,7 @@
         <v>12</v>
       </c>
       <c r="U13" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V13" t="s">
         <v>1</v>
@@ -1727,19 +1724,19 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E14" s="2">
-        <v>46078</v>
+        <v>46146</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
@@ -1754,7 +1751,7 @@
         <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
         <v>6</v>
@@ -1769,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="O14" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="P14" t="s">
         <v>10</v>
@@ -1787,7 +1784,7 @@
         <v>12</v>
       </c>
       <c r="U14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="V14" t="s">
         <v>1</v>
@@ -1804,19 +1801,19 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
         <v>58</v>
       </c>
-      <c r="B15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
-      </c>
       <c r="E15" s="2">
-        <v>46063</v>
+        <v>46104</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
@@ -1831,7 +1828,7 @@
         <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="K15" t="s">
         <v>6</v>
@@ -1846,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P15" t="s">
         <v>10</v>
@@ -1864,7 +1861,7 @@
         <v>12</v>
       </c>
       <c r="U15" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V15" t="s">
         <v>1</v>
@@ -1881,19 +1878,19 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E16" s="2">
-        <v>46063</v>
+        <v>46104</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
@@ -1908,7 +1905,7 @@
         <v>4</v>
       </c>
       <c r="J16" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="K16" t="s">
         <v>6</v>
@@ -1923,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P16" t="s">
         <v>10</v>
@@ -1941,7 +1938,7 @@
         <v>12</v>
       </c>
       <c r="U16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V16" t="s">
         <v>1</v>
@@ -1958,19 +1955,19 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2">
-        <v>46079</v>
+        <v>46104</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -1985,7 +1982,7 @@
         <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K17" t="s">
         <v>6</v>
@@ -2000,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P17" t="s">
         <v>10</v>
@@ -2018,7 +2015,7 @@
         <v>12</v>
       </c>
       <c r="U17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="V17" t="s">
         <v>1</v>
@@ -2035,19 +2032,19 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="E18" s="2">
-        <v>46065</v>
+        <v>46108</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -2062,7 +2059,7 @@
         <v>4</v>
       </c>
       <c r="J18" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
         <v>6</v>
@@ -2077,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="P18" t="s">
         <v>10</v>
@@ -2095,7 +2092,7 @@
         <v>12</v>
       </c>
       <c r="U18" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V18" t="s">
         <v>1</v>
@@ -2112,19 +2109,19 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
         <v>68</v>
       </c>
-      <c r="B19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
@@ -2139,7 +2136,7 @@
         <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K19" t="s">
         <v>6</v>
@@ -2154,25 +2151,25 @@
         <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P19" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R19" t="s">
         <v>1</v>
       </c>
       <c r="S19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="s">
         <v>12</v>
       </c>
       <c r="U19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V19" t="s">
         <v>1</v>
@@ -2189,19 +2186,19 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2">
-        <v>46077</v>
+        <v>46112</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
@@ -2216,7 +2213,7 @@
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K20" t="s">
         <v>6</v>
@@ -2231,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="O20" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="P20" t="s">
         <v>10</v>
@@ -2243,13 +2240,13 @@
         <v>1</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="s">
         <v>12</v>
       </c>
       <c r="U20" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="V20" t="s">
         <v>1</v>
@@ -2266,19 +2263,19 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2">
-        <v>46085</v>
+        <v>46112</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -2293,7 +2290,7 @@
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="K21" t="s">
         <v>6</v>
@@ -2308,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P21" t="s">
         <v>10</v>
@@ -2326,7 +2323,7 @@
         <v>12</v>
       </c>
       <c r="U21" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V21" t="s">
         <v>1</v>
@@ -2343,34 +2340,34 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2">
-        <v>46059</v>
+        <v>46112</v>
       </c>
       <c r="F22" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="s">
         <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s">
         <v>6</v>
@@ -2385,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P22" t="s">
         <v>10</v>
@@ -2397,13 +2394,13 @@
         <v>1</v>
       </c>
       <c r="S22" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T22" t="s">
         <v>12</v>
       </c>
       <c r="U22" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V22" t="s">
         <v>1</v>
@@ -2420,19 +2417,19 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>46059</v>
+        <v>46106</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
@@ -2447,7 +2444,7 @@
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K23" t="s">
         <v>6</v>
@@ -2462,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="P23" t="s">
         <v>10</v>
@@ -2497,19 +2494,19 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2">
-        <v>46059</v>
+        <v>46106</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -2524,7 +2521,7 @@
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K24" t="s">
         <v>6</v>
@@ -2539,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P24" t="s">
         <v>10</v>
@@ -2557,7 +2554,7 @@
         <v>12</v>
       </c>
       <c r="U24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V24" t="s">
         <v>1</v>
@@ -2574,7 +2571,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
@@ -2586,7 +2583,7 @@
         <v>85</v>
       </c>
       <c r="E25" s="2">
-        <v>46050</v>
+        <v>46106</v>
       </c>
       <c r="F25" s="3">
         <v>1</v>
@@ -2616,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="P25" t="s">
         <v>10</v>
@@ -2634,7 +2631,7 @@
         <v>12</v>
       </c>
       <c r="U25" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="V25" t="s">
         <v>1</v>
@@ -2651,19 +2648,19 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="E26" s="2">
-        <v>46050</v>
+        <v>46106</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
@@ -2678,7 +2675,7 @@
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s">
         <v>6</v>
@@ -2693,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="P26" t="s">
         <v>10</v>
@@ -2711,7 +2708,7 @@
         <v>12</v>
       </c>
       <c r="U26" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V26" t="s">
         <v>1</v>
@@ -2728,34 +2725,34 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="E27" s="2">
-        <v>46050</v>
+        <v>46106</v>
       </c>
       <c r="F27" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="3">
         <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="s">
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s">
         <v>6</v>
@@ -2770,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="P27" t="s">
         <v>10</v>
@@ -2782,13 +2779,13 @@
         <v>1</v>
       </c>
       <c r="S27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T27" t="s">
         <v>12</v>
       </c>
       <c r="U27" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V27" t="s">
         <v>1</v>
@@ -2805,19 +2802,19 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="E28" s="2">
-        <v>46050</v>
+        <v>46097</v>
       </c>
       <c r="F28" s="3">
         <v>1</v>
@@ -2832,7 +2829,7 @@
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="K28" t="s">
         <v>6</v>
@@ -2847,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="P28" t="s">
         <v>10</v>
@@ -2859,13 +2856,13 @@
         <v>1</v>
       </c>
       <c r="S28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="s">
         <v>12</v>
       </c>
       <c r="U28" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V28" t="s">
         <v>1</v>
@@ -2882,19 +2879,19 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="E29" s="2">
-        <v>46092</v>
+        <v>46153</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
@@ -2909,7 +2906,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="K29" t="s">
         <v>6</v>
@@ -2924,13 +2921,13 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="P29" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R29" t="s">
         <v>1</v>
@@ -2942,7 +2939,7 @@
         <v>12</v>
       </c>
       <c r="U29" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V29" t="s">
         <v>1</v>
@@ -2959,19 +2956,19 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="E30" s="2">
-        <v>46092</v>
+        <v>46161</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
@@ -2986,7 +2983,7 @@
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="K30" t="s">
         <v>6</v>
@@ -3001,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="P30" t="s">
         <v>10</v>
@@ -3019,7 +3016,7 @@
         <v>12</v>
       </c>
       <c r="U30" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V30" t="s">
         <v>1</v>
@@ -3036,19 +3033,19 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2">
-        <v>46094</v>
+        <v>46161</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -3063,7 +3060,7 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="K31" t="s">
         <v>6</v>
@@ -3078,13 +3075,13 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="P31" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="R31" t="s">
         <v>1</v>
@@ -3096,7 +3093,7 @@
         <v>12</v>
       </c>
       <c r="U31" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="V31" t="s">
         <v>1</v>
@@ -3113,19 +3110,19 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2">
-        <v>46094</v>
+        <v>46136</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -3140,7 +3137,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="K32" t="s">
         <v>6</v>
@@ -3155,25 +3152,25 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="P32" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="R32" t="s">
         <v>1</v>
       </c>
       <c r="S32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="s">
         <v>12</v>
       </c>
       <c r="U32" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="V32" t="s">
         <v>1</v>
@@ -3190,19 +3187,19 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E33" s="2">
-        <v>46094</v>
+        <v>46161</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
@@ -3217,7 +3214,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="K33" t="s">
         <v>6</v>
@@ -3232,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="P33" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="R33" t="s">
         <v>1</v>
@@ -3250,7 +3247,7 @@
         <v>12</v>
       </c>
       <c r="U33" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="V33" t="s">
         <v>1</v>
@@ -3267,19 +3264,19 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="E34" s="2">
-        <v>46092</v>
+        <v>46160</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
@@ -3294,7 +3291,7 @@
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="K34" t="s">
         <v>6</v>
@@ -3309,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P34" t="s">
         <v>10</v>
@@ -3327,7 +3324,7 @@
         <v>12</v>
       </c>
       <c r="U34" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V34" t="s">
         <v>1</v>
@@ -3344,19 +3341,19 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="E35" s="2">
-        <v>46093</v>
+        <v>46162</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
@@ -3371,7 +3368,7 @@
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="K35" t="s">
         <v>6</v>
@@ -3386,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="P35" t="s">
         <v>10</v>
@@ -3404,7 +3401,7 @@
         <v>12</v>
       </c>
       <c r="U35" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V35" t="s">
         <v>1</v>
@@ -3421,19 +3418,19 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E36" s="2">
-        <v>46093</v>
+        <v>46162</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -3448,7 +3445,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="K36" t="s">
         <v>6</v>
@@ -3463,7 +3460,7 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P36" t="s">
         <v>10</v>
@@ -3481,7 +3478,7 @@
         <v>12</v>
       </c>
       <c r="U36" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V36" t="s">
         <v>1</v>
@@ -3498,19 +3495,19 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E37" s="2">
-        <v>46085</v>
+        <v>46153</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -3525,7 +3522,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="K37" t="s">
         <v>6</v>
@@ -3540,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="P37" t="s">
         <v>10</v>
@@ -3558,7 +3555,7 @@
         <v>12</v>
       </c>
       <c r="U37" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V37" t="s">
         <v>1</v>
@@ -3575,19 +3572,19 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="E38" s="2">
-        <v>46085</v>
+        <v>46134</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
@@ -3602,7 +3599,7 @@
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="K38" t="s">
         <v>6</v>
@@ -3617,7 +3614,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="P38" t="s">
         <v>10</v>
@@ -3635,7 +3632,7 @@
         <v>12</v>
       </c>
       <c r="U38" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V38" t="s">
         <v>1</v>
@@ -3652,34 +3649,34 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="E39" s="2">
-        <v>46086</v>
+        <v>46147</v>
       </c>
       <c r="F39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="3">
         <v>0</v>
       </c>
       <c r="H39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" t="s">
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="K39" t="s">
         <v>6</v>
@@ -3694,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="P39" t="s">
         <v>10</v>
@@ -3706,13 +3703,13 @@
         <v>1</v>
       </c>
       <c r="S39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T39" t="s">
         <v>12</v>
       </c>
       <c r="U39" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V39" t="s">
         <v>1</v>
@@ -3729,34 +3726,34 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="E40" s="2">
-        <v>46086</v>
+        <v>46136</v>
       </c>
       <c r="F40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="3">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="s">
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="K40" t="s">
         <v>6</v>
@@ -3771,7 +3768,7 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P40" t="s">
         <v>10</v>
@@ -3783,13 +3780,13 @@
         <v>1</v>
       </c>
       <c r="S40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T40" t="s">
         <v>12</v>
       </c>
       <c r="U40" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V40" t="s">
         <v>1</v>
@@ -3806,19 +3803,19 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E41" s="2">
-        <v>46086</v>
+        <v>46150</v>
       </c>
       <c r="F41" s="3">
         <v>1</v>
@@ -3833,7 +3830,7 @@
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="K41" t="s">
         <v>6</v>
@@ -3848,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="P41" t="s">
         <v>10</v>
@@ -3883,34 +3880,34 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="E42" s="2">
-        <v>46086</v>
+        <v>46150</v>
       </c>
       <c r="F42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="s">
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="K42" t="s">
         <v>6</v>
@@ -3925,7 +3922,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P42" t="s">
         <v>10</v>
@@ -3937,13 +3934,13 @@
         <v>1</v>
       </c>
       <c r="S42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T42" t="s">
         <v>12</v>
       </c>
       <c r="U42" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V42" t="s">
         <v>1</v>
@@ -3960,19 +3957,19 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E43" s="2">
-        <v>46086</v>
+        <v>46150</v>
       </c>
       <c r="F43" s="3">
         <v>1</v>
@@ -3987,7 +3984,7 @@
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="K43" t="s">
         <v>6</v>
@@ -4002,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="P43" t="s">
         <v>10</v>
@@ -4020,7 +4017,7 @@
         <v>12</v>
       </c>
       <c r="U43" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V43" t="s">
         <v>1</v>
@@ -4037,19 +4034,19 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
       </c>
       <c r="E44" s="2">
-        <v>46083</v>
+        <v>46133</v>
       </c>
       <c r="F44" s="3">
         <v>2</v>
@@ -4064,7 +4061,7 @@
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="K44" t="s">
         <v>6</v>
@@ -4079,7 +4076,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="P44" t="s">
         <v>10</v>
@@ -4091,13 +4088,13 @@
         <v>1</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T44" t="s">
         <v>12</v>
       </c>
       <c r="U44" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V44" t="s">
         <v>1</v>
@@ -4114,19 +4111,19 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B45" t="s">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
+        <v>3</v>
       </c>
       <c r="E45" s="2">
-        <v>46083</v>
+        <v>46133</v>
       </c>
       <c r="F45" s="3">
         <v>2</v>
@@ -4141,7 +4138,7 @@
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="K45" t="s">
         <v>6</v>
@@ -4156,7 +4153,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="P45" t="s">
         <v>10</v>
@@ -4168,13 +4165,13 @@
         <v>1</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T45" t="s">
         <v>12</v>
       </c>
       <c r="U45" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V45" t="s">
         <v>1</v>
@@ -4191,34 +4188,34 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E46" s="2">
-        <v>46083</v>
+        <v>46133</v>
       </c>
       <c r="F46" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="3">
         <v>0</v>
       </c>
       <c r="H46" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="s">
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="K46" t="s">
         <v>6</v>
@@ -4233,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="P46" t="s">
         <v>10</v>
@@ -4245,13 +4242,13 @@
         <v>1</v>
       </c>
       <c r="S46" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T46" t="s">
         <v>12</v>
       </c>
       <c r="U46" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V46" t="s">
         <v>1</v>
@@ -4268,19 +4265,19 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="E47" s="2">
-        <v>46083</v>
+        <v>46133</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
@@ -4295,7 +4292,7 @@
         <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="K47" t="s">
         <v>6</v>
@@ -4310,7 +4307,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="P47" t="s">
         <v>10</v>
@@ -4328,7 +4325,7 @@
         <v>12</v>
       </c>
       <c r="U47" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V47" t="s">
         <v>1</v>
@@ -4345,19 +4342,19 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="E48" s="2">
-        <v>46083</v>
+        <v>46121</v>
       </c>
       <c r="F48" s="3">
         <v>1</v>
@@ -4372,7 +4369,7 @@
         <v>4</v>
       </c>
       <c r="J48" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="K48" t="s">
         <v>6</v>
@@ -4387,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="P48" t="s">
         <v>10</v>
@@ -4399,13 +4396,13 @@
         <v>1</v>
       </c>
       <c r="S48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="s">
         <v>12</v>
       </c>
       <c r="U48" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V48" t="s">
         <v>1</v>
@@ -4422,19 +4419,19 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D49" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="E49" s="2">
-        <v>46083</v>
+        <v>46142</v>
       </c>
       <c r="F49" s="3">
         <v>1</v>
@@ -4449,7 +4446,7 @@
         <v>4</v>
       </c>
       <c r="J49" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="K49" t="s">
         <v>6</v>
@@ -4464,7 +4461,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="P49" t="s">
         <v>10</v>
@@ -4476,13 +4473,13 @@
         <v>1</v>
       </c>
       <c r="S49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="s">
         <v>12</v>
       </c>
       <c r="U49" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V49" t="s">
         <v>1</v>
@@ -4499,19 +4496,19 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="B50" t="s">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="E50" s="2">
-        <v>46083</v>
+        <v>46133</v>
       </c>
       <c r="F50" s="3">
         <v>1</v>
@@ -4526,13 +4523,13 @@
         <v>4</v>
       </c>
       <c r="J50" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="K50" t="s">
         <v>6</v>
       </c>
       <c r="L50" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M50" t="s">
         <v>8</v>
@@ -4541,7 +4538,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="P50" t="s">
         <v>10</v>
@@ -4553,13 +4550,13 @@
         <v>1</v>
       </c>
       <c r="S50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="s">
         <v>12</v>
       </c>
       <c r="U50" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V50" t="s">
         <v>1</v>
@@ -4576,19 +4573,19 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="D51" t="s">
-        <v>137</v>
+        <v>7</v>
       </c>
       <c r="E51" s="2">
-        <v>46083</v>
+        <v>46135</v>
       </c>
       <c r="F51" s="3">
         <v>1</v>
@@ -4603,7 +4600,7 @@
         <v>4</v>
       </c>
       <c r="J51" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="K51" t="s">
         <v>6</v>
@@ -4618,7 +4615,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P51" t="s">
         <v>10</v>
@@ -4630,13 +4627,13 @@
         <v>1</v>
       </c>
       <c r="S51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" t="s">
         <v>12</v>
       </c>
       <c r="U51" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V51" t="s">
         <v>1</v>
@@ -4653,34 +4650,34 @@
     </row>
     <row r="52" spans="1:25">
       <c r="A52" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="B52" t="s">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E52" s="2">
-        <v>46083</v>
+        <v>46135</v>
       </c>
       <c r="F52" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" t="s">
         <v>4</v>
       </c>
       <c r="J52" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="K52" t="s">
         <v>6</v>
@@ -4695,7 +4692,7 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="P52" t="s">
         <v>10</v>
@@ -4713,7 +4710,7 @@
         <v>12</v>
       </c>
       <c r="U52" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V52" t="s">
         <v>1</v>
@@ -4730,34 +4727,34 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="B53" t="s">
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="D53" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E53" s="2">
-        <v>46083</v>
+        <v>46135</v>
       </c>
       <c r="F53" s="3">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G53" s="3">
         <v>0</v>
       </c>
       <c r="H53" s="3">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="I53" t="s">
         <v>4</v>
       </c>
       <c r="J53" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="K53" t="s">
         <v>6</v>
@@ -4772,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="P53" t="s">
         <v>10</v>
@@ -4790,7 +4787,7 @@
         <v>12</v>
       </c>
       <c r="U53" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V53" t="s">
         <v>1</v>
@@ -4807,34 +4804,34 @@
     </row>
     <row r="54" spans="1:25">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="B54" t="s">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="D54" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="E54" s="2">
-        <v>46083</v>
+        <v>46135</v>
       </c>
       <c r="F54" s="3">
-        <v>60</v>
+        <v>-1</v>
       </c>
       <c r="G54" s="3">
         <v>0</v>
       </c>
       <c r="H54" s="3">
-        <v>60</v>
+        <v>-1</v>
       </c>
       <c r="I54" t="s">
         <v>4</v>
       </c>
       <c r="J54" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="K54" t="s">
         <v>6</v>
@@ -4849,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="P54" t="s">
         <v>10</v>
@@ -4861,13 +4858,13 @@
         <v>1</v>
       </c>
       <c r="S54" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T54" t="s">
         <v>12</v>
       </c>
       <c r="U54" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V54" t="s">
         <v>1</v>
@@ -4879,2162 +4876,6 @@
         <v>1</v>
       </c>
       <c r="Y54" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25">
-      <c r="A55" t="s">
-        <v>139</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" t="s">
-        <v>74</v>
-      </c>
-      <c r="D55" t="s">
-        <v>118</v>
-      </c>
-      <c r="E55" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F55" s="3">
-        <v>2</v>
-      </c>
-      <c r="G55" s="3">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3">
-        <v>2</v>
-      </c>
-      <c r="I55" t="s">
-        <v>4</v>
-      </c>
-      <c r="J55" t="s">
-        <v>76</v>
-      </c>
-      <c r="K55" t="s">
-        <v>6</v>
-      </c>
-      <c r="L55" t="s">
-        <v>7</v>
-      </c>
-      <c r="M55" t="s">
-        <v>8</v>
-      </c>
-      <c r="N55" t="s">
-        <v>1</v>
-      </c>
-      <c r="O55" t="s">
-        <v>23</v>
-      </c>
-      <c r="P55" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>11</v>
-      </c>
-      <c r="R55" t="s">
-        <v>1</v>
-      </c>
-      <c r="S55" s="3">
-        <v>2</v>
-      </c>
-      <c r="T55" t="s">
-        <v>12</v>
-      </c>
-      <c r="U55" t="s">
-        <v>13</v>
-      </c>
-      <c r="V55" t="s">
-        <v>1</v>
-      </c>
-      <c r="W55" t="s">
-        <v>1</v>
-      </c>
-      <c r="X55" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:25">
-      <c r="A56" t="s">
-        <v>139</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>130</v>
-      </c>
-      <c r="D56" t="s">
-        <v>131</v>
-      </c>
-      <c r="E56" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F56" s="3">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3">
-        <v>0</v>
-      </c>
-      <c r="H56" s="3">
-        <v>1</v>
-      </c>
-      <c r="I56" t="s">
-        <v>4</v>
-      </c>
-      <c r="J56" t="s">
-        <v>132</v>
-      </c>
-      <c r="K56" t="s">
-        <v>6</v>
-      </c>
-      <c r="L56" t="s">
-        <v>7</v>
-      </c>
-      <c r="M56" t="s">
-        <v>8</v>
-      </c>
-      <c r="N56" t="s">
-        <v>1</v>
-      </c>
-      <c r="O56" t="s">
-        <v>23</v>
-      </c>
-      <c r="P56" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>11</v>
-      </c>
-      <c r="R56" t="s">
-        <v>1</v>
-      </c>
-      <c r="S56" s="3">
-        <v>1</v>
-      </c>
-      <c r="T56" t="s">
-        <v>12</v>
-      </c>
-      <c r="U56" t="s">
-        <v>13</v>
-      </c>
-      <c r="V56" t="s">
-        <v>1</v>
-      </c>
-      <c r="W56" t="s">
-        <v>1</v>
-      </c>
-      <c r="X56" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25">
-      <c r="A57" t="s">
-        <v>139</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" t="s">
-        <v>65</v>
-      </c>
-      <c r="E57" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1</v>
-      </c>
-      <c r="I57" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" t="s">
-        <v>79</v>
-      </c>
-      <c r="K57" t="s">
-        <v>6</v>
-      </c>
-      <c r="L57" t="s">
-        <v>7</v>
-      </c>
-      <c r="M57" t="s">
-        <v>8</v>
-      </c>
-      <c r="N57" t="s">
-        <v>1</v>
-      </c>
-      <c r="O57" t="s">
-        <v>23</v>
-      </c>
-      <c r="P57" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>11</v>
-      </c>
-      <c r="R57" t="s">
-        <v>1</v>
-      </c>
-      <c r="S57" s="3">
-        <v>1</v>
-      </c>
-      <c r="T57" t="s">
-        <v>12</v>
-      </c>
-      <c r="U57" t="s">
-        <v>13</v>
-      </c>
-      <c r="V57" t="s">
-        <v>1</v>
-      </c>
-      <c r="W57" t="s">
-        <v>1</v>
-      </c>
-      <c r="X57" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25">
-      <c r="A58" t="s">
-        <v>139</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" t="s">
-        <v>133</v>
-      </c>
-      <c r="D58" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1</v>
-      </c>
-      <c r="I58" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" t="s">
-        <v>135</v>
-      </c>
-      <c r="K58" t="s">
-        <v>6</v>
-      </c>
-      <c r="L58" t="s">
-        <v>7</v>
-      </c>
-      <c r="M58" t="s">
-        <v>8</v>
-      </c>
-      <c r="N58" t="s">
-        <v>1</v>
-      </c>
-      <c r="O58" t="s">
-        <v>23</v>
-      </c>
-      <c r="P58" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>11</v>
-      </c>
-      <c r="R58" t="s">
-        <v>1</v>
-      </c>
-      <c r="S58" s="3">
-        <v>1</v>
-      </c>
-      <c r="T58" t="s">
-        <v>12</v>
-      </c>
-      <c r="U58" t="s">
-        <v>13</v>
-      </c>
-      <c r="V58" t="s">
-        <v>1</v>
-      </c>
-      <c r="W58" t="s">
-        <v>1</v>
-      </c>
-      <c r="X58" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25">
-      <c r="A59" t="s">
-        <v>139</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>119</v>
-      </c>
-      <c r="D59" t="s">
-        <v>70</v>
-      </c>
-      <c r="E59" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1</v>
-      </c>
-      <c r="I59" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" t="s">
-        <v>121</v>
-      </c>
-      <c r="K59" t="s">
-        <v>6</v>
-      </c>
-      <c r="L59" t="s">
-        <v>7</v>
-      </c>
-      <c r="M59" t="s">
-        <v>8</v>
-      </c>
-      <c r="N59" t="s">
-        <v>1</v>
-      </c>
-      <c r="O59" t="s">
-        <v>23</v>
-      </c>
-      <c r="P59" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>11</v>
-      </c>
-      <c r="R59" t="s">
-        <v>1</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1</v>
-      </c>
-      <c r="T59" t="s">
-        <v>12</v>
-      </c>
-      <c r="U59" t="s">
-        <v>13</v>
-      </c>
-      <c r="V59" t="s">
-        <v>1</v>
-      </c>
-      <c r="W59" t="s">
-        <v>1</v>
-      </c>
-      <c r="X59" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25">
-      <c r="A60" t="s">
-        <v>139</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" t="s">
-        <v>143</v>
-      </c>
-      <c r="D60" t="s">
-        <v>144</v>
-      </c>
-      <c r="E60" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1</v>
-      </c>
-      <c r="I60" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" t="s">
-        <v>145</v>
-      </c>
-      <c r="K60" t="s">
-        <v>6</v>
-      </c>
-      <c r="L60" t="s">
-        <v>7</v>
-      </c>
-      <c r="M60" t="s">
-        <v>8</v>
-      </c>
-      <c r="N60" t="s">
-        <v>1</v>
-      </c>
-      <c r="O60" t="s">
-        <v>23</v>
-      </c>
-      <c r="P60" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>11</v>
-      </c>
-      <c r="R60" t="s">
-        <v>1</v>
-      </c>
-      <c r="S60" s="3">
-        <v>1</v>
-      </c>
-      <c r="T60" t="s">
-        <v>12</v>
-      </c>
-      <c r="U60" t="s">
-        <v>13</v>
-      </c>
-      <c r="V60" t="s">
-        <v>1</v>
-      </c>
-      <c r="W60" t="s">
-        <v>1</v>
-      </c>
-      <c r="X60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y60" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25">
-      <c r="A61" t="s">
-        <v>139</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" t="s">
-        <v>146</v>
-      </c>
-      <c r="D61" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1</v>
-      </c>
-      <c r="I61" t="s">
-        <v>4</v>
-      </c>
-      <c r="J61" t="s">
-        <v>147</v>
-      </c>
-      <c r="K61" t="s">
-        <v>6</v>
-      </c>
-      <c r="L61" t="s">
-        <v>7</v>
-      </c>
-      <c r="M61" t="s">
-        <v>8</v>
-      </c>
-      <c r="N61" t="s">
-        <v>1</v>
-      </c>
-      <c r="O61" t="s">
-        <v>23</v>
-      </c>
-      <c r="P61" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>11</v>
-      </c>
-      <c r="R61" t="s">
-        <v>1</v>
-      </c>
-      <c r="S61" s="3">
-        <v>1</v>
-      </c>
-      <c r="T61" t="s">
-        <v>12</v>
-      </c>
-      <c r="U61" t="s">
-        <v>13</v>
-      </c>
-      <c r="V61" t="s">
-        <v>1</v>
-      </c>
-      <c r="W61" t="s">
-        <v>1</v>
-      </c>
-      <c r="X61" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y61" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25">
-      <c r="A62" t="s">
-        <v>139</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1</v>
-      </c>
-      <c r="C62" t="s">
-        <v>136</v>
-      </c>
-      <c r="D62" t="s">
-        <v>137</v>
-      </c>
-      <c r="E62" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1</v>
-      </c>
-      <c r="I62" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" t="s">
-        <v>138</v>
-      </c>
-      <c r="K62" t="s">
-        <v>6</v>
-      </c>
-      <c r="L62" t="s">
-        <v>7</v>
-      </c>
-      <c r="M62" t="s">
-        <v>8</v>
-      </c>
-      <c r="N62" t="s">
-        <v>1</v>
-      </c>
-      <c r="O62" t="s">
-        <v>101</v>
-      </c>
-      <c r="P62" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>11</v>
-      </c>
-      <c r="R62" t="s">
-        <v>1</v>
-      </c>
-      <c r="S62" s="3">
-        <v>1</v>
-      </c>
-      <c r="T62" t="s">
-        <v>12</v>
-      </c>
-      <c r="U62" t="s">
-        <v>13</v>
-      </c>
-      <c r="V62" t="s">
-        <v>1</v>
-      </c>
-      <c r="W62" t="s">
-        <v>1</v>
-      </c>
-      <c r="X62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y62" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:25">
-      <c r="A63" t="s">
-        <v>148</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F63" s="3">
-        <v>2</v>
-      </c>
-      <c r="G63" s="3">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3">
-        <v>2</v>
-      </c>
-      <c r="I63" t="s">
-        <v>4</v>
-      </c>
-      <c r="J63" t="s">
-        <v>126</v>
-      </c>
-      <c r="K63" t="s">
-        <v>6</v>
-      </c>
-      <c r="L63" t="s">
-        <v>7</v>
-      </c>
-      <c r="M63" t="s">
-        <v>8</v>
-      </c>
-      <c r="N63" t="s">
-        <v>1</v>
-      </c>
-      <c r="O63" t="s">
-        <v>117</v>
-      </c>
-      <c r="P63" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>11</v>
-      </c>
-      <c r="R63" t="s">
-        <v>1</v>
-      </c>
-      <c r="S63" s="3">
-        <v>0</v>
-      </c>
-      <c r="T63" t="s">
-        <v>12</v>
-      </c>
-      <c r="U63" t="s">
-        <v>13</v>
-      </c>
-      <c r="V63" t="s">
-        <v>1</v>
-      </c>
-      <c r="W63" t="s">
-        <v>1</v>
-      </c>
-      <c r="X63" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y63" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25">
-      <c r="A64" t="s">
-        <v>148</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" t="s">
-        <v>127</v>
-      </c>
-      <c r="D64" t="s">
-        <v>128</v>
-      </c>
-      <c r="E64" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F64" s="3">
-        <v>2</v>
-      </c>
-      <c r="G64" s="3">
-        <v>0</v>
-      </c>
-      <c r="H64" s="3">
-        <v>2</v>
-      </c>
-      <c r="I64" t="s">
-        <v>4</v>
-      </c>
-      <c r="J64" t="s">
-        <v>129</v>
-      </c>
-      <c r="K64" t="s">
-        <v>6</v>
-      </c>
-      <c r="L64" t="s">
-        <v>7</v>
-      </c>
-      <c r="M64" t="s">
-        <v>8</v>
-      </c>
-      <c r="N64" t="s">
-        <v>1</v>
-      </c>
-      <c r="O64" t="s">
-        <v>117</v>
-      </c>
-      <c r="P64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>11</v>
-      </c>
-      <c r="R64" t="s">
-        <v>1</v>
-      </c>
-      <c r="S64" s="3">
-        <v>0</v>
-      </c>
-      <c r="T64" t="s">
-        <v>12</v>
-      </c>
-      <c r="U64" t="s">
-        <v>13</v>
-      </c>
-      <c r="V64" t="s">
-        <v>1</v>
-      </c>
-      <c r="W64" t="s">
-        <v>1</v>
-      </c>
-      <c r="X64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25">
-      <c r="A65" t="s">
-        <v>148</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" t="s">
-        <v>140</v>
-      </c>
-      <c r="D65" t="s">
-        <v>141</v>
-      </c>
-      <c r="E65" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F65" s="3">
-        <v>60</v>
-      </c>
-      <c r="G65" s="3">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3">
-        <v>60</v>
-      </c>
-      <c r="I65" t="s">
-        <v>4</v>
-      </c>
-      <c r="J65" t="s">
-        <v>142</v>
-      </c>
-      <c r="K65" t="s">
-        <v>6</v>
-      </c>
-      <c r="L65" t="s">
-        <v>7</v>
-      </c>
-      <c r="M65" t="s">
-        <v>8</v>
-      </c>
-      <c r="N65" t="s">
-        <v>1</v>
-      </c>
-      <c r="O65" t="s">
-        <v>107</v>
-      </c>
-      <c r="P65" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>11</v>
-      </c>
-      <c r="R65" t="s">
-        <v>1</v>
-      </c>
-      <c r="S65" s="3">
-        <v>60</v>
-      </c>
-      <c r="T65" t="s">
-        <v>12</v>
-      </c>
-      <c r="U65" t="s">
-        <v>13</v>
-      </c>
-      <c r="V65" t="s">
-        <v>1</v>
-      </c>
-      <c r="W65" t="s">
-        <v>1</v>
-      </c>
-      <c r="X65" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25">
-      <c r="A66" t="s">
-        <v>148</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" t="s">
-        <v>149</v>
-      </c>
-      <c r="D66" t="s">
-        <v>43</v>
-      </c>
-      <c r="E66" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1</v>
-      </c>
-      <c r="G66" s="3">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1</v>
-      </c>
-      <c r="I66" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" t="s">
-        <v>150</v>
-      </c>
-      <c r="K66" t="s">
-        <v>6</v>
-      </c>
-      <c r="L66" t="s">
-        <v>7</v>
-      </c>
-      <c r="M66" t="s">
-        <v>8</v>
-      </c>
-      <c r="N66" t="s">
-        <v>1</v>
-      </c>
-      <c r="O66" t="s">
-        <v>107</v>
-      </c>
-      <c r="P66" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>11</v>
-      </c>
-      <c r="R66" t="s">
-        <v>1</v>
-      </c>
-      <c r="S66" s="3">
-        <v>1</v>
-      </c>
-      <c r="T66" t="s">
-        <v>12</v>
-      </c>
-      <c r="U66" t="s">
-        <v>13</v>
-      </c>
-      <c r="V66" t="s">
-        <v>1</v>
-      </c>
-      <c r="W66" t="s">
-        <v>1</v>
-      </c>
-      <c r="X66" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25">
-      <c r="A67" t="s">
-        <v>148</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" t="s">
-        <v>151</v>
-      </c>
-      <c r="D67" t="s">
-        <v>75</v>
-      </c>
-      <c r="E67" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F67" s="3">
-        <v>1</v>
-      </c>
-      <c r="G67" s="3">
-        <v>0</v>
-      </c>
-      <c r="H67" s="3">
-        <v>1</v>
-      </c>
-      <c r="I67" t="s">
-        <v>4</v>
-      </c>
-      <c r="J67" t="s">
-        <v>152</v>
-      </c>
-      <c r="K67" t="s">
-        <v>6</v>
-      </c>
-      <c r="L67" t="s">
-        <v>7</v>
-      </c>
-      <c r="M67" t="s">
-        <v>8</v>
-      </c>
-      <c r="N67" t="s">
-        <v>1</v>
-      </c>
-      <c r="O67" t="s">
-        <v>107</v>
-      </c>
-      <c r="P67" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>11</v>
-      </c>
-      <c r="R67" t="s">
-        <v>1</v>
-      </c>
-      <c r="S67" s="3">
-        <v>1</v>
-      </c>
-      <c r="T67" t="s">
-        <v>12</v>
-      </c>
-      <c r="U67" t="s">
-        <v>13</v>
-      </c>
-      <c r="V67" t="s">
-        <v>1</v>
-      </c>
-      <c r="W67" t="s">
-        <v>1</v>
-      </c>
-      <c r="X67" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25">
-      <c r="A68" t="s">
-        <v>148</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" t="s">
-        <v>74</v>
-      </c>
-      <c r="D68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E68" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F68" s="3">
-        <v>2</v>
-      </c>
-      <c r="G68" s="3">
-        <v>0</v>
-      </c>
-      <c r="H68" s="3">
-        <v>2</v>
-      </c>
-      <c r="I68" t="s">
-        <v>4</v>
-      </c>
-      <c r="J68" t="s">
-        <v>76</v>
-      </c>
-      <c r="K68" t="s">
-        <v>6</v>
-      </c>
-      <c r="L68" t="s">
-        <v>7</v>
-      </c>
-      <c r="M68" t="s">
-        <v>8</v>
-      </c>
-      <c r="N68" t="s">
-        <v>1</v>
-      </c>
-      <c r="O68" t="s">
-        <v>23</v>
-      </c>
-      <c r="P68" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>11</v>
-      </c>
-      <c r="R68" t="s">
-        <v>1</v>
-      </c>
-      <c r="S68" s="3">
-        <v>2</v>
-      </c>
-      <c r="T68" t="s">
-        <v>12</v>
-      </c>
-      <c r="U68" t="s">
-        <v>13</v>
-      </c>
-      <c r="V68" t="s">
-        <v>1</v>
-      </c>
-      <c r="W68" t="s">
-        <v>1</v>
-      </c>
-      <c r="X68" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25">
-      <c r="A69" t="s">
-        <v>148</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" t="s">
-        <v>130</v>
-      </c>
-      <c r="D69" t="s">
-        <v>131</v>
-      </c>
-      <c r="E69" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F69" s="3">
-        <v>1</v>
-      </c>
-      <c r="G69" s="3">
-        <v>0</v>
-      </c>
-      <c r="H69" s="3">
-        <v>1</v>
-      </c>
-      <c r="I69" t="s">
-        <v>4</v>
-      </c>
-      <c r="J69" t="s">
-        <v>132</v>
-      </c>
-      <c r="K69" t="s">
-        <v>6</v>
-      </c>
-      <c r="L69" t="s">
-        <v>7</v>
-      </c>
-      <c r="M69" t="s">
-        <v>8</v>
-      </c>
-      <c r="N69" t="s">
-        <v>1</v>
-      </c>
-      <c r="O69" t="s">
-        <v>23</v>
-      </c>
-      <c r="P69" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>11</v>
-      </c>
-      <c r="R69" t="s">
-        <v>1</v>
-      </c>
-      <c r="S69" s="3">
-        <v>1</v>
-      </c>
-      <c r="T69" t="s">
-        <v>12</v>
-      </c>
-      <c r="U69" t="s">
-        <v>13</v>
-      </c>
-      <c r="V69" t="s">
-        <v>1</v>
-      </c>
-      <c r="W69" t="s">
-        <v>1</v>
-      </c>
-      <c r="X69" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25">
-      <c r="A70" t="s">
-        <v>148</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" t="s">
-        <v>77</v>
-      </c>
-      <c r="D70" t="s">
-        <v>65</v>
-      </c>
-      <c r="E70" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F70" s="3">
-        <v>1</v>
-      </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3">
-        <v>1</v>
-      </c>
-      <c r="I70" t="s">
-        <v>4</v>
-      </c>
-      <c r="J70" t="s">
-        <v>79</v>
-      </c>
-      <c r="K70" t="s">
-        <v>6</v>
-      </c>
-      <c r="L70" t="s">
-        <v>7</v>
-      </c>
-      <c r="M70" t="s">
-        <v>8</v>
-      </c>
-      <c r="N70" t="s">
-        <v>1</v>
-      </c>
-      <c r="O70" t="s">
-        <v>23</v>
-      </c>
-      <c r="P70" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>11</v>
-      </c>
-      <c r="R70" t="s">
-        <v>1</v>
-      </c>
-      <c r="S70" s="3">
-        <v>1</v>
-      </c>
-      <c r="T70" t="s">
-        <v>12</v>
-      </c>
-      <c r="U70" t="s">
-        <v>13</v>
-      </c>
-      <c r="V70" t="s">
-        <v>1</v>
-      </c>
-      <c r="W70" t="s">
-        <v>1</v>
-      </c>
-      <c r="X70" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25">
-      <c r="A71" t="s">
-        <v>148</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" t="s">
-        <v>133</v>
-      </c>
-      <c r="D71" t="s">
-        <v>134</v>
-      </c>
-      <c r="E71" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F71" s="3">
-        <v>1</v>
-      </c>
-      <c r="G71" s="3">
-        <v>0</v>
-      </c>
-      <c r="H71" s="3">
-        <v>1</v>
-      </c>
-      <c r="I71" t="s">
-        <v>4</v>
-      </c>
-      <c r="J71" t="s">
-        <v>135</v>
-      </c>
-      <c r="K71" t="s">
-        <v>6</v>
-      </c>
-      <c r="L71" t="s">
-        <v>7</v>
-      </c>
-      <c r="M71" t="s">
-        <v>8</v>
-      </c>
-      <c r="N71" t="s">
-        <v>1</v>
-      </c>
-      <c r="O71" t="s">
-        <v>23</v>
-      </c>
-      <c r="P71" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>11</v>
-      </c>
-      <c r="R71" t="s">
-        <v>1</v>
-      </c>
-      <c r="S71" s="3">
-        <v>1</v>
-      </c>
-      <c r="T71" t="s">
-        <v>12</v>
-      </c>
-      <c r="U71" t="s">
-        <v>13</v>
-      </c>
-      <c r="V71" t="s">
-        <v>1</v>
-      </c>
-      <c r="W71" t="s">
-        <v>1</v>
-      </c>
-      <c r="X71" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25">
-      <c r="A72" t="s">
-        <v>148</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" t="s">
-        <v>119</v>
-      </c>
-      <c r="D72" t="s">
-        <v>70</v>
-      </c>
-      <c r="E72" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F72" s="3">
-        <v>1</v>
-      </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>1</v>
-      </c>
-      <c r="I72" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" t="s">
-        <v>121</v>
-      </c>
-      <c r="K72" t="s">
-        <v>6</v>
-      </c>
-      <c r="L72" t="s">
-        <v>7</v>
-      </c>
-      <c r="M72" t="s">
-        <v>8</v>
-      </c>
-      <c r="N72" t="s">
-        <v>1</v>
-      </c>
-      <c r="O72" t="s">
-        <v>23</v>
-      </c>
-      <c r="P72" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>11</v>
-      </c>
-      <c r="R72" t="s">
-        <v>1</v>
-      </c>
-      <c r="S72" s="3">
-        <v>1</v>
-      </c>
-      <c r="T72" t="s">
-        <v>12</v>
-      </c>
-      <c r="U72" t="s">
-        <v>13</v>
-      </c>
-      <c r="V72" t="s">
-        <v>1</v>
-      </c>
-      <c r="W72" t="s">
-        <v>1</v>
-      </c>
-      <c r="X72" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y72" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25">
-      <c r="A73" t="s">
-        <v>148</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" t="s">
-        <v>143</v>
-      </c>
-      <c r="D73" t="s">
-        <v>144</v>
-      </c>
-      <c r="E73" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F73" s="3">
-        <v>1</v>
-      </c>
-      <c r="G73" s="3">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3">
-        <v>1</v>
-      </c>
-      <c r="I73" t="s">
-        <v>4</v>
-      </c>
-      <c r="J73" t="s">
-        <v>145</v>
-      </c>
-      <c r="K73" t="s">
-        <v>6</v>
-      </c>
-      <c r="L73" t="s">
-        <v>7</v>
-      </c>
-      <c r="M73" t="s">
-        <v>8</v>
-      </c>
-      <c r="N73" t="s">
-        <v>1</v>
-      </c>
-      <c r="O73" t="s">
-        <v>23</v>
-      </c>
-      <c r="P73" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>11</v>
-      </c>
-      <c r="R73" t="s">
-        <v>1</v>
-      </c>
-      <c r="S73" s="3">
-        <v>1</v>
-      </c>
-      <c r="T73" t="s">
-        <v>12</v>
-      </c>
-      <c r="U73" t="s">
-        <v>13</v>
-      </c>
-      <c r="V73" t="s">
-        <v>1</v>
-      </c>
-      <c r="W73" t="s">
-        <v>1</v>
-      </c>
-      <c r="X73" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y73" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25">
-      <c r="A74" t="s">
-        <v>148</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" t="s">
-        <v>146</v>
-      </c>
-      <c r="D74" t="s">
-        <v>48</v>
-      </c>
-      <c r="E74" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F74" s="3">
-        <v>1</v>
-      </c>
-      <c r="G74" s="3">
-        <v>0</v>
-      </c>
-      <c r="H74" s="3">
-        <v>1</v>
-      </c>
-      <c r="I74" t="s">
-        <v>4</v>
-      </c>
-      <c r="J74" t="s">
-        <v>147</v>
-      </c>
-      <c r="K74" t="s">
-        <v>6</v>
-      </c>
-      <c r="L74" t="s">
-        <v>7</v>
-      </c>
-      <c r="M74" t="s">
-        <v>8</v>
-      </c>
-      <c r="N74" t="s">
-        <v>1</v>
-      </c>
-      <c r="O74" t="s">
-        <v>23</v>
-      </c>
-      <c r="P74" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>11</v>
-      </c>
-      <c r="R74" t="s">
-        <v>1</v>
-      </c>
-      <c r="S74" s="3">
-        <v>1</v>
-      </c>
-      <c r="T74" t="s">
-        <v>12</v>
-      </c>
-      <c r="U74" t="s">
-        <v>13</v>
-      </c>
-      <c r="V74" t="s">
-        <v>1</v>
-      </c>
-      <c r="W74" t="s">
-        <v>1</v>
-      </c>
-      <c r="X74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25">
-      <c r="A75" t="s">
-        <v>148</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1</v>
-      </c>
-      <c r="C75" t="s">
-        <v>136</v>
-      </c>
-      <c r="D75" t="s">
-        <v>137</v>
-      </c>
-      <c r="E75" s="2">
-        <v>46083</v>
-      </c>
-      <c r="F75" s="3">
-        <v>1</v>
-      </c>
-      <c r="G75" s="3">
-        <v>0</v>
-      </c>
-      <c r="H75" s="3">
-        <v>1</v>
-      </c>
-      <c r="I75" t="s">
-        <v>4</v>
-      </c>
-      <c r="J75" t="s">
-        <v>138</v>
-      </c>
-      <c r="K75" t="s">
-        <v>6</v>
-      </c>
-      <c r="L75" t="s">
-        <v>7</v>
-      </c>
-      <c r="M75" t="s">
-        <v>8</v>
-      </c>
-      <c r="N75" t="s">
-        <v>1</v>
-      </c>
-      <c r="O75" t="s">
-        <v>101</v>
-      </c>
-      <c r="P75" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>11</v>
-      </c>
-      <c r="R75" t="s">
-        <v>1</v>
-      </c>
-      <c r="S75" s="3">
-        <v>1</v>
-      </c>
-      <c r="T75" t="s">
-        <v>12</v>
-      </c>
-      <c r="U75" t="s">
-        <v>13</v>
-      </c>
-      <c r="V75" t="s">
-        <v>1</v>
-      </c>
-      <c r="W75" t="s">
-        <v>1</v>
-      </c>
-      <c r="X75" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y75" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25">
-      <c r="A76" t="s">
-        <v>153</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" t="s">
-        <v>154</v>
-      </c>
-      <c r="D76" t="s">
-        <v>128</v>
-      </c>
-      <c r="E76" s="2">
-        <v>46099</v>
-      </c>
-      <c r="F76" s="3">
-        <v>2</v>
-      </c>
-      <c r="G76" s="3">
-        <v>1</v>
-      </c>
-      <c r="H76" s="3">
-        <v>1</v>
-      </c>
-      <c r="I76" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" t="s">
-        <v>155</v>
-      </c>
-      <c r="K76" t="s">
-        <v>6</v>
-      </c>
-      <c r="L76" t="s">
-        <v>7</v>
-      </c>
-      <c r="M76" t="s">
-        <v>8</v>
-      </c>
-      <c r="N76" t="s">
-        <v>1</v>
-      </c>
-      <c r="O76" t="s">
-        <v>117</v>
-      </c>
-      <c r="P76" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>11</v>
-      </c>
-      <c r="R76" t="s">
-        <v>1</v>
-      </c>
-      <c r="S76" s="3">
-        <v>2</v>
-      </c>
-      <c r="T76" t="s">
-        <v>12</v>
-      </c>
-      <c r="U76" t="s">
-        <v>13</v>
-      </c>
-      <c r="V76" t="s">
-        <v>1</v>
-      </c>
-      <c r="W76" t="s">
-        <v>1</v>
-      </c>
-      <c r="X76" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y76" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="1:25">
-      <c r="A77" t="s">
-        <v>153</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1</v>
-      </c>
-      <c r="C77" t="s">
-        <v>156</v>
-      </c>
-      <c r="D77" t="s">
-        <v>107</v>
-      </c>
-      <c r="E77" s="2">
-        <v>46099</v>
-      </c>
-      <c r="F77" s="3">
-        <v>1</v>
-      </c>
-      <c r="G77" s="3">
-        <v>0</v>
-      </c>
-      <c r="H77" s="3">
-        <v>1</v>
-      </c>
-      <c r="I77" t="s">
-        <v>4</v>
-      </c>
-      <c r="J77" t="s">
-        <v>157</v>
-      </c>
-      <c r="K77" t="s">
-        <v>6</v>
-      </c>
-      <c r="L77" t="s">
-        <v>7</v>
-      </c>
-      <c r="M77" t="s">
-        <v>8</v>
-      </c>
-      <c r="N77" t="s">
-        <v>1</v>
-      </c>
-      <c r="O77" t="s">
-        <v>23</v>
-      </c>
-      <c r="P77" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>11</v>
-      </c>
-      <c r="R77" t="s">
-        <v>1</v>
-      </c>
-      <c r="S77" s="3">
-        <v>1</v>
-      </c>
-      <c r="T77" t="s">
-        <v>12</v>
-      </c>
-      <c r="U77" t="s">
-        <v>13</v>
-      </c>
-      <c r="V77" t="s">
-        <v>1</v>
-      </c>
-      <c r="W77" t="s">
-        <v>1</v>
-      </c>
-      <c r="X77" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="78" spans="1:25">
-      <c r="A78" t="s">
-        <v>153</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1</v>
-      </c>
-      <c r="C78" t="s">
-        <v>20</v>
-      </c>
-      <c r="D78" t="s">
-        <v>51</v>
-      </c>
-      <c r="E78" s="2">
-        <v>46099</v>
-      </c>
-      <c r="F78" s="3">
-        <v>1</v>
-      </c>
-      <c r="G78" s="3">
-        <v>0</v>
-      </c>
-      <c r="H78" s="3">
-        <v>1</v>
-      </c>
-      <c r="I78" t="s">
-        <v>4</v>
-      </c>
-      <c r="J78" t="s">
-        <v>22</v>
-      </c>
-      <c r="K78" t="s">
-        <v>6</v>
-      </c>
-      <c r="L78" t="s">
-        <v>7</v>
-      </c>
-      <c r="M78" t="s">
-        <v>8</v>
-      </c>
-      <c r="N78" t="s">
-        <v>1</v>
-      </c>
-      <c r="O78" t="s">
-        <v>23</v>
-      </c>
-      <c r="P78" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>11</v>
-      </c>
-      <c r="R78" t="s">
-        <v>1</v>
-      </c>
-      <c r="S78" s="3">
-        <v>1</v>
-      </c>
-      <c r="T78" t="s">
-        <v>12</v>
-      </c>
-      <c r="U78" t="s">
-        <v>13</v>
-      </c>
-      <c r="V78" t="s">
-        <v>1</v>
-      </c>
-      <c r="W78" t="s">
-        <v>1</v>
-      </c>
-      <c r="X78" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y78" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:25">
-      <c r="A79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1</v>
-      </c>
-      <c r="C79" t="s">
-        <v>24</v>
-      </c>
-      <c r="D79" t="s">
-        <v>52</v>
-      </c>
-      <c r="E79" s="2">
-        <v>46099</v>
-      </c>
-      <c r="F79" s="3">
-        <v>1</v>
-      </c>
-      <c r="G79" s="3">
-        <v>0</v>
-      </c>
-      <c r="H79" s="3">
-        <v>1</v>
-      </c>
-      <c r="I79" t="s">
-        <v>4</v>
-      </c>
-      <c r="J79" t="s">
-        <v>26</v>
-      </c>
-      <c r="K79" t="s">
-        <v>6</v>
-      </c>
-      <c r="L79" t="s">
-        <v>7</v>
-      </c>
-      <c r="M79" t="s">
-        <v>8</v>
-      </c>
-      <c r="N79" t="s">
-        <v>1</v>
-      </c>
-      <c r="O79" t="s">
-        <v>23</v>
-      </c>
-      <c r="P79" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>11</v>
-      </c>
-      <c r="R79" t="s">
-        <v>1</v>
-      </c>
-      <c r="S79" s="3">
-        <v>1</v>
-      </c>
-      <c r="T79" t="s">
-        <v>12</v>
-      </c>
-      <c r="U79" t="s">
-        <v>13</v>
-      </c>
-      <c r="V79" t="s">
-        <v>1</v>
-      </c>
-      <c r="W79" t="s">
-        <v>1</v>
-      </c>
-      <c r="X79" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y79" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25">
-      <c r="A80" t="s">
-        <v>153</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1</v>
-      </c>
-      <c r="C80" t="s">
-        <v>158</v>
-      </c>
-      <c r="D80" t="s">
-        <v>159</v>
-      </c>
-      <c r="E80" s="2">
-        <v>46099</v>
-      </c>
-      <c r="F80" s="3">
-        <v>1</v>
-      </c>
-      <c r="G80" s="3">
-        <v>0</v>
-      </c>
-      <c r="H80" s="3">
-        <v>1</v>
-      </c>
-      <c r="I80" t="s">
-        <v>4</v>
-      </c>
-      <c r="J80" t="s">
-        <v>160</v>
-      </c>
-      <c r="K80" t="s">
-        <v>6</v>
-      </c>
-      <c r="L80" t="s">
-        <v>7</v>
-      </c>
-      <c r="M80" t="s">
-        <v>8</v>
-      </c>
-      <c r="N80" t="s">
-        <v>1</v>
-      </c>
-      <c r="O80" t="s">
-        <v>23</v>
-      </c>
-      <c r="P80" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>11</v>
-      </c>
-      <c r="R80" t="s">
-        <v>1</v>
-      </c>
-      <c r="S80" s="3">
-        <v>1</v>
-      </c>
-      <c r="T80" t="s">
-        <v>12</v>
-      </c>
-      <c r="U80" t="s">
-        <v>13</v>
-      </c>
-      <c r="V80" t="s">
-        <v>1</v>
-      </c>
-      <c r="W80" t="s">
-        <v>1</v>
-      </c>
-      <c r="X80" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y80" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:25">
-      <c r="A81" t="s">
-        <v>161</v>
-      </c>
-      <c r="B81" t="s">
-        <v>1</v>
-      </c>
-      <c r="C81" t="s">
-        <v>162</v>
-      </c>
-      <c r="D81" t="s">
-        <v>163</v>
-      </c>
-      <c r="E81" s="2">
-        <v>46059</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1</v>
-      </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1</v>
-      </c>
-      <c r="I81" t="s">
-        <v>4</v>
-      </c>
-      <c r="J81" t="s">
-        <v>164</v>
-      </c>
-      <c r="K81" t="s">
-        <v>6</v>
-      </c>
-      <c r="L81" t="s">
-        <v>7</v>
-      </c>
-      <c r="M81" t="s">
-        <v>8</v>
-      </c>
-      <c r="N81" t="s">
-        <v>1</v>
-      </c>
-      <c r="O81" t="s">
-        <v>30</v>
-      </c>
-      <c r="P81" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>11</v>
-      </c>
-      <c r="R81" t="s">
-        <v>1</v>
-      </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" t="s">
-        <v>12</v>
-      </c>
-      <c r="U81" t="s">
-        <v>1</v>
-      </c>
-      <c r="V81" t="s">
-        <v>1</v>
-      </c>
-      <c r="W81" t="s">
-        <v>1</v>
-      </c>
-      <c r="X81" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y81" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="82" spans="1:25">
-      <c r="A82" t="s">
-        <v>165</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1</v>
-      </c>
-      <c r="C82" t="s">
-        <v>166</v>
-      </c>
-      <c r="D82" t="s">
-        <v>128</v>
-      </c>
-      <c r="E82" s="2">
-        <v>46064</v>
-      </c>
-      <c r="F82" s="3">
-        <v>1</v>
-      </c>
-      <c r="G82" s="3">
-        <v>0</v>
-      </c>
-      <c r="H82" s="3">
-        <v>1</v>
-      </c>
-      <c r="I82" t="s">
-        <v>4</v>
-      </c>
-      <c r="J82" t="s">
-        <v>167</v>
-      </c>
-      <c r="K82" t="s">
-        <v>6</v>
-      </c>
-      <c r="L82" t="s">
-        <v>7</v>
-      </c>
-      <c r="M82" t="s">
-        <v>8</v>
-      </c>
-      <c r="N82" t="s">
-        <v>1</v>
-      </c>
-      <c r="O82" t="s">
-        <v>30</v>
-      </c>
-      <c r="P82" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>11</v>
-      </c>
-      <c r="R82" t="s">
-        <v>1</v>
-      </c>
-      <c r="S82" s="3">
-        <v>0</v>
-      </c>
-      <c r="T82" t="s">
-        <v>12</v>
-      </c>
-      <c r="U82" t="s">
-        <v>1</v>
-      </c>
-      <c r="V82" t="s">
-        <v>1</v>
-      </c>
-      <c r="W82" t="s">
-        <v>1</v>
-      </c>
-      <c r="X82" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y82" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="178">
   <si>
     <t>200006418</t>
   </si>
@@ -346,18 +346,6 @@
     <t>吹氣環_d82.5*D91*H9.25</t>
   </si>
   <si>
-    <t>200006637</t>
-  </si>
-  <si>
-    <t>3059000318B1</t>
-  </si>
-  <si>
-    <t>0320</t>
-  </si>
-  <si>
-    <t>主軸承箱_直結式,#30,24000RPM</t>
-  </si>
-  <si>
     <t>200006652</t>
   </si>
   <si>
@@ -376,18 +364,6 @@
     <t>機頭加工圖,#40D長套筒_S-Plus 8</t>
   </si>
   <si>
-    <t>200006668</t>
-  </si>
-  <si>
-    <t>3215000603A1</t>
-  </si>
-  <si>
-    <t>打刀筒,CTS_LG-800</t>
-  </si>
-  <si>
-    <t>200006669</t>
-  </si>
-  <si>
     <t>200006670</t>
   </si>
   <si>
@@ -460,15 +436,6 @@
     <t>0370</t>
   </si>
   <si>
-    <t>630000348</t>
-  </si>
-  <si>
-    <t>080200572300</t>
-  </si>
-  <si>
-    <t>SMC-5機頭D24K,031793_#40,22F15,C</t>
-  </si>
-  <si>
     <t>630000351</t>
   </si>
   <si>
@@ -476,15 +443,6 @@
   </si>
   <si>
     <t>P12K 主軸,021444_BT40,8YU,CW45</t>
-  </si>
-  <si>
-    <t>630000352</t>
-  </si>
-  <si>
-    <t>080100059604</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021361_BT40,5GT,0W45</t>
   </si>
   <si>
     <t>630000354</t>
@@ -691,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y54"/>
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -723,79 +681,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="S1" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="T1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="U1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="V1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="W1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -3116,13 +3074,13 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" t="s">
         <v>112</v>
       </c>
-      <c r="D32" t="s">
-        <v>113</v>
-      </c>
       <c r="E32" s="2">
-        <v>46136</v>
+        <v>46161</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -3137,7 +3095,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="K32" t="s">
         <v>6</v>
@@ -3164,13 +3122,13 @@
         <v>1</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="s">
         <v>12</v>
       </c>
       <c r="U32" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="V32" t="s">
         <v>1</v>
@@ -3187,35 +3145,35 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" t="s">
         <v>115</v>
       </c>
-      <c r="B33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33" s="2">
+        <v>46160</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="2">
-        <v>46161</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1</v>
-      </c>
-      <c r="I33" t="s">
-        <v>4</v>
-      </c>
-      <c r="J33" t="s">
-        <v>51</v>
-      </c>
       <c r="K33" t="s">
         <v>6</v>
       </c>
@@ -3229,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="P33" t="s">
         <v>10</v>
@@ -3273,26 +3231,26 @@
         <v>118</v>
       </c>
       <c r="D34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="2">
+        <v>46153</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>4</v>
+      </c>
+      <c r="J34" t="s">
         <v>119</v>
       </c>
-      <c r="E34" s="2">
-        <v>46160</v>
-      </c>
-      <c r="F34" s="3">
-        <v>1</v>
-      </c>
-      <c r="G34" s="3">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3">
-        <v>1</v>
-      </c>
-      <c r="I34" t="s">
-        <v>4</v>
-      </c>
-      <c r="J34" t="s">
-        <v>120</v>
-      </c>
       <c r="K34" t="s">
         <v>6</v>
       </c>
@@ -3306,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P34" t="s">
         <v>10</v>
@@ -3341,35 +3299,35 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
         <v>121</v>
       </c>
-      <c r="B35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="2">
+        <v>46134</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" t="s">
         <v>122</v>
       </c>
-      <c r="D35" t="s">
-        <v>58</v>
-      </c>
-      <c r="E35" s="2">
-        <v>46162</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" t="s">
-        <v>123</v>
-      </c>
       <c r="K35" t="s">
         <v>6</v>
       </c>
@@ -3383,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="P35" t="s">
         <v>10</v>
@@ -3418,19 +3376,19 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" t="s">
         <v>124</v>
       </c>
-      <c r="B36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>122</v>
-      </c>
-      <c r="D36" t="s">
-        <v>58</v>
-      </c>
       <c r="E36" s="2">
-        <v>46162</v>
+        <v>46147</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -3445,7 +3403,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>123</v>
+        <v>51</v>
       </c>
       <c r="K36" t="s">
         <v>6</v>
@@ -3460,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="P36" t="s">
         <v>10</v>
@@ -3501,13 +3459,13 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E37" s="2">
-        <v>46153</v>
+        <v>46136</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -3522,7 +3480,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="K37" t="s">
         <v>6</v>
@@ -3537,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="P37" t="s">
         <v>10</v>
@@ -3572,35 +3530,35 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" t="s">
         <v>128</v>
       </c>
-      <c r="B38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="E38" s="2">
+        <v>46150</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" t="s">
         <v>129</v>
       </c>
-      <c r="D38" t="s">
-        <v>72</v>
-      </c>
-      <c r="E38" s="2">
-        <v>46134</v>
-      </c>
-      <c r="F38" s="3">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3">
-        <v>0</v>
-      </c>
-      <c r="H38" s="3">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>4</v>
-      </c>
-      <c r="J38" t="s">
-        <v>130</v>
-      </c>
       <c r="K38" t="s">
         <v>6</v>
       </c>
@@ -3614,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P38" t="s">
         <v>10</v>
@@ -3632,7 +3590,7 @@
         <v>12</v>
       </c>
       <c r="U38" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V38" t="s">
         <v>1</v>
@@ -3649,35 +3607,35 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="2">
+        <v>46150</v>
+      </c>
+      <c r="F39" s="3">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2</v>
+      </c>
+      <c r="I39" t="s">
+        <v>4</v>
+      </c>
+      <c r="J39" t="s">
         <v>131</v>
       </c>
-      <c r="B39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" t="s">
-        <v>132</v>
-      </c>
-      <c r="E39" s="2">
-        <v>46147</v>
-      </c>
-      <c r="F39" s="3">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3">
-        <v>0</v>
-      </c>
-      <c r="H39" s="3">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>4</v>
-      </c>
-      <c r="J39" t="s">
-        <v>51</v>
-      </c>
       <c r="K39" t="s">
         <v>6</v>
       </c>
@@ -3691,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="P39" t="s">
         <v>10</v>
@@ -3703,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="S39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T39" t="s">
         <v>12</v>
@@ -3726,35 +3684,35 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="2">
+        <v>46150</v>
+      </c>
+      <c r="F40" s="3">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>4</v>
+      </c>
+      <c r="J40" t="s">
         <v>133</v>
       </c>
-      <c r="B40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>129</v>
-      </c>
-      <c r="D40" t="s">
-        <v>72</v>
-      </c>
-      <c r="E40" s="2">
-        <v>46136</v>
-      </c>
-      <c r="F40" s="3">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3">
-        <v>0</v>
-      </c>
-      <c r="H40" s="3">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>4</v>
-      </c>
-      <c r="J40" t="s">
-        <v>130</v>
-      </c>
       <c r="K40" t="s">
         <v>6</v>
       </c>
@@ -3768,7 +3726,7 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="P40" t="s">
         <v>10</v>
@@ -3812,40 +3770,40 @@
         <v>135</v>
       </c>
       <c r="D41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="2">
+        <v>46133</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2</v>
+      </c>
+      <c r="I41" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" t="s">
         <v>136</v>
       </c>
-      <c r="E41" s="2">
-        <v>46150</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
+        <v>6</v>
+      </c>
+      <c r="L41" t="s">
+        <v>7</v>
+      </c>
+      <c r="M41" t="s">
+        <v>8</v>
+      </c>
+      <c r="N41" t="s">
+        <v>1</v>
+      </c>
+      <c r="O41" t="s">
         <v>137</v>
-      </c>
-      <c r="K41" t="s">
-        <v>6</v>
-      </c>
-      <c r="L41" t="s">
-        <v>7</v>
-      </c>
-      <c r="M41" t="s">
-        <v>8</v>
-      </c>
-      <c r="N41" t="s">
-        <v>1</v>
-      </c>
-      <c r="O41" t="s">
-        <v>9</v>
       </c>
       <c r="P41" t="s">
         <v>10</v>
@@ -3857,13 +3815,13 @@
         <v>1</v>
       </c>
       <c r="S41" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T41" t="s">
         <v>12</v>
       </c>
       <c r="U41" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V41" t="s">
         <v>1</v>
@@ -3889,10 +3847,10 @@
         <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E42" s="2">
-        <v>46150</v>
+        <v>46133</v>
       </c>
       <c r="F42" s="3">
         <v>2</v>
@@ -3922,7 +3880,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="P42" t="s">
         <v>10</v>
@@ -3963,13 +3921,13 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="E43" s="2">
-        <v>46150</v>
+        <v>46133</v>
       </c>
       <c r="F43" s="3">
         <v>1</v>
@@ -3984,7 +3942,7 @@
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="K43" t="s">
         <v>6</v>
@@ -3999,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="P43" t="s">
         <v>10</v>
@@ -4034,34 +3992,34 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="D44" t="s">
-        <v>7</v>
+        <v>140</v>
       </c>
       <c r="E44" s="2">
         <v>46133</v>
       </c>
       <c r="F44" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="3">
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="s">
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="K44" t="s">
         <v>6</v>
@@ -4076,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="P44" t="s">
         <v>10</v>
@@ -4088,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="S44" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T44" t="s">
         <v>12</v>
@@ -4111,34 +4069,34 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
         <v>142</v>
       </c>
-      <c r="B45" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" t="s">
-        <v>146</v>
-      </c>
       <c r="D45" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="E45" s="2">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="F45" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" t="s">
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K45" t="s">
         <v>6</v>
@@ -4153,7 +4111,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="P45" t="s">
         <v>10</v>
@@ -4165,13 +4123,13 @@
         <v>1</v>
       </c>
       <c r="S45" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T45" t="s">
         <v>12</v>
       </c>
       <c r="U45" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="V45" t="s">
         <v>1</v>
@@ -4188,19 +4146,19 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="E46" s="2">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="F46" s="3">
         <v>1</v>
@@ -4215,7 +4173,7 @@
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="K46" t="s">
         <v>6</v>
@@ -4230,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="P46" t="s">
         <v>10</v>
@@ -4242,13 +4200,13 @@
         <v>1</v>
       </c>
       <c r="S46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="s">
         <v>12</v>
       </c>
       <c r="U46" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="V46" t="s">
         <v>1</v>
@@ -4265,35 +4223,35 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="D47" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2">
+        <v>46135</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="2">
-        <v>46133</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1</v>
-      </c>
-      <c r="I47" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" t="s">
-        <v>110</v>
-      </c>
       <c r="K47" t="s">
         <v>6</v>
       </c>
@@ -4307,7 +4265,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="P47" t="s">
         <v>10</v>
@@ -4319,13 +4277,13 @@
         <v>1</v>
       </c>
       <c r="S47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="s">
         <v>12</v>
       </c>
       <c r="U47" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="V47" t="s">
         <v>1</v>
@@ -4342,35 +4300,35 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
         <v>149</v>
       </c>
-      <c r="B48" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48" s="2">
+        <v>46135</v>
+      </c>
+      <c r="F48" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" t="s">
         <v>150</v>
       </c>
-      <c r="D48" t="s">
-        <v>119</v>
-      </c>
-      <c r="E48" s="2">
-        <v>46121</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1</v>
-      </c>
-      <c r="I48" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" t="s">
-        <v>151</v>
-      </c>
       <c r="K48" t="s">
         <v>6</v>
       </c>
@@ -4384,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="P48" t="s">
         <v>10</v>
@@ -4419,35 +4377,35 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" t="s">
+        <v>115</v>
+      </c>
+      <c r="E49" s="2">
+        <v>46135</v>
+      </c>
+      <c r="F49" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" t="s">
         <v>152</v>
       </c>
-      <c r="B49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>153</v>
-      </c>
-      <c r="D49" t="s">
-        <v>44</v>
-      </c>
-      <c r="E49" s="2">
-        <v>46142</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" t="s">
-        <v>154</v>
-      </c>
       <c r="K49" t="s">
         <v>6</v>
       </c>
@@ -4461,7 +4419,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P49" t="s">
         <v>10</v>
@@ -4491,391 +4449,6 @@
         <v>1</v>
       </c>
       <c r="Y49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25">
-      <c r="A50" t="s">
-        <v>155</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="2">
-        <v>46133</v>
-      </c>
-      <c r="F50" s="3">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3">
-        <v>0</v>
-      </c>
-      <c r="H50" s="3">
-        <v>1</v>
-      </c>
-      <c r="I50" t="s">
-        <v>4</v>
-      </c>
-      <c r="J50" t="s">
-        <v>157</v>
-      </c>
-      <c r="K50" t="s">
-        <v>6</v>
-      </c>
-      <c r="L50" t="s">
-        <v>3</v>
-      </c>
-      <c r="M50" t="s">
-        <v>8</v>
-      </c>
-      <c r="N50" t="s">
-        <v>1</v>
-      </c>
-      <c r="O50" t="s">
-        <v>9</v>
-      </c>
-      <c r="P50" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>11</v>
-      </c>
-      <c r="R50" t="s">
-        <v>1</v>
-      </c>
-      <c r="S50" s="3">
-        <v>0</v>
-      </c>
-      <c r="T50" t="s">
-        <v>12</v>
-      </c>
-      <c r="U50" t="s">
-        <v>1</v>
-      </c>
-      <c r="V50" t="s">
-        <v>1</v>
-      </c>
-      <c r="W50" t="s">
-        <v>1</v>
-      </c>
-      <c r="X50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25">
-      <c r="A51" t="s">
-        <v>158</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" t="s">
-        <v>159</v>
-      </c>
-      <c r="D51" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="2">
-        <v>46135</v>
-      </c>
-      <c r="F51" s="3">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3">
-        <v>1</v>
-      </c>
-      <c r="I51" t="s">
-        <v>4</v>
-      </c>
-      <c r="J51" t="s">
-        <v>160</v>
-      </c>
-      <c r="K51" t="s">
-        <v>6</v>
-      </c>
-      <c r="L51" t="s">
-        <v>7</v>
-      </c>
-      <c r="M51" t="s">
-        <v>8</v>
-      </c>
-      <c r="N51" t="s">
-        <v>1</v>
-      </c>
-      <c r="O51" t="s">
-        <v>99</v>
-      </c>
-      <c r="P51" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>11</v>
-      </c>
-      <c r="R51" t="s">
-        <v>1</v>
-      </c>
-      <c r="S51" s="3">
-        <v>0</v>
-      </c>
-      <c r="T51" t="s">
-        <v>12</v>
-      </c>
-      <c r="U51" t="s">
-        <v>1</v>
-      </c>
-      <c r="V51" t="s">
-        <v>1</v>
-      </c>
-      <c r="W51" t="s">
-        <v>1</v>
-      </c>
-      <c r="X51" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25">
-      <c r="A52" t="s">
-        <v>158</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" t="s">
-        <v>161</v>
-      </c>
-      <c r="D52" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="2">
-        <v>46135</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1</v>
-      </c>
-      <c r="I52" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" t="s">
-        <v>162</v>
-      </c>
-      <c r="K52" t="s">
-        <v>6</v>
-      </c>
-      <c r="L52" t="s">
-        <v>7</v>
-      </c>
-      <c r="M52" t="s">
-        <v>8</v>
-      </c>
-      <c r="N52" t="s">
-        <v>1</v>
-      </c>
-      <c r="O52" t="s">
-        <v>25</v>
-      </c>
-      <c r="P52" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>11</v>
-      </c>
-      <c r="R52" t="s">
-        <v>1</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" t="s">
-        <v>12</v>
-      </c>
-      <c r="U52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V52" t="s">
-        <v>1</v>
-      </c>
-      <c r="W52" t="s">
-        <v>1</v>
-      </c>
-      <c r="X52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25">
-      <c r="A53" t="s">
-        <v>158</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" t="s">
-        <v>163</v>
-      </c>
-      <c r="D53" t="s">
-        <v>136</v>
-      </c>
-      <c r="E53" s="2">
-        <v>46135</v>
-      </c>
-      <c r="F53" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G53" s="3">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J53" t="s">
-        <v>164</v>
-      </c>
-      <c r="K53" t="s">
-        <v>6</v>
-      </c>
-      <c r="L53" t="s">
-        <v>7</v>
-      </c>
-      <c r="M53" t="s">
-        <v>8</v>
-      </c>
-      <c r="N53" t="s">
-        <v>1</v>
-      </c>
-      <c r="O53" t="s">
-        <v>99</v>
-      </c>
-      <c r="P53" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>11</v>
-      </c>
-      <c r="R53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S53" s="3">
-        <v>0</v>
-      </c>
-      <c r="T53" t="s">
-        <v>12</v>
-      </c>
-      <c r="U53" t="s">
-        <v>1</v>
-      </c>
-      <c r="V53" t="s">
-        <v>1</v>
-      </c>
-      <c r="W53" t="s">
-        <v>1</v>
-      </c>
-      <c r="X53" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25">
-      <c r="A54" t="s">
-        <v>158</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" t="s">
-        <v>165</v>
-      </c>
-      <c r="D54" t="s">
-        <v>119</v>
-      </c>
-      <c r="E54" s="2">
-        <v>46135</v>
-      </c>
-      <c r="F54" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G54" s="3">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I54" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" t="s">
-        <v>166</v>
-      </c>
-      <c r="K54" t="s">
-        <v>6</v>
-      </c>
-      <c r="L54" t="s">
-        <v>7</v>
-      </c>
-      <c r="M54" t="s">
-        <v>8</v>
-      </c>
-      <c r="N54" t="s">
-        <v>1</v>
-      </c>
-      <c r="O54" t="s">
-        <v>25</v>
-      </c>
-      <c r="P54" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>11</v>
-      </c>
-      <c r="R54" t="s">
-        <v>1</v>
-      </c>
-      <c r="S54" s="3">
-        <v>0</v>
-      </c>
-      <c r="T54" t="s">
-        <v>12</v>
-      </c>
-      <c r="U54" t="s">
-        <v>1</v>
-      </c>
-      <c r="V54" t="s">
-        <v>1</v>
-      </c>
-      <c r="W54" t="s">
-        <v>1</v>
-      </c>
-      <c r="X54" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y54" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="176">
   <si>
     <t>200006418</t>
   </si>
@@ -407,12 +407,6 @@
   </si>
   <si>
     <t>前油箱蓋板_270x200*15</t>
-  </si>
-  <si>
-    <t>3227000101A0</t>
-  </si>
-  <si>
-    <t>撓性聯軸器,主軸,GS-P42_98ShA-GS,6.0-d48,6.0-d50</t>
   </si>
   <si>
     <t>200006686</t>
@@ -649,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y49"/>
+  <dimension ref="A1:Y48"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -661,7 +655,7 @@
     <col min="7" max="7" bestFit="1" width="10" customWidth="1"/>
     <col min="8" max="8" bestFit="1" width="10" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="12" customWidth="1"/>
-    <col min="10" max="10" bestFit="1" width="42" customWidth="1"/>
+    <col min="10" max="10" bestFit="1" width="38" customWidth="1"/>
     <col min="11" max="11" bestFit="1" width="4" customWidth="1"/>
     <col min="12" max="12" bestFit="1" width="6" customWidth="1"/>
     <col min="13" max="13" bestFit="1" width="6" customWidth="1"/>
@@ -681,79 +675,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -3625,10 +3619,10 @@
         <v>2</v>
       </c>
       <c r="G39" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" t="s">
         <v>4</v>
@@ -3684,34 +3678,34 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="E40" s="2">
-        <v>46150</v>
+        <v>46133</v>
       </c>
       <c r="F40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="3">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" t="s">
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K40" t="s">
         <v>6</v>
@@ -3726,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="P40" t="s">
         <v>10</v>
@@ -3738,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="S40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T40" t="s">
         <v>12</v>
@@ -3761,16 +3755,16 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D41" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E41" s="2">
         <v>46133</v>
@@ -3788,7 +3782,7 @@
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K41" t="s">
         <v>6</v>
@@ -3803,7 +3797,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P41" t="s">
         <v>10</v>
@@ -3838,34 +3832,34 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="E42" s="2">
         <v>46133</v>
       </c>
       <c r="F42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="s">
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="K42" t="s">
         <v>6</v>
@@ -3880,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>137</v>
+        <v>38</v>
       </c>
       <c r="P42" t="s">
         <v>10</v>
@@ -3892,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="S42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T42" t="s">
         <v>12</v>
@@ -3915,16 +3909,16 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E43" s="2">
         <v>46133</v>
@@ -3942,7 +3936,7 @@
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K43" t="s">
         <v>6</v>
@@ -3992,19 +3986,19 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="E44" s="2">
-        <v>46133</v>
+        <v>46142</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
@@ -4019,7 +4013,7 @@
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="K44" t="s">
         <v>6</v>
@@ -4034,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="P44" t="s">
         <v>10</v>
@@ -4046,13 +4040,13 @@
         <v>1</v>
       </c>
       <c r="S44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="s">
         <v>12</v>
       </c>
       <c r="U44" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="V44" t="s">
         <v>1</v>
@@ -4069,19 +4063,19 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B45" t="s">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E45" s="2">
-        <v>46142</v>
+        <v>46135</v>
       </c>
       <c r="F45" s="3">
         <v>1</v>
@@ -4096,7 +4090,7 @@
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K45" t="s">
         <v>6</v>
@@ -4111,7 +4105,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="P45" t="s">
         <v>10</v>
@@ -4146,7 +4140,7 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
@@ -4155,7 +4149,7 @@
         <v>145</v>
       </c>
       <c r="D46" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E46" s="2">
         <v>46135</v>
@@ -4188,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="P46" t="s">
         <v>10</v>
@@ -4223,7 +4217,7 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
@@ -4232,19 +4226,19 @@
         <v>147</v>
       </c>
       <c r="D47" t="s">
-        <v>3</v>
+        <v>128</v>
       </c>
       <c r="E47" s="2">
         <v>46135</v>
       </c>
       <c r="F47" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I47" t="s">
         <v>4</v>
@@ -4265,7 +4259,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="P47" t="s">
         <v>10</v>
@@ -4300,7 +4294,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
@@ -4309,7 +4303,7 @@
         <v>149</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="E48" s="2">
         <v>46135</v>
@@ -4342,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="P48" t="s">
         <v>10</v>
@@ -4372,83 +4366,6 @@
         <v>1</v>
       </c>
       <c r="Y48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25">
-      <c r="A49" t="s">
-        <v>144</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>151</v>
-      </c>
-      <c r="D49" t="s">
-        <v>115</v>
-      </c>
-      <c r="E49" s="2">
-        <v>46135</v>
-      </c>
-      <c r="F49" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" t="s">
-        <v>152</v>
-      </c>
-      <c r="K49" t="s">
-        <v>6</v>
-      </c>
-      <c r="L49" t="s">
-        <v>7</v>
-      </c>
-      <c r="M49" t="s">
-        <v>8</v>
-      </c>
-      <c r="N49" t="s">
-        <v>1</v>
-      </c>
-      <c r="O49" t="s">
-        <v>25</v>
-      </c>
-      <c r="P49" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>11</v>
-      </c>
-      <c r="R49" t="s">
-        <v>1</v>
-      </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" t="s">
-        <v>12</v>
-      </c>
-      <c r="U49" t="s">
-        <v>1</v>
-      </c>
-      <c r="V49" t="s">
-        <v>1</v>
-      </c>
-      <c r="W49" t="s">
-        <v>1</v>
-      </c>
-      <c r="X49" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y49" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,432 +11,399 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="176">
-  <si>
-    <t>200006418</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="161">
+  <si>
+    <t>200006482</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>080100087604</t>
+    <t>8923000586A0</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>固定板,A軸前銅套用_d142*D166*3L</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>SHEO</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>1X001</t>
+  </si>
+  <si>
+    <t>虛擬工作中心</t>
+  </si>
+  <si>
+    <t>REL</t>
+  </si>
+  <si>
+    <t>9816</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>8420002369A0</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>襯套,A軸前_d130*D145*18L</t>
+  </si>
+  <si>
+    <t>4060000066C0</t>
+  </si>
+  <si>
+    <t>0310</t>
+  </si>
+  <si>
+    <t>活塞,A軸法蘭前部_d130*D186*129.5L</t>
+  </si>
+  <si>
+    <t>3209000356A0</t>
+  </si>
+  <si>
+    <t>0350</t>
+  </si>
+  <si>
+    <t>#50 主軸,CTS,BBT_D143*368L</t>
+  </si>
+  <si>
+    <t>0102</t>
+  </si>
+  <si>
+    <t>200006500</t>
+  </si>
+  <si>
+    <t>3214000272C0</t>
+  </si>
+  <si>
+    <t>0360</t>
+  </si>
+  <si>
+    <t>吊桿_MVP-10</t>
+  </si>
+  <si>
+    <t>1F004</t>
+  </si>
+  <si>
+    <t>組件課</t>
+  </si>
+  <si>
+    <t>9804</t>
+  </si>
+  <si>
+    <t>200006511</t>
+  </si>
+  <si>
+    <t>8814001214D3</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>機頭加工圖,G6K_HCMC-1682</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>200006554</t>
+  </si>
+  <si>
+    <t>080100035602</t>
+  </si>
+  <si>
+    <t>0050</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,0045</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>0802</t>
+  </si>
+  <si>
+    <t>200006569</t>
+  </si>
+  <si>
+    <t>2069000033B0</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>螺旋斜齒輪,OGIC_31T-L-90,G5K</t>
+  </si>
+  <si>
+    <t>321000041300</t>
+  </si>
+  <si>
+    <t>0120</t>
+  </si>
+  <si>
+    <t>傳動刀把_7/24-154L萬向頭</t>
+  </si>
+  <si>
+    <t>2069000034B0</t>
+  </si>
+  <si>
+    <t>0160</t>
+  </si>
+  <si>
+    <t>螺旋斜齒輪,OGIC_31T-R-90,G5K</t>
+  </si>
+  <si>
+    <t>3058000838A0</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>軸承箱,A軸後端用_d90*D180*99L,溫降案</t>
+  </si>
+  <si>
+    <t>2069000031B0</t>
+  </si>
+  <si>
+    <t>0280</t>
+  </si>
+  <si>
+    <t>螺旋斜齒輪,OGIC_35T-R-90,G5K</t>
+  </si>
+  <si>
+    <t>8420002368A0</t>
+  </si>
+  <si>
+    <t>襯套,C軸下_D201*d185*H21</t>
+  </si>
+  <si>
+    <t>2069000032A0</t>
+  </si>
+  <si>
+    <t>螺旋斜齒輪,OGIC_35T-L-90度</t>
+  </si>
+  <si>
+    <t>4060000109B0</t>
+  </si>
+  <si>
+    <t>0730</t>
+  </si>
+  <si>
+    <t>活塞外套,C軸_d180*D240*H125,G5K</t>
+  </si>
+  <si>
+    <t>8923000735B0</t>
+  </si>
+  <si>
+    <t>0740</t>
+  </si>
+  <si>
+    <t>固定板,C軸下_D227*d197*2t,G5K</t>
+  </si>
+  <si>
+    <t>0107</t>
+  </si>
+  <si>
+    <t>200006573</t>
+  </si>
+  <si>
+    <t>3154001348A1</t>
+  </si>
+  <si>
+    <t>主軸前蓋_INC-H-90</t>
+  </si>
+  <si>
+    <t>200006578</t>
+  </si>
+  <si>
+    <t>080100021502</t>
   </si>
   <si>
     <t>0020</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>D15K 主軸,010017_BBT40,M60,CW45</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0010</t>
-  </si>
-  <si>
-    <t>SHEO</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>1F004</t>
-  </si>
-  <si>
-    <t>組件課</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>0802</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>200006445</t>
-  </si>
-  <si>
-    <t>8814001214D3</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>機頭加工圖,G6K_HCMC-1682</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>9804</t>
-  </si>
-  <si>
-    <t>200006482</t>
-  </si>
-  <si>
-    <t>8923000586A0</t>
-  </si>
-  <si>
-    <t>0200</t>
-  </si>
-  <si>
-    <t>固定板,A軸前銅套用_d142*D166*3L</t>
-  </si>
-  <si>
-    <t>0101</t>
-  </si>
-  <si>
-    <t>1X001</t>
-  </si>
-  <si>
-    <t>虛擬工作中心</t>
-  </si>
-  <si>
-    <t>9816</t>
-  </si>
-  <si>
-    <t>8420002369A0</t>
-  </si>
-  <si>
-    <t>0240</t>
-  </si>
-  <si>
-    <t>襯套,A軸前_d130*D145*18L</t>
-  </si>
-  <si>
-    <t>4060000066C0</t>
-  </si>
-  <si>
-    <t>0310</t>
-  </si>
-  <si>
-    <t>活塞,A軸法蘭前部_d130*D186*129.5L</t>
-  </si>
-  <si>
-    <t>3209000356A0</t>
-  </si>
-  <si>
-    <t>0350</t>
-  </si>
-  <si>
-    <t>#50 主軸,CTS,BBT_D143*368L</t>
-  </si>
-  <si>
-    <t>0102</t>
-  </si>
-  <si>
-    <t>3217000174A0</t>
-  </si>
-  <si>
-    <t>0440</t>
-  </si>
-  <si>
-    <t>通心軸,CTS打刀用_D80*d13*H36.2</t>
-  </si>
-  <si>
-    <t>200006488</t>
-  </si>
-  <si>
-    <t>3241000017A1</t>
-  </si>
-  <si>
-    <t>0060</t>
-  </si>
-  <si>
-    <t>直齒離合器,C軸2.5度_D330*d280*H40,144T</t>
-  </si>
-  <si>
-    <t>200006489</t>
-  </si>
-  <si>
-    <t>200006490</t>
-  </si>
-  <si>
-    <t>200006500</t>
+    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>3210000386B0</t>
+  </si>
+  <si>
+    <t>傳動軸_d50*D103*774L</t>
+  </si>
+  <si>
+    <t>999800001600</t>
+  </si>
+  <si>
+    <t>0250</t>
+  </si>
+  <si>
+    <t>內藏式主軸轉子組,FANUC_10K807N,021458</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>610400005000</t>
+  </si>
+  <si>
+    <t>0260</t>
+  </si>
+  <si>
+    <t>內藏式主軸轉子加工圖,FANUC_A06B-2726-B651#2231</t>
+  </si>
+  <si>
+    <t>0126</t>
+  </si>
+  <si>
+    <t>610400002700</t>
+  </si>
+  <si>
+    <t>內藏式主軸轉子,FANUC_A06B-2726-B651#2231</t>
+  </si>
+  <si>
+    <t>200006579</t>
+  </si>
+  <si>
+    <t>3227000145A0</t>
+  </si>
+  <si>
+    <t>0500</t>
+  </si>
+  <si>
+    <t>撓性聯軸器,主軸,Mayr_100/953.221/50/50S</t>
+  </si>
+  <si>
+    <t>200006624</t>
+  </si>
+  <si>
+    <t>3154001424A1</t>
+  </si>
+  <si>
+    <t>0330</t>
+  </si>
+  <si>
+    <t>主軸前蓋,DDS20K長套筒_d82.5*D148*H27.5</t>
+  </si>
+  <si>
+    <t>8423000091A0</t>
+  </si>
+  <si>
+    <t>吹氣環_d82.5*D91*H9.25</t>
+  </si>
+  <si>
+    <t>200006652</t>
   </si>
   <si>
     <t>8420002111A1</t>
   </si>
   <si>
-    <t>0130</t>
+    <t>0140</t>
   </si>
   <si>
     <t>間隔環組,中_HF4C15-011+012/MCS40-233</t>
   </si>
   <si>
-    <t>3214000272C0</t>
-  </si>
-  <si>
-    <t>0360</t>
-  </si>
-  <si>
-    <t>吊桿_MVP-10</t>
-  </si>
-  <si>
-    <t>200006511</t>
-  </si>
-  <si>
-    <t>200006529</t>
-  </si>
-  <si>
-    <t>2051000147A1</t>
-  </si>
-  <si>
-    <t>0070</t>
-  </si>
-  <si>
-    <t>中間軸大齒輪_D186*d62*35H</t>
-  </si>
-  <si>
-    <t>2051000148A1</t>
-  </si>
-  <si>
-    <t>0080</t>
-  </si>
-  <si>
-    <t>栓槽轂齒輪_D90*d39*106L</t>
-  </si>
-  <si>
-    <t>3211000085A0</t>
+    <t>200006670</t>
+  </si>
+  <si>
+    <t>8015002766B0</t>
+  </si>
+  <si>
+    <t>增壓缸底座_MVP-13P</t>
+  </si>
+  <si>
+    <t>200006671</t>
+  </si>
+  <si>
+    <t>8814001455A2</t>
+  </si>
+  <si>
+    <t>機頭加工圖,#40P短套筒_MVP-11</t>
+  </si>
+  <si>
+    <t>200006675</t>
+  </si>
+  <si>
+    <t>200006676</t>
+  </si>
+  <si>
+    <t>080100045203</t>
+  </si>
+  <si>
+    <t>0030</t>
+  </si>
+  <si>
+    <t>D12K 主軸,021274_BBT50,M50,C045</t>
+  </si>
+  <si>
+    <t>8311000404A0</t>
   </si>
   <si>
     <t>0090</t>
   </si>
   <si>
-    <t>中間軸_D38*d30*226L</t>
-  </si>
-  <si>
-    <t>200006548</t>
-  </si>
-  <si>
-    <t>200006573</t>
-  </si>
-  <si>
-    <t>3154001348A1</t>
-  </si>
-  <si>
-    <t>主軸前蓋_INC-H-90</t>
-  </si>
-  <si>
-    <t>200006574</t>
-  </si>
-  <si>
-    <t>3211000059B0</t>
-  </si>
-  <si>
-    <t>0050</t>
-  </si>
-  <si>
-    <t>中間軸_PI-1</t>
-  </si>
-  <si>
-    <t>2051000143A0</t>
-  </si>
-  <si>
-    <t>中間軸小齒輪/37T_PI-1</t>
-  </si>
-  <si>
-    <t>2056000065B0</t>
-  </si>
-  <si>
-    <t>中間軸大齒輪/74T_PI-1</t>
-  </si>
-  <si>
-    <t>200006578</t>
-  </si>
-  <si>
-    <t>080100021502</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
-  </si>
-  <si>
-    <t>3210000386B0</t>
-  </si>
-  <si>
-    <t>0110</t>
-  </si>
-  <si>
-    <t>傳動軸_d50*D103*774L</t>
-  </si>
-  <si>
-    <t>999800001600</t>
-  </si>
-  <si>
-    <t>0250</t>
-  </si>
-  <si>
-    <t>內藏式主軸轉子組,FANUC_10K807N,021458</t>
-  </si>
-  <si>
-    <t>0100</t>
-  </si>
-  <si>
-    <t>610400005000</t>
-  </si>
-  <si>
-    <t>0260</t>
-  </si>
-  <si>
-    <t>內藏式主軸轉子加工圖,FANUC_A06B-2726-B651#2231</t>
-  </si>
-  <si>
-    <t>0126</t>
-  </si>
-  <si>
-    <t>610400002700</t>
-  </si>
-  <si>
-    <t>0270</t>
-  </si>
-  <si>
-    <t>內藏式主軸轉子,FANUC_A06B-2726-B651#2231</t>
-  </si>
-  <si>
-    <t>200006579</t>
-  </si>
-  <si>
-    <t>3227000145A0</t>
-  </si>
-  <si>
-    <t>0500</t>
-  </si>
-  <si>
-    <t>撓性聯軸器,主軸,Mayr_100/953.221/50/50S</t>
-  </si>
-  <si>
-    <t>0120</t>
-  </si>
-  <si>
-    <t>200006580</t>
-  </si>
-  <si>
-    <t>892300066800</t>
-  </si>
-  <si>
-    <t>0480</t>
-  </si>
-  <si>
-    <t>出貨固定板_EA/EAY,HF-A90/AE/M90/MU</t>
-  </si>
-  <si>
-    <t>0107</t>
-  </si>
-  <si>
-    <t>200006624</t>
-  </si>
-  <si>
-    <t>3154001424A1</t>
-  </si>
-  <si>
-    <t>0330</t>
-  </si>
-  <si>
-    <t>主軸前蓋,DDS20K長套筒_d82.5*D148*H27.5</t>
-  </si>
-  <si>
-    <t>8423000091A0</t>
-  </si>
-  <si>
-    <t>吹氣環_d82.5*D91*H9.25</t>
-  </si>
-  <si>
-    <t>200006652</t>
-  </si>
-  <si>
-    <t>0140</t>
-  </si>
-  <si>
-    <t>200006666</t>
-  </si>
-  <si>
-    <t>8814001457A2</t>
-  </si>
-  <si>
-    <t>0040</t>
-  </si>
-  <si>
-    <t>機頭加工圖,#40D長套筒_S-Plus 8</t>
-  </si>
-  <si>
-    <t>200006670</t>
-  </si>
-  <si>
-    <t>8015002766B0</t>
-  </si>
-  <si>
-    <t>增壓缸底座_MVP-13P</t>
-  </si>
-  <si>
-    <t>200006671</t>
-  </si>
-  <si>
-    <t>8814001455A2</t>
-  </si>
-  <si>
-    <t>機頭加工圖,#40P短套筒_MVP-11</t>
-  </si>
-  <si>
-    <t>200006674</t>
-  </si>
-  <si>
-    <t>0190</t>
-  </si>
-  <si>
-    <t>200006675</t>
-  </si>
-  <si>
-    <t>200006676</t>
-  </si>
-  <si>
-    <t>080100045203</t>
-  </si>
-  <si>
-    <t>0030</t>
-  </si>
-  <si>
-    <t>D12K 主軸,021274_BBT50,M50,C045</t>
-  </si>
-  <si>
-    <t>8311000404A0</t>
-  </si>
-  <si>
     <t>前油箱蓋板_270x200*15</t>
   </si>
   <si>
     <t>200006686</t>
   </si>
   <si>
-    <t>305000005200</t>
-  </si>
-  <si>
-    <t>陶珠軸承_GMN-HYKH6012 2RZCTAP4UL</t>
-  </si>
-  <si>
-    <t>0128</t>
-  </si>
-  <si>
-    <t>305000005300</t>
-  </si>
-  <si>
-    <t>陶珠軸承_GMN-HYKH6013 2RZCTAP4UL</t>
-  </si>
-  <si>
     <t>0370</t>
   </si>
   <si>
-    <t>630000351</t>
-  </si>
-  <si>
-    <t>080100076403</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021444_BT40,8YU,CW45</t>
+    <t>200006687</t>
+  </si>
+  <si>
+    <t>200006690</t>
+  </si>
+  <si>
+    <t>3215000505A0</t>
+  </si>
+  <si>
+    <t>打刀承片_BT50/CTS-011</t>
+  </si>
+  <si>
+    <t>3215000514B0</t>
+  </si>
+  <si>
+    <t>打刀公環_BT50/CTS-009</t>
+  </si>
+  <si>
+    <t>3215000610B1</t>
+  </si>
+  <si>
+    <t>打刀母環,#50G/P6K_CTS,#50G/P6K</t>
+  </si>
+  <si>
+    <t>200006691</t>
+  </si>
+  <si>
+    <t>200006692</t>
+  </si>
+  <si>
+    <t>200006700</t>
+  </si>
+  <si>
+    <t>200006702</t>
   </si>
   <si>
     <t>630000354</t>
@@ -448,22 +415,10 @@
     <t>撓性聯軸器,主軸,GS42P_98ShA,6.0-d48,6.0-d55</t>
   </si>
   <si>
-    <t>1092001297A0</t>
-  </si>
-  <si>
-    <t>平行鍵/雙圓頭_16*6*90L</t>
-  </si>
-  <si>
     <t>3227000129A0</t>
   </si>
   <si>
     <t>撓性聯軸器,主軸,GS42P_98ShA,6.0-d48,6.0-d48</t>
-  </si>
-  <si>
-    <t>1092001294A0</t>
-  </si>
-  <si>
-    <t>平行鍵/雙圓頭_14*5.5*80L</t>
   </si>
   <si>
     <t>訂單</t>
@@ -643,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -675,79 +630,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="S1" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="U1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="V1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="W1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="X1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -764,7 +719,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="2">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -829,35 +784,35 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="2">
+        <v>46125</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2">
-        <v>46142</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
       <c r="K3" t="s">
         <v>6</v>
       </c>
@@ -871,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P3" t="s">
         <v>10</v>
@@ -889,7 +844,7 @@
         <v>12</v>
       </c>
       <c r="U3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V3" t="s">
         <v>1</v>
@@ -906,16 +861,16 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2">
         <v>46125</v>
@@ -933,7 +888,7 @@
         <v>4</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
         <v>6</v>
@@ -948,13 +903,13 @@
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="R4" t="s">
         <v>1</v>
@@ -966,7 +921,7 @@
         <v>12</v>
       </c>
       <c r="U4" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="V4" t="s">
         <v>1</v>
@@ -983,16 +938,16 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2">
         <v>46125</v>
@@ -1010,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K5" t="s">
         <v>6</v>
@@ -1025,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="R5" t="s">
         <v>1</v>
@@ -1043,7 +998,7 @@
         <v>12</v>
       </c>
       <c r="U5" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="V5" t="s">
         <v>1</v>
@@ -1060,19 +1015,19 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2">
-        <v>46125</v>
+        <v>46155</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1087,7 +1042,7 @@
         <v>4</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K6" t="s">
         <v>6</v>
@@ -1102,13 +1057,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R6" t="s">
         <v>1</v>
@@ -1120,7 +1075,7 @@
         <v>12</v>
       </c>
       <c r="U6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="V6" t="s">
         <v>1</v>
@@ -1137,55 +1092,55 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46146</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" t="s">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
+      <c r="K7" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="2">
-        <v>46125</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>4</v>
-      </c>
-      <c r="J7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" t="s">
-        <v>7</v>
-      </c>
-      <c r="M7" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" t="s">
-        <v>1</v>
-      </c>
-      <c r="O7" t="s">
-        <v>38</v>
-      </c>
       <c r="P7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R7" t="s">
         <v>1</v>
@@ -1197,7 +1152,7 @@
         <v>12</v>
       </c>
       <c r="U7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="V7" t="s">
         <v>1</v>
@@ -1214,55 +1169,55 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
       <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="2">
+        <v>46155</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="2">
-        <v>46125</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>7</v>
+      </c>
+      <c r="M8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O8" t="s">
         <v>41</v>
       </c>
-      <c r="K8" t="s">
-        <v>6</v>
-      </c>
-      <c r="L8" t="s">
-        <v>7</v>
-      </c>
-      <c r="M8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" t="s">
-        <v>1</v>
-      </c>
-      <c r="O8" t="s">
-        <v>1</v>
-      </c>
       <c r="P8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R8" t="s">
         <v>1</v>
@@ -1274,7 +1229,7 @@
         <v>12</v>
       </c>
       <c r="U8" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="V8" t="s">
         <v>1</v>
@@ -1291,19 +1246,19 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2">
-        <v>46094</v>
+        <v>46135</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -1318,7 +1273,7 @@
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K9" t="s">
         <v>6</v>
@@ -1333,25 +1288,25 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="R9" t="s">
         <v>1</v>
       </c>
       <c r="S9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="s">
         <v>12</v>
       </c>
       <c r="U9" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="V9" t="s">
         <v>1</v>
@@ -1368,19 +1323,19 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2">
-        <v>46106</v>
+        <v>46135</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
@@ -1395,7 +1350,7 @@
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K10" t="s">
         <v>6</v>
@@ -1410,13 +1365,13 @@
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P10" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="R10" t="s">
         <v>1</v>
@@ -1428,7 +1383,7 @@
         <v>12</v>
       </c>
       <c r="U10" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="V10" t="s">
         <v>1</v>
@@ -1445,19 +1400,19 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
@@ -1472,7 +1427,7 @@
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K11" t="s">
         <v>6</v>
@@ -1487,25 +1442,25 @@
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P11" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="R11" t="s">
         <v>1</v>
       </c>
       <c r="S11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="s">
         <v>12</v>
       </c>
       <c r="U11" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="V11" t="s">
         <v>1</v>
@@ -1522,19 +1477,19 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2">
-        <v>46155</v>
+        <v>46135</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
@@ -1549,7 +1504,7 @@
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="K12" t="s">
         <v>6</v>
@@ -1564,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="P12" t="s">
         <v>10</v>
@@ -1582,7 +1537,7 @@
         <v>12</v>
       </c>
       <c r="U12" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V12" t="s">
         <v>1</v>
@@ -1599,19 +1554,19 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E13" s="2">
-        <v>46155</v>
+        <v>46135</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
@@ -1626,7 +1581,7 @@
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
         <v>6</v>
@@ -1641,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="O13" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="P13" t="s">
         <v>10</v>
@@ -1659,7 +1614,7 @@
         <v>12</v>
       </c>
       <c r="U13" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V13" t="s">
         <v>1</v>
@@ -1676,35 +1631,35 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="2">
+        <v>46135</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" t="s">
         <v>55</v>
       </c>
-      <c r="B14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="2">
-        <v>46146</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" t="s">
-        <v>18</v>
-      </c>
       <c r="K14" t="s">
         <v>6</v>
       </c>
@@ -1718,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="O14" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P14" t="s">
         <v>10</v>
@@ -1736,7 +1691,7 @@
         <v>12</v>
       </c>
       <c r="U14" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V14" t="s">
         <v>1</v>
@@ -1753,35 +1708,35 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
         <v>56</v>
       </c>
-      <c r="B15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>57</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" s="2">
+        <v>46135</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="2">
-        <v>46104</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" t="s">
-        <v>59</v>
-      </c>
       <c r="K15" t="s">
         <v>6</v>
       </c>
@@ -1795,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P15" t="s">
         <v>10</v>
@@ -1807,13 +1762,13 @@
         <v>1</v>
       </c>
       <c r="S15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="s">
         <v>12</v>
       </c>
       <c r="U15" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V15" t="s">
         <v>1</v>
@@ -1830,19 +1785,19 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="E16" s="2">
-        <v>46104</v>
+        <v>46135</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
@@ -1857,7 +1812,7 @@
         <v>4</v>
       </c>
       <c r="J16" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s">
         <v>6</v>
@@ -1872,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P16" t="s">
         <v>10</v>
@@ -1890,7 +1845,7 @@
         <v>12</v>
       </c>
       <c r="U16" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V16" t="s">
         <v>1</v>
@@ -1907,19 +1862,19 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E17" s="2">
-        <v>46104</v>
+        <v>46135</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -1934,7 +1889,7 @@
         <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K17" t="s">
         <v>6</v>
@@ -1949,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P17" t="s">
         <v>10</v>
@@ -1967,7 +1922,7 @@
         <v>12</v>
       </c>
       <c r="U17" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V17" t="s">
         <v>1</v>
@@ -1984,19 +1939,19 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2">
-        <v>46108</v>
+        <v>46135</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -2011,7 +1966,7 @@
         <v>4</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="K18" t="s">
         <v>6</v>
@@ -2026,7 +1981,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P18" t="s">
         <v>10</v>
@@ -2044,7 +1999,7 @@
         <v>12</v>
       </c>
       <c r="U18" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V18" t="s">
         <v>1</v>
@@ -2061,19 +2016,19 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E19" s="2">
-        <v>46167</v>
+        <v>46135</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
@@ -2088,7 +2043,7 @@
         <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K19" t="s">
         <v>6</v>
@@ -2103,13 +2058,13 @@
         <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P19" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="R19" t="s">
         <v>1</v>
@@ -2121,7 +2076,7 @@
         <v>12</v>
       </c>
       <c r="U19" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="V19" t="s">
         <v>1</v>
@@ -2138,19 +2093,19 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2">
-        <v>46112</v>
+        <v>46135</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
@@ -2165,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K20" t="s">
         <v>6</v>
@@ -2180,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="O20" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="P20" t="s">
         <v>10</v>
@@ -2198,7 +2153,7 @@
         <v>12</v>
       </c>
       <c r="U20" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V20" t="s">
         <v>1</v>
@@ -2221,13 +2176,13 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="E21" s="2">
-        <v>46112</v>
+        <v>46167</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -2242,7 +2197,7 @@
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K21" t="s">
         <v>6</v>
@@ -2257,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P21" t="s">
         <v>10</v>
@@ -2275,7 +2230,7 @@
         <v>12</v>
       </c>
       <c r="U21" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V21" t="s">
         <v>1</v>
@@ -2292,35 +2247,35 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
       <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46106</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" t="s">
         <v>76</v>
       </c>
-      <c r="D22" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="2">
-        <v>46112</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1</v>
-      </c>
-      <c r="I22" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" t="s">
-        <v>77</v>
-      </c>
       <c r="K22" t="s">
         <v>6</v>
       </c>
@@ -2334,13 +2289,13 @@
         <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="P22" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q22" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R22" t="s">
         <v>1</v>
@@ -2352,7 +2307,7 @@
         <v>12</v>
       </c>
       <c r="U22" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="V22" t="s">
         <v>1</v>
@@ -2369,16 +2324,16 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2">
         <v>46106</v>
@@ -2396,7 +2351,7 @@
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K23" t="s">
         <v>6</v>
@@ -2414,10 +2369,10 @@
         <v>9</v>
       </c>
       <c r="P23" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q23" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R23" t="s">
         <v>1</v>
@@ -2429,7 +2384,7 @@
         <v>12</v>
       </c>
       <c r="U23" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="V23" t="s">
         <v>1</v>
@@ -2446,16 +2401,16 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2">
         <v>46106</v>
@@ -2473,7 +2428,7 @@
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K24" t="s">
         <v>6</v>
@@ -2488,25 +2443,25 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q24" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R24" t="s">
         <v>1</v>
       </c>
       <c r="S24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="s">
         <v>12</v>
       </c>
       <c r="U24" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="V24" t="s">
         <v>1</v>
@@ -2523,16 +2478,16 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
         <v>84</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
       </c>
       <c r="E25" s="2">
         <v>46106</v>
@@ -2550,28 +2505,28 @@
         <v>4</v>
       </c>
       <c r="J25" t="s">
+        <v>85</v>
+      </c>
+      <c r="K25" t="s">
+        <v>6</v>
+      </c>
+      <c r="L25" t="s">
+        <v>7</v>
+      </c>
+      <c r="M25" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" t="s">
+        <v>1</v>
+      </c>
+      <c r="O25" t="s">
         <v>86</v>
       </c>
-      <c r="K25" t="s">
-        <v>6</v>
-      </c>
-      <c r="L25" t="s">
-        <v>7</v>
-      </c>
-      <c r="M25" t="s">
-        <v>8</v>
-      </c>
-      <c r="N25" t="s">
-        <v>1</v>
-      </c>
-      <c r="O25" t="s">
-        <v>87</v>
-      </c>
       <c r="P25" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q25" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R25" t="s">
         <v>1</v>
@@ -2600,16 +2555,16 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2">
         <v>46106</v>
@@ -2627,7 +2582,7 @@
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s">
         <v>6</v>
@@ -2642,13 +2597,13 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="P26" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q26" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R26" t="s">
         <v>1</v>
@@ -2677,35 +2632,35 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="2">
+        <v>46097</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" t="s">
         <v>92</v>
       </c>
-      <c r="D27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="2">
-        <v>46106</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1</v>
-      </c>
-      <c r="I27" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" t="s">
-        <v>94</v>
-      </c>
       <c r="K27" t="s">
         <v>6</v>
       </c>
@@ -2719,13 +2674,13 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="P27" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q27" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R27" t="s">
         <v>1</v>
@@ -2737,7 +2692,7 @@
         <v>12</v>
       </c>
       <c r="U27" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="V27" t="s">
         <v>1</v>
@@ -2754,35 +2709,35 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" t="s">
         <v>95</v>
       </c>
-      <c r="B28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="E28" s="2">
+        <v>46161</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J28" t="s">
         <v>96</v>
       </c>
-      <c r="D28" t="s">
-        <v>97</v>
-      </c>
-      <c r="E28" s="2">
-        <v>46097</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1</v>
-      </c>
-      <c r="I28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J28" t="s">
-        <v>98</v>
-      </c>
       <c r="K28" t="s">
         <v>6</v>
       </c>
@@ -2796,25 +2751,25 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="P28" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q28" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R28" t="s">
         <v>1</v>
       </c>
       <c r="S28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="s">
         <v>12</v>
       </c>
       <c r="U28" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V28" t="s">
         <v>1</v>
@@ -2831,19 +2786,19 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="E29" s="2">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
@@ -2858,7 +2813,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K29" t="s">
         <v>6</v>
@@ -2873,13 +2828,13 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="P29" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q29" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R29" t="s">
         <v>1</v>
@@ -2891,7 +2846,7 @@
         <v>12</v>
       </c>
       <c r="U29" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="V29" t="s">
         <v>1</v>
@@ -2908,16 +2863,16 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E30" s="2">
         <v>46161</v>
@@ -2935,7 +2890,7 @@
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="K30" t="s">
         <v>6</v>
@@ -2950,13 +2905,13 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P30" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q30" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R30" t="s">
         <v>1</v>
@@ -2968,7 +2923,7 @@
         <v>12</v>
       </c>
       <c r="U30" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V30" t="s">
         <v>1</v>
@@ -2985,35 +2940,35 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="2">
+        <v>46153</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>4</v>
+      </c>
+      <c r="J31" t="s">
         <v>105</v>
       </c>
-      <c r="B31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="2">
-        <v>46161</v>
-      </c>
-      <c r="F31" s="3">
-        <v>1</v>
-      </c>
-      <c r="G31" s="3">
-        <v>0</v>
-      </c>
-      <c r="H31" s="3">
-        <v>1</v>
-      </c>
-      <c r="I31" t="s">
-        <v>4</v>
-      </c>
-      <c r="J31" t="s">
-        <v>110</v>
-      </c>
       <c r="K31" t="s">
         <v>6</v>
       </c>
@@ -3027,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="P31" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q31" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R31" t="s">
         <v>1</v>
@@ -3045,7 +3000,7 @@
         <v>12</v>
       </c>
       <c r="U31" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V31" t="s">
         <v>1</v>
@@ -3062,19 +3017,19 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2">
-        <v>46161</v>
+        <v>46134</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -3089,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="K32" t="s">
         <v>6</v>
@@ -3104,13 +3059,13 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P32" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q32" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R32" t="s">
         <v>1</v>
@@ -3122,7 +3077,7 @@
         <v>12</v>
       </c>
       <c r="U32" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V32" t="s">
         <v>1</v>
@@ -3139,19 +3094,19 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="E33" s="2">
-        <v>46160</v>
+        <v>46136</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
@@ -3166,7 +3121,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="K33" t="s">
         <v>6</v>
@@ -3181,13 +3136,13 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="P33" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q33" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R33" t="s">
         <v>1</v>
@@ -3199,7 +3154,7 @@
         <v>12</v>
       </c>
       <c r="U33" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V33" t="s">
         <v>1</v>
@@ -3216,19 +3171,19 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="E34" s="2">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
@@ -3243,7 +3198,7 @@
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="K34" t="s">
         <v>6</v>
@@ -3258,13 +3213,13 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="P34" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q34" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R34" t="s">
         <v>1</v>
@@ -3276,7 +3231,7 @@
         <v>12</v>
       </c>
       <c r="U34" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="V34" t="s">
         <v>1</v>
@@ -3293,25 +3248,25 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="E35" s="2">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="F35" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="3">
         <v>1</v>
@@ -3320,7 +3275,7 @@
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K35" t="s">
         <v>6</v>
@@ -3335,25 +3290,25 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P35" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q35" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R35" t="s">
         <v>1</v>
       </c>
       <c r="S35" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T35" t="s">
         <v>12</v>
       </c>
       <c r="U35" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V35" t="s">
         <v>1</v>
@@ -3370,19 +3325,19 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="E36" s="2">
-        <v>46147</v>
+        <v>46133</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -3397,7 +3352,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="K36" t="s">
         <v>6</v>
@@ -3412,13 +3367,13 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P36" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q36" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R36" t="s">
         <v>1</v>
@@ -3430,7 +3385,7 @@
         <v>12</v>
       </c>
       <c r="U36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V36" t="s">
         <v>1</v>
@@ -3447,19 +3402,19 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="E37" s="2">
-        <v>46136</v>
+        <v>46133</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -3474,7 +3429,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="K37" t="s">
         <v>6</v>
@@ -3489,13 +3444,13 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P37" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R37" t="s">
         <v>1</v>
@@ -3507,7 +3462,7 @@
         <v>12</v>
       </c>
       <c r="U37" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V37" t="s">
         <v>1</v>
@@ -3524,19 +3479,19 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="E38" s="2">
-        <v>46150</v>
+        <v>46134</v>
       </c>
       <c r="F38" s="3">
         <v>1</v>
@@ -3551,7 +3506,7 @@
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="K38" t="s">
         <v>6</v>
@@ -3566,13 +3521,13 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="P38" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q38" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R38" t="s">
         <v>1</v>
@@ -3584,7 +3539,7 @@
         <v>12</v>
       </c>
       <c r="U38" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="V38" t="s">
         <v>1</v>
@@ -3601,25 +3556,25 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2">
-        <v>46150</v>
+        <v>46139</v>
       </c>
       <c r="F39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="3">
         <v>1</v>
@@ -3628,7 +3583,7 @@
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="K39" t="s">
         <v>6</v>
@@ -3643,25 +3598,25 @@
         <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P39" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q39" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R39" t="s">
         <v>1</v>
       </c>
       <c r="S39" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T39" t="s">
         <v>12</v>
       </c>
       <c r="U39" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V39" t="s">
         <v>1</v>
@@ -3678,34 +3633,34 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="E40" s="2">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="F40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="3">
         <v>0</v>
       </c>
       <c r="H40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="s">
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="K40" t="s">
         <v>6</v>
@@ -3720,25 +3675,25 @@
         <v>1</v>
       </c>
       <c r="O40" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="P40" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q40" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R40" t="s">
         <v>1</v>
       </c>
       <c r="S40" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T40" t="s">
         <v>12</v>
       </c>
       <c r="U40" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V40" t="s">
         <v>1</v>
@@ -3755,34 +3710,34 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D41" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E41" s="2">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="F41" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="3">
         <v>0</v>
       </c>
       <c r="H41" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" t="s">
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="K41" t="s">
         <v>6</v>
@@ -3797,25 +3752,25 @@
         <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="P41" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q41" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R41" t="s">
         <v>1</v>
       </c>
       <c r="S41" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T41" t="s">
         <v>12</v>
       </c>
       <c r="U41" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V41" t="s">
         <v>1</v>
@@ -3832,19 +3787,19 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="F42" s="3">
         <v>1</v>
@@ -3859,7 +3814,7 @@
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="K42" t="s">
         <v>6</v>
@@ -3874,13 +3829,13 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="P42" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q42" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R42" t="s">
         <v>1</v>
@@ -3892,7 +3847,7 @@
         <v>12</v>
       </c>
       <c r="U42" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V42" t="s">
         <v>1</v>
@@ -3909,19 +3864,19 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D43" t="s">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="E43" s="2">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="F43" s="3">
         <v>1</v>
@@ -3936,7 +3891,7 @@
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="K43" t="s">
         <v>6</v>
@@ -3951,13 +3906,13 @@
         <v>1</v>
       </c>
       <c r="O43" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="P43" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q43" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R43" t="s">
         <v>1</v>
@@ -3969,7 +3924,7 @@
         <v>12</v>
       </c>
       <c r="U43" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="V43" t="s">
         <v>1</v>
@@ -3986,19 +3941,19 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E44" s="2">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
@@ -4013,7 +3968,7 @@
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="K44" t="s">
         <v>6</v>
@@ -4031,22 +3986,22 @@
         <v>9</v>
       </c>
       <c r="P44" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q44" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R44" t="s">
         <v>1</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" t="s">
         <v>12</v>
       </c>
       <c r="U44" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="V44" t="s">
         <v>1</v>
@@ -4063,19 +4018,19 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B45" t="s">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D45" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="F45" s="3">
         <v>1</v>
@@ -4090,7 +4045,7 @@
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="K45" t="s">
         <v>6</v>
@@ -4105,25 +4060,25 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P45" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q45" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R45" t="s">
         <v>1</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="s">
         <v>12</v>
       </c>
       <c r="U45" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="V45" t="s">
         <v>1</v>
@@ -4140,19 +4095,19 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D46" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E46" s="2">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="F46" s="3">
         <v>1</v>
@@ -4167,7 +4122,7 @@
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="K46" t="s">
         <v>6</v>
@@ -4182,25 +4137,25 @@
         <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P46" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q46" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R46" t="s">
         <v>1</v>
       </c>
       <c r="S46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="s">
         <v>12</v>
       </c>
       <c r="U46" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="V46" t="s">
         <v>1</v>
@@ -4217,34 +4172,34 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D47" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="E47" s="2">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="F47" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I47" t="s">
         <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="K47" t="s">
         <v>6</v>
@@ -4259,25 +4214,25 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P47" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q47" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R47" t="s">
         <v>1</v>
       </c>
       <c r="S47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" t="s">
         <v>12</v>
       </c>
       <c r="U47" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="V47" t="s">
         <v>1</v>
@@ -4294,78 +4249,463 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="D48" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2">
+        <v>46139</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" t="s">
+        <v>122</v>
+      </c>
+      <c r="K48" t="s">
+        <v>6</v>
+      </c>
+      <c r="L48" t="s">
+        <v>7</v>
+      </c>
+      <c r="M48" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" t="s">
+        <v>1</v>
+      </c>
+      <c r="O48" t="s">
+        <v>9</v>
+      </c>
+      <c r="P48" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>30</v>
+      </c>
+      <c r="R48" t="s">
+        <v>1</v>
+      </c>
+      <c r="S48" s="3">
+        <v>1</v>
+      </c>
+      <c r="T48" t="s">
+        <v>12</v>
+      </c>
+      <c r="U48" t="s">
+        <v>31</v>
+      </c>
+      <c r="V48" t="s">
+        <v>1</v>
+      </c>
+      <c r="W48" t="s">
+        <v>1</v>
+      </c>
+      <c r="X48" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>123</v>
+      </c>
+      <c r="D49" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="2">
+        <v>46139</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" t="s">
+        <v>124</v>
+      </c>
+      <c r="K49" t="s">
+        <v>6</v>
+      </c>
+      <c r="L49" t="s">
+        <v>7</v>
+      </c>
+      <c r="M49" t="s">
+        <v>8</v>
+      </c>
+      <c r="N49" t="s">
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
+        <v>9</v>
+      </c>
+      <c r="P49" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>30</v>
+      </c>
+      <c r="R49" t="s">
+        <v>1</v>
+      </c>
+      <c r="S49" s="3">
+        <v>1</v>
+      </c>
+      <c r="T49" t="s">
+        <v>12</v>
+      </c>
+      <c r="U49" t="s">
+        <v>31</v>
+      </c>
+      <c r="V49" t="s">
+        <v>1</v>
+      </c>
+      <c r="W49" t="s">
+        <v>1</v>
+      </c>
+      <c r="X49" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25">
+      <c r="A50" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>125</v>
+      </c>
+      <c r="D50" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="2">
+        <v>46139</v>
+      </c>
+      <c r="F50" s="3">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>4</v>
+      </c>
+      <c r="J50" t="s">
+        <v>126</v>
+      </c>
+      <c r="K50" t="s">
+        <v>6</v>
+      </c>
+      <c r="L50" t="s">
+        <v>7</v>
+      </c>
+      <c r="M50" t="s">
+        <v>8</v>
+      </c>
+      <c r="N50" t="s">
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
+        <v>9</v>
+      </c>
+      <c r="P50" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>30</v>
+      </c>
+      <c r="R50" t="s">
+        <v>1</v>
+      </c>
+      <c r="S50" s="3">
+        <v>1</v>
+      </c>
+      <c r="T50" t="s">
+        <v>12</v>
+      </c>
+      <c r="U50" t="s">
+        <v>31</v>
+      </c>
+      <c r="V50" t="s">
+        <v>1</v>
+      </c>
+      <c r="W50" t="s">
+        <v>1</v>
+      </c>
+      <c r="X50" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" t="s">
+        <v>130</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="2">
+        <v>46140</v>
+      </c>
+      <c r="F51" s="3">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>4</v>
+      </c>
+      <c r="J51" t="s">
+        <v>28</v>
+      </c>
+      <c r="K51" t="s">
+        <v>6</v>
+      </c>
+      <c r="L51" t="s">
+        <v>7</v>
+      </c>
+      <c r="M51" t="s">
+        <v>8</v>
+      </c>
+      <c r="N51" t="s">
+        <v>1</v>
+      </c>
+      <c r="O51" t="s">
+        <v>24</v>
+      </c>
+      <c r="P51" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>30</v>
+      </c>
+      <c r="R51" t="s">
+        <v>1</v>
+      </c>
+      <c r="S51" s="3">
+        <v>1</v>
+      </c>
+      <c r="T51" t="s">
+        <v>12</v>
+      </c>
+      <c r="U51" t="s">
+        <v>31</v>
+      </c>
+      <c r="V51" t="s">
+        <v>1</v>
+      </c>
+      <c r="W51" t="s">
+        <v>1</v>
+      </c>
+      <c r="X51" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25">
+      <c r="A52" t="s">
+        <v>131</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="2">
         <v>46135</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F52" s="3">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1</v>
+      </c>
+      <c r="I52" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" t="s">
+        <v>133</v>
+      </c>
+      <c r="K52" t="s">
+        <v>6</v>
+      </c>
+      <c r="L52" t="s">
+        <v>7</v>
+      </c>
+      <c r="M52" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" t="s">
+        <v>1</v>
+      </c>
+      <c r="O52" t="s">
+        <v>48</v>
+      </c>
+      <c r="P52" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>30</v>
+      </c>
+      <c r="R52" t="s">
+        <v>1</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" t="s">
+        <v>12</v>
+      </c>
+      <c r="U52" t="s">
+        <v>1</v>
+      </c>
+      <c r="V52" t="s">
+        <v>1</v>
+      </c>
+      <c r="W52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25">
+      <c r="A53" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E53" s="2">
+        <v>46135</v>
+      </c>
+      <c r="F53" s="3">
         <v>-1</v>
       </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
         <v>-1</v>
       </c>
-      <c r="I48" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" t="s">
-        <v>150</v>
-      </c>
-      <c r="K48" t="s">
-        <v>6</v>
-      </c>
-      <c r="L48" t="s">
-        <v>7</v>
-      </c>
-      <c r="M48" t="s">
-        <v>8</v>
-      </c>
-      <c r="N48" t="s">
-        <v>1</v>
-      </c>
-      <c r="O48" t="s">
-        <v>25</v>
-      </c>
-      <c r="P48" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>11</v>
-      </c>
-      <c r="R48" t="s">
-        <v>1</v>
-      </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" t="s">
-        <v>12</v>
-      </c>
-      <c r="U48" t="s">
-        <v>1</v>
-      </c>
-      <c r="V48" t="s">
-        <v>1</v>
-      </c>
-      <c r="W48" t="s">
-        <v>1</v>
-      </c>
-      <c r="X48" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y48" t="s">
+      <c r="I53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J53" t="s">
+        <v>135</v>
+      </c>
+      <c r="K53" t="s">
+        <v>6</v>
+      </c>
+      <c r="L53" t="s">
+        <v>7</v>
+      </c>
+      <c r="M53" t="s">
+        <v>8</v>
+      </c>
+      <c r="N53" t="s">
+        <v>1</v>
+      </c>
+      <c r="O53" t="s">
+        <v>48</v>
+      </c>
+      <c r="P53" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>30</v>
+      </c>
+      <c r="R53" t="s">
+        <v>1</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" t="s">
+        <v>12</v>
+      </c>
+      <c r="U53" t="s">
+        <v>1</v>
+      </c>
+      <c r="V53" t="s">
+        <v>1</v>
+      </c>
+      <c r="W53" t="s">
+        <v>1</v>
+      </c>
+      <c r="X53" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="158">
   <si>
     <t>200006482</t>
   </si>
@@ -221,15 +221,6 @@
   </si>
   <si>
     <t>0107</t>
-  </si>
-  <si>
-    <t>200006573</t>
-  </si>
-  <si>
-    <t>3154001348A1</t>
-  </si>
-  <si>
-    <t>主軸前蓋_INC-H-90</t>
   </si>
   <si>
     <t>200006578</t>
@@ -598,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y53"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -630,79 +621,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="L1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="V1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -2179,10 +2170,10 @@
         <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2">
-        <v>46167</v>
+        <v>46106</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
@@ -2197,7 +2188,7 @@
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K21" t="s">
         <v>6</v>
@@ -2212,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="P21" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q21" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R21" t="s">
         <v>1</v>
@@ -2230,7 +2221,7 @@
         <v>12</v>
       </c>
       <c r="U21" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="V21" t="s">
         <v>1</v>
@@ -2247,7 +2238,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
@@ -2256,7 +2247,7 @@
         <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2">
         <v>46106</v>
@@ -2274,7 +2265,7 @@
         <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K22" t="s">
         <v>6</v>
@@ -2289,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="P22" t="s">
         <v>29</v>
@@ -2307,7 +2298,7 @@
         <v>12</v>
       </c>
       <c r="U22" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="V22" t="s">
         <v>1</v>
@@ -2324,16 +2315,16 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" t="s">
         <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>45</v>
       </c>
       <c r="E23" s="2">
         <v>46106</v>
@@ -2366,7 +2357,7 @@
         <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="P23" t="s">
         <v>29</v>
@@ -2378,13 +2369,13 @@
         <v>1</v>
       </c>
       <c r="S23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="s">
         <v>12</v>
       </c>
       <c r="U23" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="V23" t="s">
         <v>1</v>
@@ -2401,16 +2392,16 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2">
         <v>46106</v>
@@ -2428,7 +2419,7 @@
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s">
         <v>6</v>
@@ -2443,7 +2434,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P24" t="s">
         <v>29</v>
@@ -2478,16 +2469,16 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2">
         <v>46106</v>
@@ -2520,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P25" t="s">
         <v>29</v>
@@ -2555,7 +2546,7 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
@@ -2564,10 +2555,10 @@
         <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="E26" s="2">
-        <v>46106</v>
+        <v>46097</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
@@ -2582,7 +2573,7 @@
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s">
         <v>6</v>
@@ -2597,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="P26" t="s">
         <v>29</v>
@@ -2615,7 +2606,7 @@
         <v>12</v>
       </c>
       <c r="U26" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="V26" t="s">
         <v>1</v>
@@ -2632,19 +2623,19 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E27" s="2">
-        <v>46097</v>
+        <v>46161</v>
       </c>
       <c r="F27" s="3">
         <v>1</v>
@@ -2659,7 +2650,7 @@
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s">
         <v>6</v>
@@ -2674,7 +2665,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="P27" t="s">
         <v>29</v>
@@ -2686,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="s">
         <v>12</v>
@@ -2709,7 +2700,7 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
@@ -2718,7 +2709,7 @@
         <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="E28" s="2">
         <v>46161</v>
@@ -2736,7 +2727,7 @@
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s">
         <v>6</v>
@@ -2786,7 +2777,7 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
@@ -2795,7 +2786,7 @@
         <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="E29" s="2">
         <v>46161</v>
@@ -2813,7 +2804,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K29" t="s">
         <v>6</v>
@@ -2863,19 +2854,19 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
@@ -2905,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="P30" t="s">
         <v>29</v>
@@ -2949,10 +2940,10 @@
         <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2">
-        <v>46153</v>
+        <v>46134</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -2982,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="P31" t="s">
         <v>29</v>
@@ -3023,13 +3014,13 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s">
         <v>39</v>
       </c>
       <c r="E32" s="2">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -3044,7 +3035,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K32" t="s">
         <v>6</v>
@@ -3094,19 +3085,19 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" t="s">
         <v>109</v>
       </c>
-      <c r="B33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" t="s">
-        <v>39</v>
-      </c>
       <c r="E33" s="2">
-        <v>46136</v>
+        <v>46150</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
@@ -3121,7 +3112,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K33" t="s">
         <v>6</v>
@@ -3136,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P33" t="s">
         <v>29</v>
@@ -3154,7 +3145,7 @@
         <v>12</v>
       </c>
       <c r="U33" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="V33" t="s">
         <v>1</v>
@@ -3171,7 +3162,7 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
@@ -3186,10 +3177,10 @@
         <v>46150</v>
       </c>
       <c r="F34" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3">
         <v>1</v>
@@ -3213,7 +3204,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="P34" t="s">
         <v>29</v>
@@ -3225,13 +3216,13 @@
         <v>1</v>
       </c>
       <c r="S34" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T34" t="s">
         <v>12</v>
       </c>
       <c r="U34" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="V34" t="s">
         <v>1</v>
@@ -3248,25 +3239,25 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="E35" s="2">
-        <v>46150</v>
+        <v>46133</v>
       </c>
       <c r="F35" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
         <v>1</v>
@@ -3275,7 +3266,7 @@
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s">
         <v>6</v>
@@ -3290,7 +3281,7 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="P35" t="s">
         <v>29</v>
@@ -3302,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="S35" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T35" t="s">
         <v>12</v>
@@ -3325,7 +3316,7 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
@@ -3334,7 +3325,7 @@
         <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E36" s="2">
         <v>46133</v>
@@ -3352,7 +3343,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s">
         <v>6</v>
@@ -3402,19 +3393,19 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="E37" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -3429,7 +3420,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="K37" t="s">
         <v>6</v>
@@ -3444,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="P37" t="s">
         <v>29</v>
@@ -3479,35 +3470,35 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46139</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" t="s">
         <v>119</v>
       </c>
-      <c r="B38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="2">
-        <v>46134</v>
-      </c>
-      <c r="F38" s="3">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3">
-        <v>0</v>
-      </c>
-      <c r="H38" s="3">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>4</v>
-      </c>
-      <c r="J38" t="s">
-        <v>35</v>
-      </c>
       <c r="K38" t="s">
         <v>6</v>
       </c>
@@ -3521,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="P38" t="s">
         <v>29</v>
@@ -3556,16 +3547,16 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
         <v>120</v>
       </c>
-      <c r="B39" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>121</v>
-      </c>
       <c r="D39" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E39" s="2">
         <v>46139</v>
@@ -3583,7 +3574,7 @@
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K39" t="s">
         <v>6</v>
@@ -3633,16 +3624,16 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E40" s="2">
         <v>46139</v>
@@ -3660,7 +3651,7 @@
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K40" t="s">
         <v>6</v>
@@ -3710,16 +3701,16 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D41" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2">
         <v>46139</v>
@@ -3737,7 +3728,7 @@
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K41" t="s">
         <v>6</v>
@@ -3787,16 +3778,16 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D42" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E42" s="2">
         <v>46139</v>
@@ -3814,7 +3805,7 @@
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K42" t="s">
         <v>6</v>
@@ -3864,16 +3855,16 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E43" s="2">
         <v>46139</v>
@@ -3891,7 +3882,7 @@
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K43" t="s">
         <v>6</v>
@@ -3941,16 +3932,16 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="E44" s="2">
         <v>46139</v>
@@ -3968,7 +3959,7 @@
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K44" t="s">
         <v>6</v>
@@ -4018,16 +4009,16 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B45" t="s">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D45" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E45" s="2">
         <v>46139</v>
@@ -4045,7 +4036,7 @@
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K45" t="s">
         <v>6</v>
@@ -4095,16 +4086,16 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E46" s="2">
         <v>46139</v>
@@ -4122,7 +4113,7 @@
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K46" t="s">
         <v>6</v>
@@ -4172,16 +4163,16 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D47" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="E47" s="2">
         <v>46139</v>
@@ -4199,7 +4190,7 @@
         <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K47" t="s">
         <v>6</v>
@@ -4249,16 +4240,16 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E48" s="2">
         <v>46139</v>
@@ -4276,7 +4267,7 @@
         <v>4</v>
       </c>
       <c r="J48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K48" t="s">
         <v>6</v>
@@ -4326,16 +4317,16 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E49" s="2">
         <v>46139</v>
@@ -4353,7 +4344,7 @@
         <v>4</v>
       </c>
       <c r="J49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K49" t="s">
         <v>6</v>
@@ -4403,19 +4394,19 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B50" t="s">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
       </c>
       <c r="E50" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="F50" s="3">
         <v>1</v>
@@ -4430,7 +4421,7 @@
         <v>4</v>
       </c>
       <c r="J50" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="K50" t="s">
         <v>6</v>
@@ -4445,7 +4436,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="P50" t="s">
         <v>29</v>
@@ -4480,35 +4471,35 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>129</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="2">
+        <v>46135</v>
+      </c>
+      <c r="F51" s="3">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>4</v>
+      </c>
+      <c r="J51" t="s">
         <v>130</v>
       </c>
-      <c r="B51" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" t="s">
-        <v>26</v>
-      </c>
-      <c r="D51" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="2">
-        <v>46140</v>
-      </c>
-      <c r="F51" s="3">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3">
-        <v>1</v>
-      </c>
-      <c r="I51" t="s">
-        <v>4</v>
-      </c>
-      <c r="J51" t="s">
-        <v>28</v>
-      </c>
       <c r="K51" t="s">
         <v>6</v>
       </c>
@@ -4522,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="P51" t="s">
         <v>29</v>
@@ -4534,13 +4525,13 @@
         <v>1</v>
       </c>
       <c r="S51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" t="s">
         <v>12</v>
       </c>
       <c r="U51" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="V51" t="s">
         <v>1</v>
@@ -4557,34 +4548,34 @@
     </row>
     <row r="52" spans="1:25">
       <c r="A52" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
         <v>131</v>
       </c>
-      <c r="B52" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" t="s">
-        <v>132</v>
-      </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="E52" s="2">
         <v>46135</v>
       </c>
       <c r="F52" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I52" t="s">
         <v>4</v>
       </c>
       <c r="J52" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K52" t="s">
         <v>6</v>
@@ -4629,83 +4620,6 @@
         <v>1</v>
       </c>
       <c r="Y52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25">
-      <c r="A53" t="s">
-        <v>131</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" t="s">
-        <v>134</v>
-      </c>
-      <c r="D53" t="s">
-        <v>112</v>
-      </c>
-      <c r="E53" s="2">
-        <v>46135</v>
-      </c>
-      <c r="F53" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G53" s="3">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J53" t="s">
-        <v>135</v>
-      </c>
-      <c r="K53" t="s">
-        <v>6</v>
-      </c>
-      <c r="L53" t="s">
-        <v>7</v>
-      </c>
-      <c r="M53" t="s">
-        <v>8</v>
-      </c>
-      <c r="N53" t="s">
-        <v>1</v>
-      </c>
-      <c r="O53" t="s">
-        <v>48</v>
-      </c>
-      <c r="P53" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>30</v>
-      </c>
-      <c r="R53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S53" s="3">
-        <v>0</v>
-      </c>
-      <c r="T53" t="s">
-        <v>12</v>
-      </c>
-      <c r="U53" t="s">
-        <v>1</v>
-      </c>
-      <c r="V53" t="s">
-        <v>1</v>
-      </c>
-      <c r="W53" t="s">
-        <v>1</v>
-      </c>
-      <c r="X53" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y53" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="200">
   <si>
     <t>200006482</t>
   </si>
@@ -76,213 +76,177 @@
     <t>活塞,A軸法蘭前部_d130*D186*129.5L</t>
   </si>
   <si>
-    <t>3209000356A0</t>
+    <t>200006500</t>
+  </si>
+  <si>
+    <t>3214000272C0</t>
+  </si>
+  <si>
+    <t>0360</t>
+  </si>
+  <si>
+    <t>吊桿_MVP-10</t>
+  </si>
+  <si>
+    <t>0102</t>
+  </si>
+  <si>
+    <t>1F004</t>
+  </si>
+  <si>
+    <t>組件課</t>
+  </si>
+  <si>
+    <t>9804</t>
+  </si>
+  <si>
+    <t>200006511</t>
+  </si>
+  <si>
+    <t>8814001214D3</t>
+  </si>
+  <si>
+    <t>0210</t>
+  </si>
+  <si>
+    <t>機頭加工圖,G6K_HCMC-1682</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>200006554</t>
+  </si>
+  <si>
+    <t>080100035602</t>
+  </si>
+  <si>
+    <t>0050</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BBT50,0045</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>0802</t>
+  </si>
+  <si>
+    <t>200006569</t>
+  </si>
+  <si>
+    <t>2069000033B0</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>螺旋斜齒輪,OGIC_31T-L-90,G5K</t>
+  </si>
+  <si>
+    <t>321000041300</t>
+  </si>
+  <si>
+    <t>0120</t>
+  </si>
+  <si>
+    <t>傳動刀把_7/24-154L萬向頭</t>
+  </si>
+  <si>
+    <t>2069000034B0</t>
+  </si>
+  <si>
+    <t>0160</t>
+  </si>
+  <si>
+    <t>螺旋斜齒輪,OGIC_31T-R-90,G5K</t>
+  </si>
+  <si>
+    <t>2069000031B0</t>
+  </si>
+  <si>
+    <t>0280</t>
+  </si>
+  <si>
+    <t>螺旋斜齒輪,OGIC_35T-R-90,G5K</t>
+  </si>
+  <si>
+    <t>2069000032A0</t>
   </si>
   <si>
     <t>0350</t>
   </si>
   <si>
-    <t>#50 主軸,CTS,BBT_D143*368L</t>
-  </si>
-  <si>
-    <t>0102</t>
-  </si>
-  <si>
-    <t>200006500</t>
-  </si>
-  <si>
-    <t>3214000272C0</t>
-  </si>
-  <si>
-    <t>0360</t>
-  </si>
-  <si>
-    <t>吊桿_MVP-10</t>
-  </si>
-  <si>
-    <t>1F004</t>
-  </si>
-  <si>
-    <t>組件課</t>
-  </si>
-  <si>
-    <t>9804</t>
-  </si>
-  <si>
-    <t>200006511</t>
-  </si>
-  <si>
-    <t>8814001214D3</t>
-  </si>
-  <si>
-    <t>0210</t>
-  </si>
-  <si>
-    <t>機頭加工圖,G6K_HCMC-1682</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>200006554</t>
-  </si>
-  <si>
-    <t>080100035602</t>
-  </si>
-  <si>
-    <t>0050</t>
-  </si>
-  <si>
-    <t>G6K 主軸,021327_BBT50,0045</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>0802</t>
-  </si>
-  <si>
-    <t>200006569</t>
-  </si>
-  <si>
-    <t>2069000033B0</t>
-  </si>
-  <si>
-    <t>0110</t>
-  </si>
-  <si>
-    <t>螺旋斜齒輪,OGIC_31T-L-90,G5K</t>
-  </si>
-  <si>
-    <t>321000041300</t>
-  </si>
-  <si>
-    <t>0120</t>
-  </si>
-  <si>
-    <t>傳動刀把_7/24-154L萬向頭</t>
-  </si>
-  <si>
-    <t>2069000034B0</t>
-  </si>
-  <si>
-    <t>0160</t>
-  </si>
-  <si>
-    <t>螺旋斜齒輪,OGIC_31T-R-90,G5K</t>
-  </si>
-  <si>
-    <t>3058000838A0</t>
+    <t>螺旋斜齒輪,OGIC_35T-L-90度</t>
+  </si>
+  <si>
+    <t>200006575</t>
+  </si>
+  <si>
+    <t>892300066800</t>
+  </si>
+  <si>
+    <t>0480</t>
+  </si>
+  <si>
+    <t>出貨固定板_EA/EAY,HF-A90/AE/M90/MU</t>
+  </si>
+  <si>
+    <t>0107</t>
+  </si>
+  <si>
+    <t>200006578</t>
+  </si>
+  <si>
+    <t>080100021502</t>
+  </si>
+  <si>
+    <t>0020</t>
+  </si>
+  <si>
+    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
+  </si>
+  <si>
+    <t>3210000386B0</t>
+  </si>
+  <si>
+    <t>傳動軸_d50*D103*774L</t>
+  </si>
+  <si>
+    <t>999800001600</t>
+  </si>
+  <si>
+    <t>0250</t>
+  </si>
+  <si>
+    <t>內藏式主軸轉子組,FANUC_10K807N,021458</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>610400005000</t>
+  </si>
+  <si>
+    <t>0260</t>
+  </si>
+  <si>
+    <t>內藏式主軸轉子加工圖,FANUC_A06B-2726-B651#2231</t>
+  </si>
+  <si>
+    <t>0126</t>
+  </si>
+  <si>
+    <t>610400002700</t>
   </si>
   <si>
     <t>0270</t>
   </si>
   <si>
-    <t>軸承箱,A軸後端用_d90*D180*99L,溫降案</t>
-  </si>
-  <si>
-    <t>2069000031B0</t>
-  </si>
-  <si>
-    <t>0280</t>
-  </si>
-  <si>
-    <t>螺旋斜齒輪,OGIC_35T-R-90,G5K</t>
-  </si>
-  <si>
-    <t>8420002368A0</t>
-  </si>
-  <si>
-    <t>襯套,C軸下_D201*d185*H21</t>
-  </si>
-  <si>
-    <t>2069000032A0</t>
-  </si>
-  <si>
-    <t>螺旋斜齒輪,OGIC_35T-L-90度</t>
-  </si>
-  <si>
-    <t>4060000109B0</t>
-  </si>
-  <si>
-    <t>0730</t>
-  </si>
-  <si>
-    <t>活塞外套,C軸_d180*D240*H125,G5K</t>
-  </si>
-  <si>
-    <t>8923000735B0</t>
-  </si>
-  <si>
-    <t>0740</t>
-  </si>
-  <si>
-    <t>固定板,C軸下_D227*d197*2t,G5K</t>
-  </si>
-  <si>
-    <t>0107</t>
-  </si>
-  <si>
-    <t>200006578</t>
-  </si>
-  <si>
-    <t>080100021502</t>
-  </si>
-  <si>
-    <t>0020</t>
-  </si>
-  <si>
-    <t>D10K 主軸,021454_BBT50,M50E,C045</t>
-  </si>
-  <si>
-    <t>3210000386B0</t>
-  </si>
-  <si>
-    <t>傳動軸_d50*D103*774L</t>
-  </si>
-  <si>
-    <t>999800001600</t>
-  </si>
-  <si>
-    <t>0250</t>
-  </si>
-  <si>
-    <t>內藏式主軸轉子組,FANUC_10K807N,021458</t>
-  </si>
-  <si>
-    <t>0100</t>
-  </si>
-  <si>
-    <t>610400005000</t>
-  </si>
-  <si>
-    <t>0260</t>
-  </si>
-  <si>
-    <t>內藏式主軸轉子加工圖,FANUC_A06B-2726-B651#2231</t>
-  </si>
-  <si>
-    <t>0126</t>
-  </si>
-  <si>
-    <t>610400002700</t>
-  </si>
-  <si>
     <t>內藏式主軸轉子,FANUC_A06B-2726-B651#2231</t>
   </si>
   <si>
-    <t>200006579</t>
-  </si>
-  <si>
-    <t>3227000145A0</t>
-  </si>
-  <si>
-    <t>0500</t>
-  </si>
-  <si>
-    <t>撓性聯軸器,主軸,Mayr_100/953.221/50/50S</t>
-  </si>
-  <si>
     <t>200006624</t>
   </si>
   <si>
@@ -322,18 +286,6 @@
     <t>增壓缸底座_MVP-13P</t>
   </si>
   <si>
-    <t>200006671</t>
-  </si>
-  <si>
-    <t>8814001455A2</t>
-  </si>
-  <si>
-    <t>機頭加工圖,#40P短套筒_MVP-11</t>
-  </si>
-  <si>
-    <t>200006675</t>
-  </si>
-  <si>
     <t>200006676</t>
   </si>
   <si>
@@ -346,70 +298,244 @@
     <t>D12K 主軸,021274_BBT50,M50,C045</t>
   </si>
   <si>
-    <t>8311000404A0</t>
+    <t>200006686</t>
+  </si>
+  <si>
+    <t>0370</t>
+  </si>
+  <si>
+    <t>200006687</t>
+  </si>
+  <si>
+    <t>200006690</t>
+  </si>
+  <si>
+    <t>3215000505A0</t>
+  </si>
+  <si>
+    <t>打刀承片_BT50/CTS-011</t>
+  </si>
+  <si>
+    <t>3215000514B0</t>
+  </si>
+  <si>
+    <t>打刀公環_BT50/CTS-009</t>
+  </si>
+  <si>
+    <t>3215000610B1</t>
+  </si>
+  <si>
+    <t>打刀母環,#50G/P6K_CTS,#50G/P6K</t>
+  </si>
+  <si>
+    <t>200006691</t>
+  </si>
+  <si>
+    <t>200006692</t>
+  </si>
+  <si>
+    <t>200006700</t>
+  </si>
+  <si>
+    <t>200006702</t>
+  </si>
+  <si>
+    <t>200006703</t>
+  </si>
+  <si>
+    <t>3058000776B0</t>
+  </si>
+  <si>
+    <t>傳動軸承箱,中_D215-d100,P190*134L-8</t>
+  </si>
+  <si>
+    <t>8814001386B1</t>
+  </si>
+  <si>
+    <t>機頭加工圖,G8K,Z780_HAS2215,4線軌,BT50</t>
+  </si>
+  <si>
+    <t>200006704</t>
+  </si>
+  <si>
+    <t>4023000016B0</t>
   </si>
   <si>
     <t>0090</t>
   </si>
   <si>
-    <t>前油箱蓋板_270x200*15</t>
-  </si>
-  <si>
-    <t>200006686</t>
-  </si>
-  <si>
-    <t>0370</t>
-  </si>
-  <si>
-    <t>200006687</t>
-  </si>
-  <si>
-    <t>200006690</t>
-  </si>
-  <si>
-    <t>3215000505A0</t>
-  </si>
-  <si>
-    <t>打刀承片_BT50/CTS-011</t>
-  </si>
-  <si>
-    <t>3215000514B0</t>
-  </si>
-  <si>
-    <t>打刀公環_BT50/CTS-009</t>
-  </si>
-  <si>
-    <t>3215000610B1</t>
-  </si>
-  <si>
-    <t>打刀母環,#50G/P6K_CTS,#50G/P6K</t>
-  </si>
-  <si>
-    <t>200006691</t>
-  </si>
-  <si>
-    <t>200006692</t>
-  </si>
-  <si>
-    <t>200006700</t>
-  </si>
-  <si>
-    <t>200006702</t>
-  </si>
-  <si>
-    <t>630000354</t>
-  </si>
-  <si>
-    <t>3227000130A0</t>
-  </si>
-  <si>
-    <t>撓性聯軸器,主軸,GS42P_98ShA,6.0-d48,6.0-d55</t>
-  </si>
-  <si>
-    <t>3227000129A0</t>
-  </si>
-  <si>
-    <t>撓性聯軸器,主軸,GS42P_98ShA,6.0-d48,6.0-d48</t>
+    <t>油壓缸/臻賞_50-1044/HB-45</t>
+  </si>
+  <si>
+    <t>1092001297A0</t>
+  </si>
+  <si>
+    <t>平行鍵/雙圓頭_16*6*90L</t>
+  </si>
+  <si>
+    <t>8311000418A0</t>
+  </si>
+  <si>
+    <t>0230</t>
+  </si>
+  <si>
+    <t>機頭蓋板_276Lx186Wx10t,EA機頭齒輪箱用</t>
+  </si>
+  <si>
+    <t>8819000023A0</t>
+  </si>
+  <si>
+    <t>齒輪箱加工鑽孔圖_SW-G8K</t>
+  </si>
+  <si>
+    <t>200006706</t>
+  </si>
+  <si>
+    <t>8420002326A0</t>
+  </si>
+  <si>
+    <t>主軸承箱外蓋_d175*D185*108,HSA</t>
+  </si>
+  <si>
+    <t>8420002332A1</t>
+  </si>
+  <si>
+    <t>0400</t>
+  </si>
+  <si>
+    <t>間隔環,長內_d90*D116*213,HSA2215</t>
+  </si>
+  <si>
+    <t>200006710</t>
+  </si>
+  <si>
+    <t>8310000678A0</t>
+  </si>
+  <si>
+    <t>0060</t>
+  </si>
+  <si>
+    <t>馬達座,D38直結主軸用_MVP-1060</t>
+  </si>
+  <si>
+    <t>200006714</t>
+  </si>
+  <si>
+    <t>200006715</t>
+  </si>
+  <si>
+    <t>200006716</t>
+  </si>
+  <si>
+    <t>200006717</t>
+  </si>
+  <si>
+    <t>200006718</t>
+  </si>
+  <si>
+    <t>200006719</t>
+  </si>
+  <si>
+    <t>8423000105A0</t>
+  </si>
+  <si>
+    <t>吹氣環_d89.5*D99.5*H6.5</t>
+  </si>
+  <si>
+    <t>3154001562A0</t>
+  </si>
+  <si>
+    <t>主軸前蓋_d89.5*D155*27L</t>
+  </si>
+  <si>
+    <t>3209000343A1</t>
+  </si>
+  <si>
+    <t>0340</t>
+  </si>
+  <si>
+    <t>主軸/直結式實心馬達_直結式,BBT40,10K~15KRPM</t>
+  </si>
+  <si>
+    <t>200006722</t>
+  </si>
+  <si>
+    <t>111400008500</t>
+  </si>
+  <si>
+    <t>盤型彈簧_φ56*φ28.5*3t</t>
+  </si>
+  <si>
+    <t>8420002433A0</t>
+  </si>
+  <si>
+    <t>間隔環,長_D116*d90*222H,SW</t>
+  </si>
+  <si>
+    <t>3154001546B0</t>
+  </si>
+  <si>
+    <t>0380</t>
+  </si>
+  <si>
+    <t>主軸前蓋_d123*D188*55L</t>
+  </si>
+  <si>
+    <t>200006730</t>
+  </si>
+  <si>
+    <t>3058000694A1</t>
+  </si>
+  <si>
+    <t>軸承箱/換檔用_SW-x26</t>
+  </si>
+  <si>
+    <t>0180</t>
+  </si>
+  <si>
+    <t>3058000777A2</t>
+  </si>
+  <si>
+    <t>0300</t>
+  </si>
+  <si>
+    <t>傳動軸承箱,上_D159-d52,P139*82L-8</t>
+  </si>
+  <si>
+    <t>200006733</t>
+  </si>
+  <si>
+    <t>8010000088A2</t>
+  </si>
+  <si>
+    <t>0040</t>
+  </si>
+  <si>
+    <t>夾刀限動開關凸塊_HB120-22</t>
+  </si>
+  <si>
+    <t>080100022704</t>
+  </si>
+  <si>
+    <t>G6K 主軸,021327_BT50,0045</t>
+  </si>
+  <si>
+    <t>0080</t>
+  </si>
+  <si>
+    <t>3216000148B1</t>
+  </si>
+  <si>
+    <t>0170</t>
+  </si>
+  <si>
+    <t>變速叉_d127,P155,HSA-x23</t>
+  </si>
+  <si>
+    <t>8814001070B2</t>
+  </si>
+  <si>
+    <t>機頭滑座加工圖,Z軸780_G6K,Z780</t>
   </si>
   <si>
     <t>訂單</t>
@@ -589,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y52"/>
+  <dimension ref="A1:Y76"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -610,7 +736,7 @@
     <col min="16" max="16" bestFit="1" width="7" customWidth="1"/>
     <col min="17" max="17" bestFit="1" width="8" customWidth="1"/>
     <col min="18" max="18" bestFit="1" width="6" customWidth="1"/>
-    <col min="19" max="19" bestFit="1" width="10" customWidth="1"/>
+    <col min="19" max="19" bestFit="1" width="11" customWidth="1"/>
     <col min="20" max="20" bestFit="1" width="6" customWidth="1"/>
     <col min="21" max="21" bestFit="1" width="6" customWidth="1"/>
     <col min="22" max="22" bestFit="1" width="6" customWidth="1"/>
@@ -621,79 +747,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -929,19 +1055,19 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2">
-        <v>46125</v>
+        <v>46155</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -956,7 +1082,7 @@
         <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
         <v>6</v>
@@ -971,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P5" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R5" t="s">
         <v>1</v>
@@ -989,7 +1115,7 @@
         <v>12</v>
       </c>
       <c r="U5" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V5" t="s">
         <v>1</v>
@@ -1006,67 +1132,67 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46146</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="Q6" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2">
-        <v>46155</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="R6" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6" s="3">
+        <v>1</v>
+      </c>
+      <c r="T6" t="s">
+        <v>12</v>
+      </c>
+      <c r="U6" t="s">
         <v>28</v>
-      </c>
-      <c r="K6" t="s">
-        <v>6</v>
-      </c>
-      <c r="L6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" t="s">
-        <v>1</v>
-      </c>
-      <c r="O6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>30</v>
-      </c>
-      <c r="R6" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="3">
-        <v>1</v>
-      </c>
-      <c r="T6" t="s">
-        <v>12</v>
-      </c>
-      <c r="U6" t="s">
-        <v>31</v>
       </c>
       <c r="V6" t="s">
         <v>1</v>
@@ -1083,19 +1209,19 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2">
-        <v>46146</v>
+        <v>46155</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1110,7 +1236,7 @@
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K7" t="s">
         <v>6</v>
@@ -1125,13 +1251,13 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R7" t="s">
         <v>1</v>
@@ -1143,7 +1269,7 @@
         <v>12</v>
       </c>
       <c r="U7" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="V7" t="s">
         <v>1</v>
@@ -1160,19 +1286,19 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2">
-        <v>46155</v>
+        <v>46135</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -1187,7 +1313,7 @@
         <v>4</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K8" t="s">
         <v>6</v>
@@ -1202,25 +1328,25 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="P8" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="R8" t="s">
         <v>1</v>
       </c>
       <c r="S8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="s">
         <v>12</v>
       </c>
       <c r="U8" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="V8" t="s">
         <v>1</v>
@@ -1237,7 +1363,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -1291,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="s">
         <v>12</v>
@@ -1314,7 +1440,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
@@ -1368,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="s">
         <v>12</v>
@@ -1391,16 +1517,16 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2">
         <v>46135</v>
@@ -1418,7 +1544,7 @@
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="K11" t="s">
         <v>6</v>
@@ -1445,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="S11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="s">
         <v>12</v>
@@ -1468,16 +1594,16 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2">
         <v>46135</v>
@@ -1495,7 +1621,7 @@
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
         <v>6</v>
@@ -1545,16 +1671,16 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2">
         <v>46135</v>
@@ -1572,7 +1698,7 @@
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="K13" t="s">
         <v>6</v>
@@ -1599,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="S13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="s">
         <v>12</v>
@@ -1622,16 +1748,16 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2">
         <v>46135</v>
@@ -1649,7 +1775,7 @@
         <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s">
         <v>6</v>
@@ -1699,16 +1825,16 @@
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2">
         <v>46135</v>
@@ -1726,7 +1852,7 @@
         <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K15" t="s">
         <v>6</v>
@@ -1753,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="S15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="s">
         <v>12</v>
@@ -1776,19 +1902,19 @@
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2">
-        <v>46135</v>
+        <v>46167</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
@@ -1803,7 +1929,7 @@
         <v>4</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="K16" t="s">
         <v>6</v>
@@ -1818,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="P16" t="s">
         <v>10</v>
@@ -1853,19 +1979,19 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E17" s="2">
-        <v>46135</v>
+        <v>46106</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -1880,7 +2006,7 @@
         <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K17" t="s">
         <v>6</v>
@@ -1895,13 +2021,13 @@
         <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="P17" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R17" t="s">
         <v>1</v>
@@ -1913,7 +2039,7 @@
         <v>12</v>
       </c>
       <c r="U17" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="V17" t="s">
         <v>1</v>
@@ -1930,19 +2056,19 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E18" s="2">
-        <v>46135</v>
+        <v>46106</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -1957,7 +2083,7 @@
         <v>4</v>
       </c>
       <c r="J18" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K18" t="s">
         <v>6</v>
@@ -1975,10 +2101,10 @@
         <v>9</v>
       </c>
       <c r="P18" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q18" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R18" t="s">
         <v>1</v>
@@ -1990,7 +2116,7 @@
         <v>12</v>
       </c>
       <c r="U18" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V18" t="s">
         <v>1</v>
@@ -2007,19 +2133,19 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2">
-        <v>46135</v>
+        <v>46106</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
@@ -2034,7 +2160,7 @@
         <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K19" t="s">
         <v>6</v>
@@ -2049,25 +2175,25 @@
         <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R19" t="s">
         <v>1</v>
       </c>
       <c r="S19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="s">
         <v>12</v>
       </c>
       <c r="U19" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V19" t="s">
         <v>1</v>
@@ -2084,19 +2210,19 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2">
-        <v>46135</v>
+        <v>46106</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
@@ -2111,7 +2237,7 @@
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K20" t="s">
         <v>6</v>
@@ -2126,25 +2252,25 @@
         <v>1</v>
       </c>
       <c r="O20" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P20" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="R20" t="s">
         <v>1</v>
       </c>
       <c r="S20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="s">
         <v>12</v>
       </c>
       <c r="U20" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V20" t="s">
         <v>1</v>
@@ -2161,16 +2287,16 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E21" s="2">
         <v>46106</v>
@@ -2188,7 +2314,7 @@
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s">
         <v>6</v>
@@ -2203,25 +2329,25 @@
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="P21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R21" t="s">
         <v>1</v>
       </c>
       <c r="S21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="s">
         <v>12</v>
       </c>
       <c r="U21" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="V21" t="s">
         <v>1</v>
@@ -2238,19 +2364,19 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2">
-        <v>46106</v>
+        <v>46161</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
@@ -2265,7 +2391,7 @@
         <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K22" t="s">
         <v>6</v>
@@ -2280,13 +2406,13 @@
         <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R22" t="s">
         <v>1</v>
@@ -2298,7 +2424,7 @@
         <v>12</v>
       </c>
       <c r="U22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V22" t="s">
         <v>1</v>
@@ -2315,19 +2441,19 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="E23" s="2">
-        <v>46106</v>
+        <v>46161</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
@@ -2342,7 +2468,7 @@
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K23" t="s">
         <v>6</v>
@@ -2357,25 +2483,25 @@
         <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="P23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R23" t="s">
         <v>1</v>
       </c>
       <c r="S23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="s">
         <v>12</v>
       </c>
       <c r="U23" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="V23" t="s">
         <v>1</v>
@@ -2392,19 +2518,19 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E24" s="2">
-        <v>46106</v>
+        <v>46161</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
@@ -2419,7 +2545,7 @@
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s">
         <v>6</v>
@@ -2434,25 +2560,25 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="P24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q24" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R24" t="s">
         <v>1</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="s">
         <v>12</v>
       </c>
       <c r="U24" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="V24" t="s">
         <v>1</v>
@@ -2469,19 +2595,19 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" t="s">
         <v>70</v>
       </c>
-      <c r="B25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" t="s">
-        <v>54</v>
-      </c>
       <c r="E25" s="2">
-        <v>46106</v>
+        <v>46153</v>
       </c>
       <c r="F25" s="3">
         <v>1</v>
@@ -2496,7 +2622,7 @@
         <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s">
         <v>6</v>
@@ -2511,25 +2637,25 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="P25" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R25" t="s">
         <v>1</v>
       </c>
       <c r="S25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="s">
         <v>12</v>
       </c>
       <c r="U25" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="V25" t="s">
         <v>1</v>
@@ -2546,19 +2672,19 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E26" s="2">
-        <v>46097</v>
+        <v>46150</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
@@ -2573,7 +2699,7 @@
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s">
         <v>6</v>
@@ -2588,25 +2714,25 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="P26" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q26" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R26" t="s">
         <v>1</v>
       </c>
       <c r="S26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="s">
         <v>12</v>
       </c>
       <c r="U26" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="V26" t="s">
         <v>1</v>
@@ -2623,19 +2749,19 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E27" s="2">
-        <v>46161</v>
+        <v>46133</v>
       </c>
       <c r="F27" s="3">
         <v>1</v>
@@ -2650,7 +2776,7 @@
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K27" t="s">
         <v>6</v>
@@ -2665,13 +2791,13 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P27" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q27" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R27" t="s">
         <v>1</v>
@@ -2683,7 +2809,7 @@
         <v>12</v>
       </c>
       <c r="U27" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V27" t="s">
         <v>1</v>
@@ -2700,56 +2826,56 @@
     </row>
     <row r="28" spans="1:25">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="2">
+        <v>46133</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J28" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" t="s">
+        <v>6</v>
+      </c>
+      <c r="L28" t="s">
+        <v>7</v>
+      </c>
+      <c r="M28" t="s">
+        <v>8</v>
+      </c>
+      <c r="N28" t="s">
+        <v>1</v>
+      </c>
+      <c r="O28" t="s">
+        <v>25</v>
+      </c>
+      <c r="P28" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="2">
-        <v>46161</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1</v>
-      </c>
-      <c r="I28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J28" t="s">
-        <v>95</v>
-      </c>
-      <c r="K28" t="s">
-        <v>6</v>
-      </c>
-      <c r="L28" t="s">
-        <v>7</v>
-      </c>
-      <c r="M28" t="s">
-        <v>8</v>
-      </c>
-      <c r="N28" t="s">
-        <v>1</v>
-      </c>
-      <c r="O28" t="s">
-        <v>24</v>
-      </c>
-      <c r="P28" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>30</v>
-      </c>
       <c r="R28" t="s">
         <v>1</v>
       </c>
@@ -2760,7 +2886,7 @@
         <v>12</v>
       </c>
       <c r="U28" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V28" t="s">
         <v>1</v>
@@ -2777,19 +2903,19 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="E29" s="2">
-        <v>46161</v>
+        <v>46134</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
@@ -2804,7 +2930,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="K29" t="s">
         <v>6</v>
@@ -2819,13 +2945,13 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P29" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R29" t="s">
         <v>1</v>
@@ -2837,7 +2963,7 @@
         <v>12</v>
       </c>
       <c r="U29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V29" t="s">
         <v>1</v>
@@ -2854,34 +2980,34 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="2">
+        <v>46139</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>4</v>
+      </c>
+      <c r="J30" t="s">
         <v>100</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="2">
-        <v>46153</v>
-      </c>
-      <c r="F30" s="3">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3">
-        <v>1</v>
-      </c>
-      <c r="I30" t="s">
-        <v>4</v>
-      </c>
-      <c r="J30" t="s">
-        <v>102</v>
       </c>
       <c r="K30" t="s">
         <v>6</v>
@@ -2899,10 +3025,10 @@
         <v>9</v>
       </c>
       <c r="P30" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q30" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R30" t="s">
         <v>1</v>
@@ -2914,7 +3040,7 @@
         <v>12</v>
       </c>
       <c r="U30" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V30" t="s">
         <v>1</v>
@@ -2931,19 +3057,19 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -2958,7 +3084,7 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K31" t="s">
         <v>6</v>
@@ -2973,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="P31" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q31" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
         <v>1</v>
@@ -2991,7 +3117,7 @@
         <v>12</v>
       </c>
       <c r="U31" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V31" t="s">
         <v>1</v>
@@ -3008,35 +3134,35 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="2">
+        <v>46139</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" t="s">
         <v>104</v>
       </c>
-      <c r="D32" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="2">
-        <v>46136</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1</v>
-      </c>
-      <c r="I32" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" t="s">
-        <v>105</v>
-      </c>
       <c r="K32" t="s">
         <v>6</v>
       </c>
@@ -3050,13 +3176,13 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="P32" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R32" t="s">
         <v>1</v>
@@ -3068,7 +3194,7 @@
         <v>12</v>
       </c>
       <c r="U32" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V32" t="s">
         <v>1</v>
@@ -3085,19 +3211,19 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="E33" s="2">
-        <v>46150</v>
+        <v>46139</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
@@ -3112,7 +3238,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K33" t="s">
         <v>6</v>
@@ -3127,13 +3253,13 @@
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="P33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q33" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R33" t="s">
         <v>1</v>
@@ -3145,7 +3271,7 @@
         <v>12</v>
       </c>
       <c r="U33" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="V33" t="s">
         <v>1</v>
@@ -3162,25 +3288,25 @@
     </row>
     <row r="34" spans="1:25">
       <c r="A34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="E34" s="2">
-        <v>46150</v>
+        <v>46139</v>
       </c>
       <c r="F34" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="3">
         <v>1</v>
@@ -3189,7 +3315,7 @@
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="K34" t="s">
         <v>6</v>
@@ -3207,22 +3333,22 @@
         <v>9</v>
       </c>
       <c r="P34" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q34" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R34" t="s">
         <v>1</v>
       </c>
       <c r="S34" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T34" t="s">
         <v>12</v>
       </c>
       <c r="U34" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V34" t="s">
         <v>1</v>
@@ -3239,19 +3365,19 @@
     </row>
     <row r="35" spans="1:25">
       <c r="A35" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D35" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="E35" s="2">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
@@ -3266,7 +3392,7 @@
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="K35" t="s">
         <v>6</v>
@@ -3281,13 +3407,13 @@
         <v>1</v>
       </c>
       <c r="O35" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="P35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q35" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R35" t="s">
         <v>1</v>
@@ -3299,7 +3425,7 @@
         <v>12</v>
       </c>
       <c r="U35" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V35" t="s">
         <v>1</v>
@@ -3316,19 +3442,19 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="E36" s="2">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="F36" s="3">
         <v>1</v>
@@ -3343,7 +3469,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K36" t="s">
         <v>6</v>
@@ -3358,13 +3484,13 @@
         <v>1</v>
       </c>
       <c r="O36" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="P36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R36" t="s">
         <v>1</v>
@@ -3376,7 +3502,7 @@
         <v>12</v>
       </c>
       <c r="U36" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V36" t="s">
         <v>1</v>
@@ -3393,19 +3519,19 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E37" s="2">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="F37" s="3">
         <v>1</v>
@@ -3420,7 +3546,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="K37" t="s">
         <v>6</v>
@@ -3435,13 +3561,13 @@
         <v>1</v>
       </c>
       <c r="O37" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="P37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q37" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R37" t="s">
         <v>1</v>
@@ -3453,7 +3579,7 @@
         <v>12</v>
       </c>
       <c r="U37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V37" t="s">
         <v>1</v>
@@ -3470,16 +3596,16 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="E38" s="2">
         <v>46139</v>
@@ -3497,7 +3623,7 @@
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="K38" t="s">
         <v>6</v>
@@ -3515,10 +3641,10 @@
         <v>9</v>
       </c>
       <c r="P38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q38" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R38" t="s">
         <v>1</v>
@@ -3530,7 +3656,7 @@
         <v>12</v>
       </c>
       <c r="U38" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V38" t="s">
         <v>1</v>
@@ -3547,16 +3673,16 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E39" s="2">
         <v>46139</v>
@@ -3574,7 +3700,7 @@
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="K39" t="s">
         <v>6</v>
@@ -3592,10 +3718,10 @@
         <v>9</v>
       </c>
       <c r="P39" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q39" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R39" t="s">
         <v>1</v>
@@ -3607,7 +3733,7 @@
         <v>12</v>
       </c>
       <c r="U39" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V39" t="s">
         <v>1</v>
@@ -3624,16 +3750,16 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E40" s="2">
         <v>46139</v>
@@ -3651,7 +3777,7 @@
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="K40" t="s">
         <v>6</v>
@@ -3669,10 +3795,10 @@
         <v>9</v>
       </c>
       <c r="P40" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q40" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R40" t="s">
         <v>1</v>
@@ -3684,7 +3810,7 @@
         <v>12</v>
       </c>
       <c r="U40" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V40" t="s">
         <v>1</v>
@@ -3701,16 +3827,16 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="E41" s="2">
         <v>46139</v>
@@ -3728,7 +3854,7 @@
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="K41" t="s">
         <v>6</v>
@@ -3746,10 +3872,10 @@
         <v>9</v>
       </c>
       <c r="P41" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q41" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R41" t="s">
         <v>1</v>
@@ -3761,7 +3887,7 @@
         <v>12</v>
       </c>
       <c r="U41" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V41" t="s">
         <v>1</v>
@@ -3778,19 +3904,19 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E42" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="F42" s="3">
         <v>1</v>
@@ -3805,7 +3931,7 @@
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="K42" t="s">
         <v>6</v>
@@ -3820,13 +3946,13 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P42" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q42" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R42" t="s">
         <v>1</v>
@@ -3838,7 +3964,7 @@
         <v>12</v>
       </c>
       <c r="U42" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V42" t="s">
         <v>1</v>
@@ -3855,19 +3981,19 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E43" s="2">
-        <v>46139</v>
+        <v>46183</v>
       </c>
       <c r="F43" s="3">
         <v>1</v>
@@ -3882,7 +4008,7 @@
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="K43" t="s">
         <v>6</v>
@@ -3900,10 +4026,10 @@
         <v>9</v>
       </c>
       <c r="P43" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q43" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R43" t="s">
         <v>1</v>
@@ -3915,7 +4041,7 @@
         <v>12</v>
       </c>
       <c r="U43" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V43" t="s">
         <v>1</v>
@@ -3932,19 +4058,19 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E44" s="2">
-        <v>46139</v>
+        <v>46183</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
@@ -3959,7 +4085,7 @@
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="K44" t="s">
         <v>6</v>
@@ -3974,25 +4100,25 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="P44" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q44" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R44" t="s">
         <v>1</v>
       </c>
       <c r="S44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="s">
         <v>12</v>
       </c>
       <c r="U44" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="V44" t="s">
         <v>1</v>
@@ -4009,19 +4135,19 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="E45" s="2">
-        <v>46139</v>
+        <v>46183</v>
       </c>
       <c r="F45" s="3">
         <v>1</v>
@@ -4036,7 +4162,7 @@
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K45" t="s">
         <v>6</v>
@@ -4054,10 +4180,10 @@
         <v>9</v>
       </c>
       <c r="P45" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q45" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R45" t="s">
         <v>1</v>
@@ -4069,7 +4195,7 @@
         <v>12</v>
       </c>
       <c r="U45" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V45" t="s">
         <v>1</v>
@@ -4086,19 +4212,19 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E46" s="2">
-        <v>46139</v>
+        <v>46183</v>
       </c>
       <c r="F46" s="3">
         <v>1</v>
@@ -4113,7 +4239,7 @@
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K46" t="s">
         <v>6</v>
@@ -4131,10 +4257,10 @@
         <v>9</v>
       </c>
       <c r="P46" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q46" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R46" t="s">
         <v>1</v>
@@ -4146,7 +4272,7 @@
         <v>12</v>
       </c>
       <c r="U46" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V46" t="s">
         <v>1</v>
@@ -4163,19 +4289,19 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="E47" s="2">
-        <v>46139</v>
+        <v>46183</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
@@ -4190,7 +4316,7 @@
         <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="K47" t="s">
         <v>6</v>
@@ -4208,10 +4334,10 @@
         <v>9</v>
       </c>
       <c r="P47" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q47" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R47" t="s">
         <v>1</v>
@@ -4223,7 +4349,7 @@
         <v>12</v>
       </c>
       <c r="U47" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V47" t="s">
         <v>1</v>
@@ -4240,7 +4366,7 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
@@ -4249,10 +4375,10 @@
         <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="E48" s="2">
-        <v>46139</v>
+        <v>46183</v>
       </c>
       <c r="F48" s="3">
         <v>1</v>
@@ -4267,7 +4393,7 @@
         <v>4</v>
       </c>
       <c r="J48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K48" t="s">
         <v>6</v>
@@ -4285,10 +4411,10 @@
         <v>9</v>
       </c>
       <c r="P48" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q48" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R48" t="s">
         <v>1</v>
@@ -4300,7 +4426,7 @@
         <v>12</v>
       </c>
       <c r="U48" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V48" t="s">
         <v>1</v>
@@ -4317,56 +4443,56 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B49" t="s">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="2">
+        <v>46183</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" t="s">
+        <v>124</v>
+      </c>
+      <c r="K49" t="s">
+        <v>6</v>
+      </c>
+      <c r="L49" t="s">
+        <v>7</v>
+      </c>
+      <c r="M49" t="s">
+        <v>8</v>
+      </c>
+      <c r="N49" t="s">
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
+        <v>33</v>
+      </c>
+      <c r="P49" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q49" t="s">
         <v>27</v>
       </c>
-      <c r="E49" s="2">
-        <v>46139</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" t="s">
-        <v>123</v>
-      </c>
-      <c r="K49" t="s">
-        <v>6</v>
-      </c>
-      <c r="L49" t="s">
-        <v>7</v>
-      </c>
-      <c r="M49" t="s">
-        <v>8</v>
-      </c>
-      <c r="N49" t="s">
-        <v>1</v>
-      </c>
-      <c r="O49" t="s">
-        <v>9</v>
-      </c>
-      <c r="P49" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>30</v>
-      </c>
       <c r="R49" t="s">
         <v>1</v>
       </c>
@@ -4377,7 +4503,7 @@
         <v>12</v>
       </c>
       <c r="U49" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V49" t="s">
         <v>1</v>
@@ -4394,67 +4520,67 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B50" t="s">
         <v>1</v>
       </c>
       <c r="C50" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="2">
+        <v>46183</v>
+      </c>
+      <c r="F50" s="3">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>4</v>
+      </c>
+      <c r="J50" t="s">
+        <v>113</v>
+      </c>
+      <c r="K50" t="s">
+        <v>6</v>
+      </c>
+      <c r="L50" t="s">
+        <v>7</v>
+      </c>
+      <c r="M50" t="s">
+        <v>8</v>
+      </c>
+      <c r="N50" t="s">
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
+        <v>33</v>
+      </c>
+      <c r="P50" t="s">
         <v>26</v>
       </c>
-      <c r="D50" t="s">
+      <c r="Q50" t="s">
         <v>27</v>
       </c>
-      <c r="E50" s="2">
-        <v>46140</v>
-      </c>
-      <c r="F50" s="3">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3">
-        <v>0</v>
-      </c>
-      <c r="H50" s="3">
-        <v>1</v>
-      </c>
-      <c r="I50" t="s">
-        <v>4</v>
-      </c>
-      <c r="J50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K50" t="s">
-        <v>6</v>
-      </c>
-      <c r="L50" t="s">
-        <v>7</v>
-      </c>
-      <c r="M50" t="s">
-        <v>8</v>
-      </c>
-      <c r="N50" t="s">
-        <v>1</v>
-      </c>
-      <c r="O50" t="s">
-        <v>24</v>
-      </c>
-      <c r="P50" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>30</v>
-      </c>
       <c r="R50" t="s">
         <v>1</v>
       </c>
       <c r="S50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="s">
         <v>12</v>
       </c>
       <c r="U50" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="V50" t="s">
         <v>1</v>
@@ -4471,19 +4597,19 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="E51" s="2">
-        <v>46135</v>
+        <v>46176</v>
       </c>
       <c r="F51" s="3">
         <v>1</v>
@@ -4498,7 +4624,7 @@
         <v>4</v>
       </c>
       <c r="J51" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K51" t="s">
         <v>6</v>
@@ -4513,25 +4639,25 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="P51" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q51" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R51" t="s">
         <v>1</v>
       </c>
       <c r="S51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="s">
         <v>12</v>
       </c>
       <c r="U51" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="V51" t="s">
         <v>1</v>
@@ -4548,78 +4674,1926 @@
     </row>
     <row r="52" spans="1:25">
       <c r="A52" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
         <v>128</v>
       </c>
-      <c r="B52" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
+        <v>129</v>
+      </c>
+      <c r="E52" s="2">
+        <v>46176</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1</v>
+      </c>
+      <c r="I52" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" t="s">
+        <v>130</v>
+      </c>
+      <c r="K52" t="s">
+        <v>6</v>
+      </c>
+      <c r="L52" t="s">
+        <v>7</v>
+      </c>
+      <c r="M52" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" t="s">
+        <v>1</v>
+      </c>
+      <c r="O52" t="s">
+        <v>25</v>
+      </c>
+      <c r="P52" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>27</v>
+      </c>
+      <c r="R52" t="s">
+        <v>1</v>
+      </c>
+      <c r="S52" s="3">
+        <v>1</v>
+      </c>
+      <c r="T52" t="s">
+        <v>12</v>
+      </c>
+      <c r="U52" t="s">
+        <v>28</v>
+      </c>
+      <c r="V52" t="s">
+        <v>1</v>
+      </c>
+      <c r="W52" t="s">
+        <v>1</v>
+      </c>
+      <c r="X52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25">
+      <c r="A53" t="s">
         <v>131</v>
       </c>
-      <c r="D52" t="s">
-        <v>109</v>
-      </c>
-      <c r="E52" s="2">
-        <v>46135</v>
-      </c>
-      <c r="F52" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>-1</v>
-      </c>
-      <c r="I52" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" t="s">
+      <c r="B53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
         <v>132</v>
       </c>
-      <c r="K52" t="s">
-        <v>6</v>
-      </c>
-      <c r="L52" t="s">
-        <v>7</v>
-      </c>
-      <c r="M52" t="s">
-        <v>8</v>
-      </c>
-      <c r="N52" t="s">
-        <v>1</v>
-      </c>
-      <c r="O52" t="s">
-        <v>48</v>
-      </c>
-      <c r="P52" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>30</v>
-      </c>
-      <c r="R52" t="s">
-        <v>1</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" t="s">
-        <v>12</v>
-      </c>
-      <c r="U52" t="s">
-        <v>1</v>
-      </c>
-      <c r="V52" t="s">
-        <v>1</v>
-      </c>
-      <c r="W52" t="s">
-        <v>1</v>
-      </c>
-      <c r="X52" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y52" t="s">
+      <c r="D53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E53" s="2">
+        <v>46150</v>
+      </c>
+      <c r="F53" s="3">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J53" t="s">
+        <v>134</v>
+      </c>
+      <c r="K53" t="s">
+        <v>6</v>
+      </c>
+      <c r="L53" t="s">
+        <v>7</v>
+      </c>
+      <c r="M53" t="s">
+        <v>8</v>
+      </c>
+      <c r="N53" t="s">
+        <v>1</v>
+      </c>
+      <c r="O53" t="s">
+        <v>9</v>
+      </c>
+      <c r="P53" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>27</v>
+      </c>
+      <c r="R53" t="s">
+        <v>1</v>
+      </c>
+      <c r="S53" s="3">
+        <v>1</v>
+      </c>
+      <c r="T53" t="s">
+        <v>12</v>
+      </c>
+      <c r="U53" t="s">
+        <v>28</v>
+      </c>
+      <c r="V53" t="s">
+        <v>1</v>
+      </c>
+      <c r="W53" t="s">
+        <v>1</v>
+      </c>
+      <c r="X53" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25">
+      <c r="A54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54" s="2">
+        <v>46155</v>
+      </c>
+      <c r="F54" s="3">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3">
+        <v>1</v>
+      </c>
+      <c r="I54" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" t="s">
+        <v>24</v>
+      </c>
+      <c r="K54" t="s">
+        <v>6</v>
+      </c>
+      <c r="L54" t="s">
+        <v>7</v>
+      </c>
+      <c r="M54" t="s">
+        <v>8</v>
+      </c>
+      <c r="N54" t="s">
+        <v>1</v>
+      </c>
+      <c r="O54" t="s">
+        <v>25</v>
+      </c>
+      <c r="P54" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>27</v>
+      </c>
+      <c r="R54" t="s">
+        <v>1</v>
+      </c>
+      <c r="S54" s="3">
+        <v>1</v>
+      </c>
+      <c r="T54" t="s">
+        <v>12</v>
+      </c>
+      <c r="U54" t="s">
+        <v>28</v>
+      </c>
+      <c r="V54" t="s">
+        <v>1</v>
+      </c>
+      <c r="W54" t="s">
+        <v>1</v>
+      </c>
+      <c r="X54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25">
+      <c r="A55" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F55" s="3">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3">
+        <v>1</v>
+      </c>
+      <c r="I55" t="s">
+        <v>4</v>
+      </c>
+      <c r="J55" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" t="s">
+        <v>6</v>
+      </c>
+      <c r="L55" t="s">
+        <v>7</v>
+      </c>
+      <c r="M55" t="s">
+        <v>8</v>
+      </c>
+      <c r="N55" t="s">
+        <v>1</v>
+      </c>
+      <c r="O55" t="s">
+        <v>25</v>
+      </c>
+      <c r="P55" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>27</v>
+      </c>
+      <c r="R55" t="s">
+        <v>1</v>
+      </c>
+      <c r="S55" s="3">
+        <v>1</v>
+      </c>
+      <c r="T55" t="s">
+        <v>12</v>
+      </c>
+      <c r="U55" t="s">
+        <v>28</v>
+      </c>
+      <c r="V55" t="s">
+        <v>1</v>
+      </c>
+      <c r="W55" t="s">
+        <v>1</v>
+      </c>
+      <c r="X55" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25">
+      <c r="A56" t="s">
+        <v>137</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" t="s">
+        <v>96</v>
+      </c>
+      <c r="E56" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F56" s="3">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" t="s">
+        <v>4</v>
+      </c>
+      <c r="J56" t="s">
+        <v>24</v>
+      </c>
+      <c r="K56" t="s">
+        <v>6</v>
+      </c>
+      <c r="L56" t="s">
+        <v>7</v>
+      </c>
+      <c r="M56" t="s">
+        <v>8</v>
+      </c>
+      <c r="N56" t="s">
+        <v>1</v>
+      </c>
+      <c r="O56" t="s">
+        <v>25</v>
+      </c>
+      <c r="P56" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>27</v>
+      </c>
+      <c r="R56" t="s">
+        <v>1</v>
+      </c>
+      <c r="S56" s="3">
+        <v>1</v>
+      </c>
+      <c r="T56" t="s">
+        <v>12</v>
+      </c>
+      <c r="U56" t="s">
+        <v>28</v>
+      </c>
+      <c r="V56" t="s">
+        <v>1</v>
+      </c>
+      <c r="W56" t="s">
+        <v>1</v>
+      </c>
+      <c r="X56" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25">
+      <c r="A57" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="2">
+        <v>46177</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" t="s">
+        <v>6</v>
+      </c>
+      <c r="L57" t="s">
+        <v>7</v>
+      </c>
+      <c r="M57" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" t="s">
+        <v>1</v>
+      </c>
+      <c r="O57" t="s">
+        <v>25</v>
+      </c>
+      <c r="P57" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>27</v>
+      </c>
+      <c r="R57" t="s">
+        <v>1</v>
+      </c>
+      <c r="S57" s="3">
+        <v>1</v>
+      </c>
+      <c r="T57" t="s">
+        <v>12</v>
+      </c>
+      <c r="U57" t="s">
+        <v>28</v>
+      </c>
+      <c r="V57" t="s">
+        <v>1</v>
+      </c>
+      <c r="W57" t="s">
+        <v>1</v>
+      </c>
+      <c r="X57" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25">
+      <c r="A58" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" t="s">
+        <v>96</v>
+      </c>
+      <c r="E58" s="2">
+        <v>46177</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1</v>
+      </c>
+      <c r="I58" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" t="s">
+        <v>24</v>
+      </c>
+      <c r="K58" t="s">
+        <v>6</v>
+      </c>
+      <c r="L58" t="s">
+        <v>7</v>
+      </c>
+      <c r="M58" t="s">
+        <v>8</v>
+      </c>
+      <c r="N58" t="s">
+        <v>1</v>
+      </c>
+      <c r="O58" t="s">
+        <v>25</v>
+      </c>
+      <c r="P58" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>27</v>
+      </c>
+      <c r="R58" t="s">
+        <v>1</v>
+      </c>
+      <c r="S58" s="3">
+        <v>1</v>
+      </c>
+      <c r="T58" t="s">
+        <v>12</v>
+      </c>
+      <c r="U58" t="s">
+        <v>28</v>
+      </c>
+      <c r="V58" t="s">
+        <v>1</v>
+      </c>
+      <c r="W58" t="s">
+        <v>1</v>
+      </c>
+      <c r="X58" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25">
+      <c r="A59" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>141</v>
+      </c>
+      <c r="D59" t="s">
+        <v>51</v>
+      </c>
+      <c r="E59" s="2">
+        <v>46177</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1</v>
+      </c>
+      <c r="I59" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" t="s">
+        <v>142</v>
+      </c>
+      <c r="K59" t="s">
+        <v>6</v>
+      </c>
+      <c r="L59" t="s">
+        <v>7</v>
+      </c>
+      <c r="M59" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" t="s">
+        <v>1</v>
+      </c>
+      <c r="O59" t="s">
+        <v>25</v>
+      </c>
+      <c r="P59" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>27</v>
+      </c>
+      <c r="R59" t="s">
+        <v>1</v>
+      </c>
+      <c r="S59" s="3">
+        <v>1</v>
+      </c>
+      <c r="T59" t="s">
+        <v>12</v>
+      </c>
+      <c r="U59" t="s">
+        <v>28</v>
+      </c>
+      <c r="V59" t="s">
+        <v>1</v>
+      </c>
+      <c r="W59" t="s">
+        <v>1</v>
+      </c>
+      <c r="X59" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25">
+      <c r="A60" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="2">
+        <v>46177</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
+        <v>1</v>
+      </c>
+      <c r="I60" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" t="s">
+        <v>144</v>
+      </c>
+      <c r="K60" t="s">
+        <v>6</v>
+      </c>
+      <c r="L60" t="s">
+        <v>7</v>
+      </c>
+      <c r="M60" t="s">
+        <v>8</v>
+      </c>
+      <c r="N60" t="s">
+        <v>1</v>
+      </c>
+      <c r="O60" t="s">
+        <v>25</v>
+      </c>
+      <c r="P60" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>27</v>
+      </c>
+      <c r="R60" t="s">
+        <v>1</v>
+      </c>
+      <c r="S60" s="3">
+        <v>1</v>
+      </c>
+      <c r="T60" t="s">
+        <v>12</v>
+      </c>
+      <c r="U60" t="s">
+        <v>28</v>
+      </c>
+      <c r="V60" t="s">
+        <v>1</v>
+      </c>
+      <c r="W60" t="s">
+        <v>1</v>
+      </c>
+      <c r="X60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25">
+      <c r="A61" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>145</v>
+      </c>
+      <c r="D61" t="s">
+        <v>146</v>
+      </c>
+      <c r="E61" s="2">
+        <v>46177</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>4</v>
+      </c>
+      <c r="J61" t="s">
+        <v>147</v>
+      </c>
+      <c r="K61" t="s">
+        <v>6</v>
+      </c>
+      <c r="L61" t="s">
+        <v>7</v>
+      </c>
+      <c r="M61" t="s">
+        <v>8</v>
+      </c>
+      <c r="N61" t="s">
+        <v>1</v>
+      </c>
+      <c r="O61" t="s">
+        <v>25</v>
+      </c>
+      <c r="P61" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>27</v>
+      </c>
+      <c r="R61" t="s">
+        <v>1</v>
+      </c>
+      <c r="S61" s="3">
+        <v>1</v>
+      </c>
+      <c r="T61" t="s">
+        <v>12</v>
+      </c>
+      <c r="U61" t="s">
+        <v>28</v>
+      </c>
+      <c r="V61" t="s">
+        <v>1</v>
+      </c>
+      <c r="W61" t="s">
+        <v>1</v>
+      </c>
+      <c r="X61" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25">
+      <c r="A62" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" s="2">
+        <v>46177</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" t="s">
+        <v>6</v>
+      </c>
+      <c r="L62" t="s">
+        <v>7</v>
+      </c>
+      <c r="M62" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" t="s">
+        <v>1</v>
+      </c>
+      <c r="O62" t="s">
+        <v>25</v>
+      </c>
+      <c r="P62" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>27</v>
+      </c>
+      <c r="R62" t="s">
+        <v>1</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1</v>
+      </c>
+      <c r="T62" t="s">
+        <v>12</v>
+      </c>
+      <c r="U62" t="s">
+        <v>28</v>
+      </c>
+      <c r="V62" t="s">
+        <v>1</v>
+      </c>
+      <c r="W62" t="s">
+        <v>1</v>
+      </c>
+      <c r="X62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25">
+      <c r="A63" t="s">
+        <v>148</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>149</v>
+      </c>
+      <c r="D63" t="s">
+        <v>121</v>
+      </c>
+      <c r="E63" s="2">
+        <v>46157</v>
+      </c>
+      <c r="F63" s="3">
+        <v>66</v>
+      </c>
+      <c r="G63" s="3">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3">
+        <v>66</v>
+      </c>
+      <c r="I63" t="s">
+        <v>4</v>
+      </c>
+      <c r="J63" t="s">
+        <v>150</v>
+      </c>
+      <c r="K63" t="s">
+        <v>6</v>
+      </c>
+      <c r="L63" t="s">
+        <v>7</v>
+      </c>
+      <c r="M63" t="s">
+        <v>8</v>
+      </c>
+      <c r="N63" t="s">
+        <v>1</v>
+      </c>
+      <c r="O63" t="s">
+        <v>45</v>
+      </c>
+      <c r="P63" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>27</v>
+      </c>
+      <c r="R63" t="s">
+        <v>1</v>
+      </c>
+      <c r="S63" s="3">
+        <v>66</v>
+      </c>
+      <c r="T63" t="s">
+        <v>12</v>
+      </c>
+      <c r="U63" t="s">
+        <v>28</v>
+      </c>
+      <c r="V63" t="s">
+        <v>1</v>
+      </c>
+      <c r="W63" t="s">
+        <v>1</v>
+      </c>
+      <c r="X63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25">
+      <c r="A64" t="s">
+        <v>148</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D64" t="s">
+        <v>54</v>
+      </c>
+      <c r="E64" s="2">
+        <v>46157</v>
+      </c>
+      <c r="F64" s="3">
+        <v>1</v>
+      </c>
+      <c r="G64" s="3">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3">
+        <v>1</v>
+      </c>
+      <c r="I64" t="s">
+        <v>4</v>
+      </c>
+      <c r="J64" t="s">
+        <v>152</v>
+      </c>
+      <c r="K64" t="s">
+        <v>6</v>
+      </c>
+      <c r="L64" t="s">
+        <v>7</v>
+      </c>
+      <c r="M64" t="s">
+        <v>8</v>
+      </c>
+      <c r="N64" t="s">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
+        <v>25</v>
+      </c>
+      <c r="P64" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>27</v>
+      </c>
+      <c r="R64" t="s">
+        <v>1</v>
+      </c>
+      <c r="S64" s="3">
+        <v>1</v>
+      </c>
+      <c r="T64" t="s">
+        <v>12</v>
+      </c>
+      <c r="U64" t="s">
+        <v>28</v>
+      </c>
+      <c r="V64" t="s">
+        <v>1</v>
+      </c>
+      <c r="W64" t="s">
+        <v>1</v>
+      </c>
+      <c r="X64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25">
+      <c r="A65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65" t="s">
+        <v>154</v>
+      </c>
+      <c r="E65" s="2">
+        <v>46157</v>
+      </c>
+      <c r="F65" s="3">
+        <v>1</v>
+      </c>
+      <c r="G65" s="3">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3">
+        <v>1</v>
+      </c>
+      <c r="I65" t="s">
+        <v>4</v>
+      </c>
+      <c r="J65" t="s">
+        <v>155</v>
+      </c>
+      <c r="K65" t="s">
+        <v>6</v>
+      </c>
+      <c r="L65" t="s">
+        <v>7</v>
+      </c>
+      <c r="M65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N65" t="s">
+        <v>1</v>
+      </c>
+      <c r="O65" t="s">
+        <v>25</v>
+      </c>
+      <c r="P65" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>27</v>
+      </c>
+      <c r="R65" t="s">
+        <v>1</v>
+      </c>
+      <c r="S65" s="3">
+        <v>1</v>
+      </c>
+      <c r="T65" t="s">
+        <v>12</v>
+      </c>
+      <c r="U65" t="s">
+        <v>28</v>
+      </c>
+      <c r="V65" t="s">
+        <v>1</v>
+      </c>
+      <c r="W65" t="s">
+        <v>1</v>
+      </c>
+      <c r="X65" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25">
+      <c r="A66" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66" t="s">
+        <v>116</v>
+      </c>
+      <c r="E66" s="2">
+        <v>46190</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" t="s">
+        <v>117</v>
+      </c>
+      <c r="K66" t="s">
+        <v>6</v>
+      </c>
+      <c r="L66" t="s">
+        <v>7</v>
+      </c>
+      <c r="M66" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" t="s">
+        <v>1</v>
+      </c>
+      <c r="O66" t="s">
+        <v>9</v>
+      </c>
+      <c r="P66" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>27</v>
+      </c>
+      <c r="R66" t="s">
+        <v>1</v>
+      </c>
+      <c r="S66" s="3">
+        <v>1</v>
+      </c>
+      <c r="T66" t="s">
+        <v>12</v>
+      </c>
+      <c r="U66" t="s">
+        <v>28</v>
+      </c>
+      <c r="V66" t="s">
+        <v>1</v>
+      </c>
+      <c r="W66" t="s">
+        <v>1</v>
+      </c>
+      <c r="X66" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25">
+      <c r="A67" t="s">
+        <v>156</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>157</v>
+      </c>
+      <c r="D67" t="s">
+        <v>42</v>
+      </c>
+      <c r="E67" s="2">
+        <v>46190</v>
+      </c>
+      <c r="F67" s="3">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3">
+        <v>1</v>
+      </c>
+      <c r="I67" t="s">
+        <v>4</v>
+      </c>
+      <c r="J67" t="s">
+        <v>158</v>
+      </c>
+      <c r="K67" t="s">
+        <v>6</v>
+      </c>
+      <c r="L67" t="s">
+        <v>7</v>
+      </c>
+      <c r="M67" t="s">
+        <v>8</v>
+      </c>
+      <c r="N67" t="s">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>9</v>
+      </c>
+      <c r="P67" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>27</v>
+      </c>
+      <c r="R67" t="s">
+        <v>1</v>
+      </c>
+      <c r="S67" s="3">
+        <v>1</v>
+      </c>
+      <c r="T67" t="s">
+        <v>12</v>
+      </c>
+      <c r="U67" t="s">
+        <v>28</v>
+      </c>
+      <c r="V67" t="s">
+        <v>1</v>
+      </c>
+      <c r="W67" t="s">
+        <v>1</v>
+      </c>
+      <c r="X67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25">
+      <c r="A68" t="s">
+        <v>156</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>110</v>
+      </c>
+      <c r="D68" t="s">
+        <v>159</v>
+      </c>
+      <c r="E68" s="2">
+        <v>46190</v>
+      </c>
+      <c r="F68" s="3">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>4</v>
+      </c>
+      <c r="J68" t="s">
+        <v>111</v>
+      </c>
+      <c r="K68" t="s">
+        <v>6</v>
+      </c>
+      <c r="L68" t="s">
+        <v>7</v>
+      </c>
+      <c r="M68" t="s">
+        <v>8</v>
+      </c>
+      <c r="N68" t="s">
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
+        <v>9</v>
+      </c>
+      <c r="P68" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>27</v>
+      </c>
+      <c r="R68" t="s">
+        <v>1</v>
+      </c>
+      <c r="S68" s="3">
+        <v>1</v>
+      </c>
+      <c r="T68" t="s">
+        <v>12</v>
+      </c>
+      <c r="U68" t="s">
+        <v>28</v>
+      </c>
+      <c r="V68" t="s">
+        <v>1</v>
+      </c>
+      <c r="W68" t="s">
+        <v>1</v>
+      </c>
+      <c r="X68" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25">
+      <c r="A69" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>120</v>
+      </c>
+      <c r="D69" t="s">
+        <v>68</v>
+      </c>
+      <c r="E69" s="2">
+        <v>46190</v>
+      </c>
+      <c r="F69" s="3">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3">
+        <v>1</v>
+      </c>
+      <c r="I69" t="s">
+        <v>4</v>
+      </c>
+      <c r="J69" t="s">
+        <v>122</v>
+      </c>
+      <c r="K69" t="s">
+        <v>6</v>
+      </c>
+      <c r="L69" t="s">
+        <v>7</v>
+      </c>
+      <c r="M69" t="s">
+        <v>8</v>
+      </c>
+      <c r="N69" t="s">
+        <v>1</v>
+      </c>
+      <c r="O69" t="s">
+        <v>9</v>
+      </c>
+      <c r="P69" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>27</v>
+      </c>
+      <c r="R69" t="s">
+        <v>1</v>
+      </c>
+      <c r="S69" s="3">
+        <v>1</v>
+      </c>
+      <c r="T69" t="s">
+        <v>12</v>
+      </c>
+      <c r="U69" t="s">
+        <v>28</v>
+      </c>
+      <c r="V69" t="s">
+        <v>1</v>
+      </c>
+      <c r="W69" t="s">
+        <v>1</v>
+      </c>
+      <c r="X69" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25">
+      <c r="A70" t="s">
+        <v>156</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>160</v>
+      </c>
+      <c r="D70" t="s">
+        <v>161</v>
+      </c>
+      <c r="E70" s="2">
+        <v>46190</v>
+      </c>
+      <c r="F70" s="3">
+        <v>1</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <v>1</v>
+      </c>
+      <c r="I70" t="s">
+        <v>4</v>
+      </c>
+      <c r="J70" t="s">
+        <v>162</v>
+      </c>
+      <c r="K70" t="s">
+        <v>6</v>
+      </c>
+      <c r="L70" t="s">
+        <v>7</v>
+      </c>
+      <c r="M70" t="s">
+        <v>8</v>
+      </c>
+      <c r="N70" t="s">
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
+        <v>9</v>
+      </c>
+      <c r="P70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>27</v>
+      </c>
+      <c r="R70" t="s">
+        <v>1</v>
+      </c>
+      <c r="S70" s="3">
+        <v>1</v>
+      </c>
+      <c r="T70" t="s">
+        <v>12</v>
+      </c>
+      <c r="U70" t="s">
+        <v>28</v>
+      </c>
+      <c r="V70" t="s">
+        <v>1</v>
+      </c>
+      <c r="W70" t="s">
+        <v>1</v>
+      </c>
+      <c r="X70" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25">
+      <c r="A71" t="s">
+        <v>163</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
+        <v>164</v>
+      </c>
+      <c r="D71" t="s">
+        <v>165</v>
+      </c>
+      <c r="E71" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F71" s="3">
+        <v>2</v>
+      </c>
+      <c r="G71" s="3">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3">
+        <v>2</v>
+      </c>
+      <c r="I71" t="s">
+        <v>4</v>
+      </c>
+      <c r="J71" t="s">
+        <v>166</v>
+      </c>
+      <c r="K71" t="s">
+        <v>6</v>
+      </c>
+      <c r="L71" t="s">
+        <v>7</v>
+      </c>
+      <c r="M71" t="s">
+        <v>8</v>
+      </c>
+      <c r="N71" t="s">
+        <v>1</v>
+      </c>
+      <c r="O71" t="s">
+        <v>70</v>
+      </c>
+      <c r="P71" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>27</v>
+      </c>
+      <c r="R71" t="s">
+        <v>1</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" t="s">
+        <v>12</v>
+      </c>
+      <c r="U71" t="s">
+        <v>28</v>
+      </c>
+      <c r="V71" t="s">
+        <v>1</v>
+      </c>
+      <c r="W71" t="s">
+        <v>1</v>
+      </c>
+      <c r="X71" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25">
+      <c r="A72" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
+        <v>167</v>
+      </c>
+      <c r="D72" t="s">
+        <v>36</v>
+      </c>
+      <c r="E72" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F72" s="3">
+        <v>1</v>
+      </c>
+      <c r="G72" s="3">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" t="s">
+        <v>168</v>
+      </c>
+      <c r="K72" t="s">
+        <v>6</v>
+      </c>
+      <c r="L72" t="s">
+        <v>7</v>
+      </c>
+      <c r="M72" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" t="s">
+        <v>1</v>
+      </c>
+      <c r="O72" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>27</v>
+      </c>
+      <c r="R72" t="s">
+        <v>1</v>
+      </c>
+      <c r="S72" s="3">
+        <v>0</v>
+      </c>
+      <c r="T72" t="s">
+        <v>12</v>
+      </c>
+      <c r="U72" t="s">
+        <v>39</v>
+      </c>
+      <c r="V72" t="s">
+        <v>1</v>
+      </c>
+      <c r="W72" t="s">
+        <v>1</v>
+      </c>
+      <c r="X72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25">
+      <c r="A73" t="s">
+        <v>163</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s">
+        <v>115</v>
+      </c>
+      <c r="D73" t="s">
+        <v>169</v>
+      </c>
+      <c r="E73" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F73" s="3">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>4</v>
+      </c>
+      <c r="J73" t="s">
+        <v>117</v>
+      </c>
+      <c r="K73" t="s">
+        <v>6</v>
+      </c>
+      <c r="L73" t="s">
+        <v>7</v>
+      </c>
+      <c r="M73" t="s">
+        <v>8</v>
+      </c>
+      <c r="N73" t="s">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
+        <v>9</v>
+      </c>
+      <c r="P73" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>27</v>
+      </c>
+      <c r="R73" t="s">
+        <v>1</v>
+      </c>
+      <c r="S73" s="3">
+        <v>1</v>
+      </c>
+      <c r="T73" t="s">
+        <v>12</v>
+      </c>
+      <c r="U73" t="s">
+        <v>28</v>
+      </c>
+      <c r="V73" t="s">
+        <v>1</v>
+      </c>
+      <c r="W73" t="s">
+        <v>1</v>
+      </c>
+      <c r="X73" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25">
+      <c r="A74" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>157</v>
+      </c>
+      <c r="D74" t="s">
+        <v>42</v>
+      </c>
+      <c r="E74" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F74" s="3">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>4</v>
+      </c>
+      <c r="J74" t="s">
+        <v>158</v>
+      </c>
+      <c r="K74" t="s">
+        <v>6</v>
+      </c>
+      <c r="L74" t="s">
+        <v>7</v>
+      </c>
+      <c r="M74" t="s">
+        <v>8</v>
+      </c>
+      <c r="N74" t="s">
+        <v>1</v>
+      </c>
+      <c r="O74" t="s">
+        <v>9</v>
+      </c>
+      <c r="P74" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>27</v>
+      </c>
+      <c r="R74" t="s">
+        <v>1</v>
+      </c>
+      <c r="S74" s="3">
+        <v>1</v>
+      </c>
+      <c r="T74" t="s">
+        <v>12</v>
+      </c>
+      <c r="U74" t="s">
+        <v>28</v>
+      </c>
+      <c r="V74" t="s">
+        <v>1</v>
+      </c>
+      <c r="W74" t="s">
+        <v>1</v>
+      </c>
+      <c r="X74" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25">
+      <c r="A75" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>170</v>
+      </c>
+      <c r="D75" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F75" s="3">
+        <v>1</v>
+      </c>
+      <c r="G75" s="3">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>4</v>
+      </c>
+      <c r="J75" t="s">
+        <v>172</v>
+      </c>
+      <c r="K75" t="s">
+        <v>6</v>
+      </c>
+      <c r="L75" t="s">
+        <v>7</v>
+      </c>
+      <c r="M75" t="s">
+        <v>8</v>
+      </c>
+      <c r="N75" t="s">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
+        <v>9</v>
+      </c>
+      <c r="P75" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>27</v>
+      </c>
+      <c r="R75" t="s">
+        <v>1</v>
+      </c>
+      <c r="S75" s="3">
+        <v>1</v>
+      </c>
+      <c r="T75" t="s">
+        <v>12</v>
+      </c>
+      <c r="U75" t="s">
+        <v>28</v>
+      </c>
+      <c r="V75" t="s">
+        <v>1</v>
+      </c>
+      <c r="W75" t="s">
+        <v>1</v>
+      </c>
+      <c r="X75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25">
+      <c r="A76" t="s">
+        <v>163</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>173</v>
+      </c>
+      <c r="D76" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1</v>
+      </c>
+      <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
+        <v>1</v>
+      </c>
+      <c r="I76" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" t="s">
+        <v>174</v>
+      </c>
+      <c r="K76" t="s">
+        <v>6</v>
+      </c>
+      <c r="L76" t="s">
+        <v>7</v>
+      </c>
+      <c r="M76" t="s">
+        <v>8</v>
+      </c>
+      <c r="N76" t="s">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
+        <v>33</v>
+      </c>
+      <c r="P76" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>27</v>
+      </c>
+      <c r="R76" t="s">
+        <v>1</v>
+      </c>
+      <c r="S76" s="3">
+        <v>1</v>
+      </c>
+      <c r="T76" t="s">
+        <v>12</v>
+      </c>
+      <c r="U76" t="s">
+        <v>28</v>
+      </c>
+      <c r="V76" t="s">
+        <v>1</v>
+      </c>
+      <c r="W76" t="s">
+        <v>1</v>
+      </c>
+      <c r="X76" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y76" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Newdata/已撥缺料.XLSX
+++ b/Newdata/已撥缺料.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="206">
   <si>
     <t>200006482</t>
   </si>
@@ -247,6 +247,27 @@
     <t>內藏式主軸轉子,FANUC_A06B-2726-B651#2231</t>
   </si>
   <si>
+    <t>200006605</t>
+  </si>
+  <si>
+    <t>8814001434A2</t>
+  </si>
+  <si>
+    <t>機頭加工圖,HSKA63D長套筒_MVP-8</t>
+  </si>
+  <si>
+    <t>200006606</t>
+  </si>
+  <si>
+    <t>8310000698A0</t>
+  </si>
+  <si>
+    <t>0080</t>
+  </si>
+  <si>
+    <t>直結主軸馬達座,含冷卻_d230*85H,S-Plus10</t>
+  </si>
+  <si>
     <t>200006624</t>
   </si>
   <si>
@@ -518,9 +539,6 @@
   </si>
   <si>
     <t>G6K 主軸,021327_BT50,0045</t>
-  </si>
-  <si>
-    <t>0080</t>
   </si>
   <si>
     <t>3216000148B1</t>
@@ -715,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y76"/>
+  <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -747,79 +765,79 @@
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -2373,26 +2391,26 @@
         <v>79</v>
       </c>
       <c r="D22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46167</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="2">
-        <v>46161</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1</v>
-      </c>
-      <c r="I22" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" t="s">
-        <v>81</v>
-      </c>
       <c r="K22" t="s">
         <v>6</v>
       </c>
@@ -2406,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="O22" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="P22" t="s">
         <v>26</v>
@@ -2441,19 +2459,19 @@
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
@@ -2468,7 +2486,7 @@
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K23" t="s">
         <v>6</v>
@@ -2483,7 +2501,7 @@
         <v>1</v>
       </c>
       <c r="O23" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="P23" t="s">
         <v>26</v>
@@ -2518,35 +2536,35 @@
     </row>
     <row r="24" spans="1:25">
       <c r="A24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="2">
+        <v>46167</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" t="s">
         <v>84</v>
       </c>
-      <c r="B24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="2">
-        <v>46161</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1</v>
-      </c>
-      <c r="I24" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" t="s">
-        <v>87</v>
-      </c>
       <c r="K24" t="s">
         <v>6</v>
       </c>
@@ -2560,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P24" t="s">
         <v>26</v>
@@ -2572,13 +2590,13 @@
         <v>1</v>
       </c>
       <c r="S24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="s">
         <v>12</v>
       </c>
       <c r="U24" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="V24" t="s">
         <v>1</v>
@@ -2595,35 +2613,35 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="2">
+        <v>46161</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J25" t="s">
         <v>88</v>
       </c>
-      <c r="B25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="2">
-        <v>46153</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1</v>
-      </c>
-      <c r="I25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J25" t="s">
-        <v>90</v>
-      </c>
       <c r="K25" t="s">
         <v>6</v>
       </c>
@@ -2637,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P25" t="s">
         <v>26</v>
@@ -2672,19 +2690,19 @@
     </row>
     <row r="26" spans="1:25">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="E26" s="2">
-        <v>46150</v>
+        <v>46161</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
@@ -2699,7 +2717,7 @@
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s">
         <v>6</v>
@@ -2714,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="P26" t="s">
         <v>26</v>
@@ -2732,7 +2750,7 @@
         <v>12</v>
       </c>
       <c r="U26" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="V26" t="s">
         <v>1</v>
@@ -2749,19 +2767,19 @@
     </row>
     <row r="27" spans="1:25">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E27" s="2">
-        <v>46133</v>
+        <v>46161</v>
       </c>
       <c r="F27" s="3">
         <v>1</v>
@@ -2776,7 +2794,7 @@
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s">
         <v>6</v>
@@ -2832,13 +2850,13 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="E28" s="2">
-        <v>46133</v>
+        <v>46153</v>
       </c>
       <c r="F28" s="3">
         <v>1</v>
@@ -2853,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="K28" t="s">
         <v>6</v>
@@ -2868,7 +2886,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P28" t="s">
         <v>26</v>
@@ -2903,19 +2921,19 @@
     </row>
     <row r="29" spans="1:25">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="E29" s="2">
-        <v>46134</v>
+        <v>46150</v>
       </c>
       <c r="F29" s="3">
         <v>1</v>
@@ -2930,7 +2948,7 @@
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="K29" t="s">
         <v>6</v>
@@ -2945,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="P29" t="s">
         <v>26</v>
@@ -2963,7 +2981,7 @@
         <v>12</v>
       </c>
       <c r="U29" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="V29" t="s">
         <v>1</v>
@@ -2980,19 +2998,19 @@
     </row>
     <row r="30" spans="1:25">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E30" s="2">
-        <v>46139</v>
+        <v>46133</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
@@ -3007,7 +3025,7 @@
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s">
         <v>6</v>
@@ -3022,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P30" t="s">
         <v>26</v>
@@ -3057,19 +3075,19 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="E31" s="2">
-        <v>46139</v>
+        <v>46133</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -3084,7 +3102,7 @@
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s">
         <v>6</v>
@@ -3099,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P31" t="s">
         <v>26</v>
@@ -3134,19 +3152,19 @@
     </row>
     <row r="32" spans="1:25">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E32" s="2">
-        <v>46139</v>
+        <v>46134</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
@@ -3161,7 +3179,7 @@
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="K32" t="s">
         <v>6</v>
@@ -3176,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="P32" t="s">
         <v>26</v>
@@ -3217,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
         <v>70</v>
@@ -3238,7 +3256,7 @@
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K33" t="s">
         <v>6</v>
@@ -3294,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
         <v>42</v>
@@ -3315,7 +3333,7 @@
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K34" t="s">
         <v>6</v>
@@ -3371,7 +3389,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D35" t="s">
         <v>23</v>
@@ -3392,7 +3410,7 @@
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="K35" t="s">
         <v>6</v>
@@ -3442,13 +3460,13 @@
     </row>
     <row r="36" spans="1:25">
       <c r="A36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
         <v>106</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>99</v>
       </c>
       <c r="D36" t="s">
         <v>70</v>
@@ -3469,7 +3487,7 @@
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K36" t="s">
         <v>6</v>
@@ -3519,13 +3537,13 @@
     </row>
     <row r="37" spans="1:25">
       <c r="A37" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
         <v>42</v>
@@ -3546,7 +3564,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K37" t="s">
         <v>6</v>
@@ -3596,13 +3614,13 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
         <v>23</v>
@@ -3623,7 +3641,7 @@
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="K38" t="s">
         <v>6</v>
@@ -3673,13 +3691,13 @@
     </row>
     <row r="39" spans="1:25">
       <c r="A39" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
         <v>70</v>
@@ -3700,7 +3718,7 @@
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K39" t="s">
         <v>6</v>
@@ -3750,13 +3768,13 @@
     </row>
     <row r="40" spans="1:25">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D40" t="s">
         <v>42</v>
@@ -3777,7 +3795,7 @@
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K40" t="s">
         <v>6</v>
@@ -3827,13 +3845,13 @@
     </row>
     <row r="41" spans="1:25">
       <c r="A41" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
         <v>23</v>
@@ -3854,7 +3872,7 @@
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="K41" t="s">
         <v>6</v>
@@ -3904,19 +3922,19 @@
     </row>
     <row r="42" spans="1:25">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E42" s="2">
-        <v>46140</v>
+        <v>46139</v>
       </c>
       <c r="F42" s="3">
         <v>1</v>
@@ -3931,7 +3949,7 @@
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="K42" t="s">
         <v>6</v>
@@ -3946,7 +3964,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P42" t="s">
         <v>26</v>
@@ -3981,34 +3999,34 @@
     </row>
     <row r="43" spans="1:25">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="2">
+        <v>46139</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" t="s">
         <v>109</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D43" t="s">
-        <v>31</v>
-      </c>
-      <c r="E43" s="2">
-        <v>46183</v>
-      </c>
-      <c r="F43" s="3">
-        <v>1</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" t="s">
-        <v>111</v>
       </c>
       <c r="K43" t="s">
         <v>6</v>
@@ -4058,19 +4076,19 @@
     </row>
     <row r="44" spans="1:25">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E44" s="2">
-        <v>46183</v>
+        <v>46139</v>
       </c>
       <c r="F44" s="3">
         <v>1</v>
@@ -4085,7 +4103,7 @@
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K44" t="s">
         <v>6</v>
@@ -4100,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="P44" t="s">
         <v>26</v>
@@ -4112,13 +4130,13 @@
         <v>1</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" t="s">
         <v>12</v>
       </c>
       <c r="U44" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="V44" t="s">
         <v>1</v>
@@ -4135,19 +4153,19 @@
     </row>
     <row r="45" spans="1:25">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="E45" s="2">
-        <v>46183</v>
+        <v>46140</v>
       </c>
       <c r="F45" s="3">
         <v>1</v>
@@ -4162,7 +4180,7 @@
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>117</v>
+        <v>24</v>
       </c>
       <c r="K45" t="s">
         <v>6</v>
@@ -4177,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="O45" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P45" t="s">
         <v>26</v>
@@ -4212,13 +4230,13 @@
     </row>
     <row r="46" spans="1:25">
       <c r="A46" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D46" t="s">
         <v>31</v>
@@ -4239,7 +4257,7 @@
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K46" t="s">
         <v>6</v>
@@ -4289,16 +4307,16 @@
     </row>
     <row r="47" spans="1:25">
       <c r="A47" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E47" s="2">
         <v>46183</v>
@@ -4316,7 +4334,7 @@
         <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K47" t="s">
         <v>6</v>
@@ -4331,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="O47" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="P47" t="s">
         <v>26</v>
@@ -4343,13 +4361,13 @@
         <v>1</v>
       </c>
       <c r="S47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="s">
         <v>12</v>
       </c>
       <c r="U47" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="V47" t="s">
         <v>1</v>
@@ -4366,16 +4384,16 @@
     </row>
     <row r="48" spans="1:25">
       <c r="A48" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D48" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E48" s="2">
         <v>46183</v>
@@ -4393,7 +4411,7 @@
         <v>4</v>
       </c>
       <c r="J48" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K48" t="s">
         <v>6</v>
@@ -4443,16 +4461,16 @@
     </row>
     <row r="49" spans="1:25">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E49" s="2">
         <v>46183</v>
@@ -4470,7 +4488,7 @@
         <v>4</v>
       </c>
       <c r="J49" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K49" t="s">
         <v>6</v>
@@ -4485,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="P49" t="s">
         <v>26</v>
@@ -4520,16 +4538,16 @@
     </row>
     <row r="50" spans="1:25">
       <c r="A50" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B50" t="s">
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E50" s="2">
         <v>46183</v>
@@ -4547,7 +4565,7 @@
         <v>4</v>
       </c>
       <c r="J50" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K50" t="s">
         <v>6</v>
@@ -4562,7 +4580,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="P50" t="s">
         <v>26</v>
@@ -4574,13 +4592,13 @@
         <v>1</v>
       </c>
       <c r="S50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" t="s">
         <v>12</v>
       </c>
       <c r="U50" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="V50" t="s">
         <v>1</v>
@@ -4597,19 +4615,19 @@
     </row>
     <row r="51" spans="1:25">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="E51" s="2">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="F51" s="3">
         <v>1</v>
@@ -4624,7 +4642,7 @@
         <v>4</v>
       </c>
       <c r="J51" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K51" t="s">
         <v>6</v>
@@ -4639,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P51" t="s">
         <v>26</v>
@@ -4674,19 +4692,19 @@
     </row>
     <row r="52" spans="1:25">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B52" t="s">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D52" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="E52" s="2">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="F52" s="3">
         <v>1</v>
@@ -4701,7 +4719,7 @@
         <v>4</v>
       </c>
       <c r="J52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K52" t="s">
         <v>6</v>
@@ -4716,7 +4734,7 @@
         <v>1</v>
       </c>
       <c r="O52" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="P52" t="s">
         <v>26</v>
@@ -4751,19 +4769,19 @@
     </row>
     <row r="53" spans="1:25">
       <c r="A53" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B53" t="s">
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="E53" s="2">
-        <v>46150</v>
+        <v>46183</v>
       </c>
       <c r="F53" s="3">
         <v>1</v>
@@ -4778,7 +4796,7 @@
         <v>4</v>
       </c>
       <c r="J53" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="K53" t="s">
         <v>6</v>
@@ -4793,7 +4811,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="P53" t="s">
         <v>26</v>
@@ -4805,13 +4823,13 @@
         <v>1</v>
       </c>
       <c r="S53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="s">
         <v>12</v>
       </c>
       <c r="U53" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="V53" t="s">
         <v>1</v>
@@ -4828,19 +4846,19 @@
     </row>
     <row r="54" spans="1:25">
       <c r="A54" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B54" t="s">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="D54" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="E54" s="2">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="F54" s="3">
         <v>1</v>
@@ -4855,7 +4873,7 @@
         <v>4</v>
       </c>
       <c r="J54" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="K54" t="s">
         <v>6</v>
@@ -4905,19 +4923,19 @@
     </row>
     <row r="55" spans="1:25">
       <c r="A55" t="s">
+        <v>132</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" t="s">
         <v>136</v>
       </c>
-      <c r="B55" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D55" t="s">
-        <v>96</v>
-      </c>
       <c r="E55" s="2">
-        <v>46156</v>
+        <v>46176</v>
       </c>
       <c r="F55" s="3">
         <v>1</v>
@@ -4932,7 +4950,7 @@
         <v>4</v>
       </c>
       <c r="J55" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="K55" t="s">
         <v>6</v>
@@ -4982,19 +5000,19 @@
     </row>
     <row r="56" spans="1:25">
       <c r="A56" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B56" t="s">
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="D56" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2">
-        <v>46156</v>
+        <v>46150</v>
       </c>
       <c r="F56" s="3">
         <v>1</v>
@@ -5009,7 +5027,7 @@
         <v>4</v>
       </c>
       <c r="J56" t="s">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="K56" t="s">
         <v>6</v>
@@ -5024,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P56" t="s">
         <v>26</v>
@@ -5059,7 +5077,7 @@
     </row>
     <row r="57" spans="1:25">
       <c r="A57" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
@@ -5068,10 +5086,10 @@
         <v>22</v>
       </c>
       <c r="D57" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E57" s="2">
-        <v>46177</v>
+        <v>46155</v>
       </c>
       <c r="F57" s="3">
         <v>1</v>
@@ -5136,7 +5154,7 @@
     </row>
     <row r="58" spans="1:25">
       <c r="A58" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B58" t="s">
         <v>1</v>
@@ -5145,10 +5163,10 @@
         <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E58" s="2">
-        <v>46177</v>
+        <v>46156</v>
       </c>
       <c r="F58" s="3">
         <v>1</v>
@@ -5213,19 +5231,19 @@
     </row>
     <row r="59" spans="1:25">
       <c r="A59" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B59" t="s">
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="E59" s="2">
-        <v>46177</v>
+        <v>46156</v>
       </c>
       <c r="F59" s="3">
         <v>1</v>
@@ -5240,7 +5258,7 @@
         <v>4</v>
       </c>
       <c r="J59" t="s">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="K59" t="s">
         <v>6</v>
@@ -5290,16 +5308,16 @@
     </row>
     <row r="60" spans="1:25">
       <c r="A60" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B60" t="s">
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>143</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="E60" s="2">
         <v>46177</v>
@@ -5317,7 +5335,7 @@
         <v>4</v>
       </c>
       <c r="J60" t="s">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="K60" t="s">
         <v>6</v>
@@ -5367,16 +5385,16 @@
     </row>
     <row r="61" spans="1:25">
       <c r="A61" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B61" t="s">
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="D61" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="E61" s="2">
         <v>46177</v>
@@ -5394,7 +5412,7 @@
         <v>4</v>
       </c>
       <c r="J61" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="K61" t="s">
         <v>6</v>
@@ -5444,16 +5462,16 @@
     </row>
     <row r="62" spans="1:25">
       <c r="A62" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B62" t="s">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="D62" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="E62" s="2">
         <v>46177</v>
@@ -5471,7 +5489,7 @@
         <v>4</v>
       </c>
       <c r="J62" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="K62" t="s">
         <v>6</v>
@@ -5521,34 +5539,34 @@
     </row>
     <row r="63" spans="1:25">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B63" t="s">
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D63" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="E63" s="2">
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="F63" s="3">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="G63" s="3">
         <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="I63" t="s">
         <v>4</v>
       </c>
       <c r="J63" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K63" t="s">
         <v>6</v>
@@ -5563,7 +5581,7 @@
         <v>1</v>
       </c>
       <c r="O63" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="P63" t="s">
         <v>26</v>
@@ -5575,7 +5593,7 @@
         <v>1</v>
       </c>
       <c r="S63" s="3">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="T63" t="s">
         <v>12</v>
@@ -5598,19 +5616,19 @@
     </row>
     <row r="64" spans="1:25">
       <c r="A64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B64" t="s">
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="E64" s="2">
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="F64" s="3">
         <v>1</v>
@@ -5625,7 +5643,7 @@
         <v>4</v>
       </c>
       <c r="J64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K64" t="s">
         <v>6</v>
@@ -5675,19 +5693,19 @@
     </row>
     <row r="65" spans="1:25">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B65" t="s">
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="D65" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="E65" s="2">
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="F65" s="3">
         <v>1</v>
@@ -5702,7 +5720,7 @@
         <v>4</v>
       </c>
       <c r="J65" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="K65" t="s">
         <v>6</v>
@@ -5752,34 +5770,34 @@
     </row>
     <row r="66" spans="1:25">
       <c r="A66" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
         <v>156</v>
       </c>
-      <c r="B66" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" t="s">
-        <v>115</v>
-      </c>
       <c r="D66" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E66" s="2">
-        <v>46190</v>
+        <v>46157</v>
       </c>
       <c r="F66" s="3">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="G66" s="3">
         <v>0</v>
       </c>
       <c r="H66" s="3">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="I66" t="s">
         <v>4</v>
       </c>
       <c r="J66" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="K66" t="s">
         <v>6</v>
@@ -5794,7 +5812,7 @@
         <v>1</v>
       </c>
       <c r="O66" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="P66" t="s">
         <v>26</v>
@@ -5806,7 +5824,7 @@
         <v>1</v>
       </c>
       <c r="S66" s="3">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="T66" t="s">
         <v>12</v>
@@ -5829,19 +5847,19 @@
     </row>
     <row r="67" spans="1:25">
       <c r="A67" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B67" t="s">
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D67" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E67" s="2">
-        <v>46190</v>
+        <v>46157</v>
       </c>
       <c r="F67" s="3">
         <v>1</v>
@@ -5856,7 +5874,7 @@
         <v>4</v>
       </c>
       <c r="J67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K67" t="s">
         <v>6</v>
@@ -5871,7 +5889,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P67" t="s">
         <v>26</v>
@@ -5906,19 +5924,19 @@
     </row>
     <row r="68" spans="1:25">
       <c r="A68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B68" t="s">
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="D68" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E68" s="2">
-        <v>46190</v>
+        <v>46157</v>
       </c>
       <c r="F68" s="3">
         <v>1</v>
@@ -5933,7 +5951,7 @@
         <v>4</v>
       </c>
       <c r="J68" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="K68" t="s">
         <v>6</v>
@@ -5948,7 +5966,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="P68" t="s">
         <v>26</v>
@@ -5983,16 +6001,16 @@
     </row>
     <row r="69" spans="1:25">
       <c r="A69" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B69" t="s">
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D69" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="E69" s="2">
         <v>46190</v>
@@ -6010,7 +6028,7 @@
         <v>4</v>
       </c>
       <c r="J69" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K69" t="s">
         <v>6</v>
@@ -6060,16 +6078,16 @@
     </row>
     <row r="70" spans="1:25">
       <c r="A70" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D70" t="s">
-        <v>161</v>
+        <v>42</v>
       </c>
       <c r="E70" s="2">
         <v>46190</v>
@@ -6087,7 +6105,7 @@
         <v>4</v>
       </c>
       <c r="J70" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K70" t="s">
         <v>6</v>
@@ -6143,28 +6161,28 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="D71" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E71" s="2">
-        <v>46156</v>
+        <v>46190</v>
       </c>
       <c r="F71" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" s="3">
         <v>0</v>
       </c>
       <c r="H71" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71" t="s">
         <v>4</v>
       </c>
       <c r="J71" t="s">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="K71" t="s">
         <v>6</v>
@@ -6179,7 +6197,7 @@
         <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="P71" t="s">
         <v>26</v>
@@ -6191,7 +6209,7 @@
         <v>1</v>
       </c>
       <c r="S71" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="s">
         <v>12</v>
@@ -6220,13 +6238,13 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="D72" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E72" s="2">
-        <v>46156</v>
+        <v>46190</v>
       </c>
       <c r="F72" s="3">
         <v>1</v>
@@ -6241,7 +6259,7 @@
         <v>4</v>
       </c>
       <c r="J72" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="K72" t="s">
         <v>6</v>
@@ -6256,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="P72" t="s">
         <v>26</v>
@@ -6268,13 +6286,13 @@
         <v>1</v>
       </c>
       <c r="S72" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="s">
         <v>12</v>
       </c>
       <c r="U72" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="V72" t="s">
         <v>1</v>
@@ -6297,28 +6315,28 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="D73" t="s">
+        <v>168</v>
+      </c>
+      <c r="E73" s="2">
+        <v>46190</v>
+      </c>
+      <c r="F73" s="3">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>4</v>
+      </c>
+      <c r="J73" t="s">
         <v>169</v>
-      </c>
-      <c r="E73" s="2">
-        <v>46156</v>
-      </c>
-      <c r="F73" s="3">
-        <v>1</v>
-      </c>
-      <c r="G73" s="3">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3">
-        <v>1</v>
-      </c>
-      <c r="I73" t="s">
-        <v>4</v>
-      </c>
-      <c r="J73" t="s">
-        <v>117</v>
       </c>
       <c r="K73" t="s">
         <v>6</v>
@@ -6368,34 +6386,34 @@
     </row>
     <row r="74" spans="1:25">
       <c r="A74" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B74" t="s">
         <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D74" t="s">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="E74" s="2">
         <v>46156</v>
       </c>
       <c r="F74" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="3">
         <v>0</v>
       </c>
       <c r="H74" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" t="s">
         <v>4</v>
       </c>
       <c r="J74" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="K74" t="s">
         <v>6</v>
@@ -6410,7 +6428,7 @@
         <v>1</v>
       </c>
       <c r="O74" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="P74" t="s">
         <v>26</v>
@@ -6422,7 +6440,7 @@
         <v>1</v>
       </c>
       <c r="S74" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T74" t="s">
         <v>12</v>
@@ -6445,16 +6463,16 @@
     </row>
     <row r="75" spans="1:25">
       <c r="A75" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B75" t="s">
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="E75" s="2">
         <v>46156</v>
@@ -6472,7 +6490,7 @@
         <v>4</v>
       </c>
       <c r="J75" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K75" t="s">
         <v>6</v>
@@ -6487,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="P75" t="s">
         <v>26</v>
@@ -6499,13 +6517,13 @@
         <v>1</v>
       </c>
       <c r="S75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75" t="s">
         <v>12</v>
       </c>
       <c r="U75" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="V75" t="s">
         <v>1</v>
@@ -6522,16 +6540,16 @@
     </row>
     <row r="76" spans="1:25">
       <c r="A76" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B76" t="s">
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="D76" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E76" s="2">
         <v>46156</v>
@@ -6549,7 +6567,7 @@
         <v>4</v>
       </c>
       <c r="J76" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="K76" t="s">
         <v>6</v>
@@ -6564,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="O76" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="P76" t="s">
         <v>26</v>
@@ -6594,6 +6612,237 @@
         <v>1</v>
       </c>
       <c r="Y76" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25">
+      <c r="A77" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>164</v>
+      </c>
+      <c r="D77" t="s">
+        <v>42</v>
+      </c>
+      <c r="E77" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F77" s="3">
+        <v>1</v>
+      </c>
+      <c r="G77" s="3">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3">
+        <v>1</v>
+      </c>
+      <c r="I77" t="s">
+        <v>4</v>
+      </c>
+      <c r="J77" t="s">
+        <v>165</v>
+      </c>
+      <c r="K77" t="s">
+        <v>6</v>
+      </c>
+      <c r="L77" t="s">
+        <v>7</v>
+      </c>
+      <c r="M77" t="s">
+        <v>8</v>
+      </c>
+      <c r="N77" t="s">
+        <v>1</v>
+      </c>
+      <c r="O77" t="s">
+        <v>9</v>
+      </c>
+      <c r="P77" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>27</v>
+      </c>
+      <c r="R77" t="s">
+        <v>1</v>
+      </c>
+      <c r="S77" s="3">
+        <v>1</v>
+      </c>
+      <c r="T77" t="s">
+        <v>12</v>
+      </c>
+      <c r="U77" t="s">
+        <v>28</v>
+      </c>
+      <c r="V77" t="s">
+        <v>1</v>
+      </c>
+      <c r="W77" t="s">
+        <v>1</v>
+      </c>
+      <c r="X77" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25">
+      <c r="A78" t="s">
+        <v>170</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>176</v>
+      </c>
+      <c r="D78" t="s">
+        <v>177</v>
+      </c>
+      <c r="E78" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F78" s="3">
+        <v>1</v>
+      </c>
+      <c r="G78" s="3">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>4</v>
+      </c>
+      <c r="J78" t="s">
+        <v>178</v>
+      </c>
+      <c r="K78" t="s">
+        <v>6</v>
+      </c>
+      <c r="L78" t="s">
+        <v>7</v>
+      </c>
+      <c r="M78" t="s">
+        <v>8</v>
+      </c>
+      <c r="N78" t="s">
+        <v>1</v>
+      </c>
+      <c r="O78" t="s">
+        <v>9</v>
+      </c>
+      <c r="P78" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>27</v>
+      </c>
+      <c r="R78" t="s">
+        <v>1</v>
+      </c>
+      <c r="S78" s="3">
+        <v>1</v>
+      </c>
+      <c r="T78" t="s">
+        <v>12</v>
+      </c>
+      <c r="U78" t="s">
+        <v>28</v>
+      </c>
+      <c r="V78" t="s">
+        <v>1</v>
+      </c>
+      <c r="W78" t="s">
+        <v>1</v>
+      </c>
+      <c r="X78" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25">
+      <c r="A79" t="s">
+        <v>170</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>179</v>
+      </c>
+      <c r="D79" t="s">
+        <v>31</v>
+      </c>
+      <c r="E79" s="2">
+        <v>46156</v>
+      </c>
+      <c r="F79" s="3">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>4</v>
+      </c>
+      <c r="J79" t="s">
+        <v>180</v>
+      </c>
+      <c r="K79" t="s">
+        <v>6</v>
+      </c>
+      <c r="L79" t="s">
+        <v>7</v>
+      </c>
+      <c r="M79" t="s">
+        <v>8</v>
+      </c>
+      <c r="N79" t="s">
+        <v>1</v>
+      </c>
+      <c r="O79" t="s">
+        <v>33</v>
+      </c>
+      <c r="P79" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>27</v>
+      </c>
+      <c r="R79" t="s">
+        <v>1</v>
+      </c>
+      <c r="S79" s="3">
+        <v>1</v>
+      </c>
+      <c r="T79" t="s">
+        <v>12</v>
+      </c>
+      <c r="U79" t="s">
+        <v>28</v>
+      </c>
+      <c r="V79" t="s">
+        <v>1</v>
+      </c>
+      <c r="W79" t="s">
+        <v>1</v>
+      </c>
+      <c r="X79" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="s">
         <v>14</v>
       </c>
     </row>
